--- a/dados/notas_fiscais.xlsx
+++ b/dados/notas_fiscais.xlsx
@@ -1,18 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <workbookPr defaultThemeVersion="202300"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\juliaflora\Documents\JULIA\Relatórios\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D821664-E4B8-41FC-816D-BC4C02CF57E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Registros_1" sheetId="1" r:id="rId1"/>
+    <sheet name="SQL" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="572" uniqueCount="572">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1811" uniqueCount="601">
   <si>
     <t>CPF_CNPJ</t>
   </si>
@@ -1728,14 +1737,100 @@
   </si>
   <si>
     <t>001861787</t>
+  </si>
+  <si>
+    <t>SELECT --NOTAS FISCAIS LIGADAS AO PEG - COMPETÊNCIA CONTÁBIL DO PEG 07 e 08/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    PRE.CPFCNPJ                                  AS CPF_CNPJ,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    PRE.NOME                                     AS NOME_PRESTADOR,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    PRE.FANTASIA                                 AS NOME_FANTASIA_PRESTADOR,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    CATP.DESCRICAO                               AS CATEGORIA_PRESTADOR,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    TPP.DESCRICAO                                AS TIPO_PRESTADOR,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    DFN.NUMERONOTA                               AS NUMERO_NOTA,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    TO_CHAR(DFN.DATAEMISSAO,'DD/MM/YYYY')        AS DATA_EMISSAO,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    TO_CHAR(DFN.DATAINCLUSAO,'MM/YYYY')          AS MES_INCLUSAO,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    TO_CHAR(PG.PRIMEIRA_DATACONTABIL,'MM/YYYY')  AS MES_ANO,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    TO_CHAR(PG.ULTIMA_DATACONTABIL,'MM/YYYY')    AS MES_ANO_ULTIMO,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    PG.QTD_PEG                                   AS QTD_PEG_VINCULADOS,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    DFN.VALOR                                    AS VALOR_NOTA</t>
+  </si>
+  <si>
+    <t>FROM SAM_DOCUMENTOFISCAL_NOTA DFN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    JOIN SAM_DOCUMENTOFISCAL    DF ON DF.HANDLE = DFN.DOCUMENTOFISCAL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    JOIN SAM_AGRUPADORPAGAMENTO AP ON AP.HANDLE = DF.PAGAMENTO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    JOIN (SELECT P.AGRUPADORPAGAMENTO,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">                 MIN(P.DATACONTABIL) AS PRIMEIRA_DATACONTABIL,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">                 MAX(P.DATACONTABIL) AS ULTIMA_DATACONTABIL,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">                 COUNT(*)            AS QTD_PEG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">          FROM SAM_PEG P</t>
+  </si>
+  <si>
+    <t xml:space="preserve">          WHERE P.AGRUPADORPAGAMENTO IS NOT NULL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">            AND P.DATACONTABIL &gt;= TO_DATE('01/07/2026','DD/MM/YYYY')</t>
+  </si>
+  <si>
+    <t xml:space="preserve">            AND P.DATACONTABIL &lt;  TO_DATE('01/09/2026','DD/MM/YYYY')</t>
+  </si>
+  <si>
+    <t xml:space="preserve">          GROUP BY P.AGRUPADORPAGAMENTO) PG ON PG.AGRUPADORPAGAMENTO = AP.HANDLE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    JOIN SAM_PRESTADOR PRE                 ON PRE.HANDLE = AP.RECEBEDOR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    LEFT JOIN SAM_CATEGORIA_PRESTADOR CATP ON CATP.HANDLE = PRE.CATEGORIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    LEFT JOIN SAM_TIPOPRESTADOR       TPP  ON TPP.HANDLE  = PRE.TIPOPRESTADOR</t>
+  </si>
+  <si>
+    <t>ORDER BY PRE.NOME, MES_ANO</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -1764,40 +1859,364 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="3">
-    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" xfId="0" applyProtection="1"/>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="1" applyFont="1" xfId="0" applyProtection="1"/>
-    <xf numFmtId="2" applyNumberFormat="1" fontId="0" applyFont="1" xfId="0" applyProtection="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema do Office">
+  <a:themeElements>
+    <a:clrScheme name="Office">
+      <a:dk1>
+        <a:sysClr val="windowText" lastClr="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="0E2841"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="E8E8E8"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="156082"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="E97132"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="196B24"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="0F9ED5"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="A02B93"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="4EA72E"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="467886"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="96607D"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック Light"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线 Light"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme name="Office">
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="110000"/>
+                <a:satMod val="105000"/>
+                <a:tint val="67000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="103000"/>
+                <a:tint val="73000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="109000"/>
+                <a:tint val="81000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:satMod val="103000"/>
+                <a:lumMod val="102000"/>
+                <a:tint val="94000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:satMod val="110000"/>
+                <a:lumMod val="100000"/>
+                <a:shade val="100000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="99000"/>
+                <a:satMod val="120000"/>
+                <a:shade val="78000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="63000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:tint val="95000"/>
+            <a:satMod val="170000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="93000"/>
+                <a:satMod val="150000"/>
+                <a:shade val="98000"/>
+                <a:lumMod val="102000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:tint val="98000"/>
+                <a:satMod val="130000"/>
+                <a:shade val="90000"/>
+                <a:lumMod val="103000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="63000"/>
+                <a:satMod val="120000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+  <a:objectDefaults>
+    <a:lnDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </a:style>
+    </a:lnDef>
+  </a:objectDefaults>
+  <a:extraClrSchemeLst/>
+  <a:extLst>
+    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
+    </a:ext>
+  </a:extLst>
+</a:theme>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:L178"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="16.7238933018276" customWidth="1"/>
-    <col min="2" max="2" width="73.6257629394531" customWidth="1"/>
-    <col min="3" max="3" width="51.9470084054129" customWidth="1"/>
-    <col min="4" max="4" width="30.0503431047712" customWidth="1"/>
-    <col min="5" max="5" width="41.7644391741071" customWidth="1"/>
-    <col min="6" max="6" width="16.7238933018276" customWidth="1"/>
-    <col min="7" max="7" width="15.853264944894" customWidth="1"/>
-    <col min="8" max="8" width="15.694690159389" customWidth="1"/>
-    <col min="9" max="9" width="10.635632106236" customWidth="1"/>
-    <col min="10" max="10" width="19.0216979980469" customWidth="1"/>
-    <col min="11" max="11" width="22.9328765869141" customWidth="1"/>
-    <col min="12" max="12" width="13.9155796595982" customWidth="1"/>
+    <col min="1" max="1" width="16.7109375" customWidth="1"/>
+    <col min="2" max="2" width="73.5703125" customWidth="1"/>
+    <col min="3" max="3" width="52" customWidth="1"/>
+    <col min="4" max="4" width="30" customWidth="1"/>
+    <col min="5" max="5" width="41.7109375" customWidth="1"/>
+    <col min="6" max="6" width="16.7109375" customWidth="1"/>
+    <col min="7" max="7" width="15.85546875" customWidth="1"/>
+    <col min="8" max="8" width="15.7109375" customWidth="1"/>
+    <col min="9" max="9" width="10.5703125" customWidth="1"/>
+    <col min="10" max="10" width="19" customWidth="1"/>
+    <col min="11" max="11" width="23" customWidth="1"/>
+    <col min="12" max="12" width="13.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1835,35 +2254,35 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="0" t="s">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
         <v>12</v>
       </c>
-      <c r="B2" s="0" t="s">
+      <c r="B2" t="s">
         <v>13</v>
       </c>
-      <c r="C2" s="0" t="s">
+      <c r="C2" t="s">
         <v>14</v>
       </c>
-      <c r="D2" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="E2" s="0" t="s">
+      <c r="D2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E2" t="s">
         <v>16</v>
       </c>
-      <c r="F2" s="0" t="s">
+      <c r="F2" t="s">
         <v>17</v>
       </c>
-      <c r="G2" s="0" t="s">
+      <c r="G2" t="s">
         <v>18</v>
       </c>
-      <c r="H2" s="0" t="s">
-        <v>19</v>
-      </c>
-      <c r="I2" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="J2" s="0" t="s">
+      <c r="H2" t="s">
+        <v>19</v>
+      </c>
+      <c r="I2" t="s">
+        <v>20</v>
+      </c>
+      <c r="J2" t="s">
         <v>20</v>
       </c>
       <c r="K2" s="2">
@@ -1873,35 +2292,35 @@
         <v>3225</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="0" t="s">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
         <v>12</v>
       </c>
-      <c r="B3" s="0" t="s">
+      <c r="B3" t="s">
         <v>13</v>
       </c>
-      <c r="C3" s="0" t="s">
+      <c r="C3" t="s">
         <v>14</v>
       </c>
-      <c r="D3" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="E3" s="0" t="s">
+      <c r="D3" t="s">
+        <v>15</v>
+      </c>
+      <c r="E3" t="s">
         <v>16</v>
       </c>
-      <c r="F3" s="0" t="s">
+      <c r="F3" t="s">
         <v>21</v>
       </c>
-      <c r="G3" s="0" t="s">
+      <c r="G3" t="s">
         <v>22</v>
       </c>
-      <c r="H3" s="0" t="s">
-        <v>19</v>
-      </c>
-      <c r="I3" s="0" t="s">
+      <c r="H3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I3" t="s">
         <v>23</v>
       </c>
-      <c r="J3" s="0" t="s">
+      <c r="J3" t="s">
         <v>23</v>
       </c>
       <c r="K3" s="2">
@@ -1911,35 +2330,35 @@
         <v>3225</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="0" t="s">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
         <v>24</v>
       </c>
-      <c r="B4" s="0" t="s">
+      <c r="B4" t="s">
         <v>25</v>
       </c>
-      <c r="C4" s="0" t="s">
+      <c r="C4" t="s">
         <v>26</v>
       </c>
-      <c r="D4" s="0" t="s">
+      <c r="D4" t="s">
         <v>27</v>
       </c>
-      <c r="E4" s="0" t="s">
+      <c r="E4" t="s">
         <v>28</v>
       </c>
-      <c r="F4" s="0" t="s">
+      <c r="F4" t="s">
         <v>29</v>
       </c>
-      <c r="G4" s="0" t="s">
+      <c r="G4" t="s">
         <v>30</v>
       </c>
-      <c r="H4" s="0" t="s">
-        <v>19</v>
-      </c>
-      <c r="I4" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="J4" s="0" t="s">
+      <c r="H4" t="s">
+        <v>19</v>
+      </c>
+      <c r="I4" t="s">
+        <v>20</v>
+      </c>
+      <c r="J4" t="s">
         <v>20</v>
       </c>
       <c r="K4" s="2">
@@ -1949,35 +2368,35 @@
         <v>104</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="0" t="s">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
         <v>24</v>
       </c>
-      <c r="B5" s="0" t="s">
+      <c r="B5" t="s">
         <v>25</v>
       </c>
-      <c r="C5" s="0" t="s">
+      <c r="C5" t="s">
         <v>26</v>
       </c>
-      <c r="D5" s="0" t="s">
+      <c r="D5" t="s">
         <v>27</v>
       </c>
-      <c r="E5" s="0" t="s">
+      <c r="E5" t="s">
         <v>28</v>
       </c>
-      <c r="F5" s="0" t="s">
+      <c r="F5" t="s">
         <v>31</v>
       </c>
-      <c r="G5" s="0" t="s">
+      <c r="G5" t="s">
         <v>30</v>
       </c>
-      <c r="H5" s="0" t="s">
-        <v>19</v>
-      </c>
-      <c r="I5" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="J5" s="0" t="s">
+      <c r="H5" t="s">
+        <v>19</v>
+      </c>
+      <c r="I5" t="s">
+        <v>20</v>
+      </c>
+      <c r="J5" t="s">
         <v>20</v>
       </c>
       <c r="K5" s="2">
@@ -1987,35 +2406,35 @@
         <v>406.5</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="0" t="s">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
         <v>32</v>
       </c>
-      <c r="B6" s="0" t="s">
+      <c r="B6" t="s">
         <v>33</v>
       </c>
-      <c r="C6" s="0" t="s">
+      <c r="C6" t="s">
         <v>34</v>
       </c>
-      <c r="D6" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="E6" s="0" t="s">
+      <c r="D6" t="s">
+        <v>15</v>
+      </c>
+      <c r="E6" t="s">
         <v>16</v>
       </c>
-      <c r="F6" s="0" t="s">
+      <c r="F6" t="s">
         <v>35</v>
       </c>
-      <c r="G6" s="0" t="s">
+      <c r="G6" t="s">
         <v>36</v>
       </c>
-      <c r="H6" s="0" t="s">
-        <v>19</v>
-      </c>
-      <c r="I6" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="J6" s="0" t="s">
+      <c r="H6" t="s">
+        <v>19</v>
+      </c>
+      <c r="I6" t="s">
+        <v>20</v>
+      </c>
+      <c r="J6" t="s">
         <v>20</v>
       </c>
       <c r="K6" s="2">
@@ -2025,35 +2444,35 @@
         <v>5350</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="0" t="s">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="0" t="s">
+      <c r="B7" t="s">
         <v>38</v>
       </c>
-      <c r="C7" s="0" t="s">
+      <c r="C7" t="s">
         <v>39</v>
       </c>
-      <c r="D7" s="0" t="s">
+      <c r="D7" t="s">
         <v>40</v>
       </c>
-      <c r="E7" s="0" t="s">
+      <c r="E7" t="s">
         <v>28</v>
       </c>
-      <c r="F7" s="0" t="s">
+      <c r="F7" t="s">
         <v>41</v>
       </c>
-      <c r="G7" s="0" t="s">
+      <c r="G7" t="s">
         <v>42</v>
       </c>
-      <c r="H7" s="0" t="s">
-        <v>19</v>
-      </c>
-      <c r="I7" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="J7" s="0" t="s">
+      <c r="H7" t="s">
+        <v>19</v>
+      </c>
+      <c r="I7" t="s">
+        <v>20</v>
+      </c>
+      <c r="J7" t="s">
         <v>20</v>
       </c>
       <c r="K7" s="2">
@@ -2063,35 +2482,35 @@
         <v>22800</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="0" t="s">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
         <v>37</v>
       </c>
-      <c r="B8" s="0" t="s">
+      <c r="B8" t="s">
         <v>38</v>
       </c>
-      <c r="C8" s="0" t="s">
+      <c r="C8" t="s">
         <v>39</v>
       </c>
-      <c r="D8" s="0" t="s">
+      <c r="D8" t="s">
         <v>40</v>
       </c>
-      <c r="E8" s="0" t="s">
+      <c r="E8" t="s">
         <v>28</v>
       </c>
-      <c r="F8" s="0" t="s">
+      <c r="F8" t="s">
         <v>43</v>
       </c>
-      <c r="G8" s="0" t="s">
+      <c r="G8" t="s">
         <v>44</v>
       </c>
-      <c r="H8" s="0" t="s">
-        <v>19</v>
-      </c>
-      <c r="I8" s="0" t="s">
+      <c r="H8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I8" t="s">
         <v>23</v>
       </c>
-      <c r="J8" s="0" t="s">
+      <c r="J8" t="s">
         <v>23</v>
       </c>
       <c r="K8" s="2">
@@ -2101,35 +2520,35 @@
         <v>19200</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="0" t="s">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
         <v>45</v>
       </c>
-      <c r="B9" s="0" t="s">
+      <c r="B9" t="s">
         <v>46</v>
       </c>
-      <c r="C9" s="0" t="s">
+      <c r="C9" t="s">
         <v>47</v>
       </c>
-      <c r="D9" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="E9" s="0" t="s">
+      <c r="D9" t="s">
+        <v>15</v>
+      </c>
+      <c r="E9" t="s">
         <v>16</v>
       </c>
-      <c r="F9" s="0" t="s">
+      <c r="F9" t="s">
         <v>48</v>
       </c>
-      <c r="G9" s="0" t="s">
+      <c r="G9" t="s">
         <v>49</v>
       </c>
-      <c r="H9" s="0" t="s">
+      <c r="H9" t="s">
         <v>23</v>
       </c>
-      <c r="I9" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="J9" s="0" t="s">
+      <c r="I9" t="s">
+        <v>20</v>
+      </c>
+      <c r="J9" t="s">
         <v>20</v>
       </c>
       <c r="K9" s="2">
@@ -2139,35 +2558,35 @@
         <v>3800</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="0" t="s">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
         <v>50</v>
       </c>
-      <c r="B10" s="0" t="s">
+      <c r="B10" t="s">
         <v>51</v>
       </c>
-      <c r="C10" s="0" t="s">
+      <c r="C10" t="s">
         <v>51</v>
       </c>
-      <c r="D10" s="0" t="s">
+      <c r="D10" t="s">
         <v>27</v>
       </c>
-      <c r="E10" s="0" t="s">
+      <c r="E10" t="s">
         <v>28</v>
       </c>
-      <c r="F10" s="0" t="s">
+      <c r="F10" t="s">
         <v>52</v>
       </c>
-      <c r="G10" s="0" t="s">
+      <c r="G10" t="s">
         <v>53</v>
       </c>
-      <c r="H10" s="0" t="s">
-        <v>19</v>
-      </c>
-      <c r="I10" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="J10" s="0" t="s">
+      <c r="H10" t="s">
+        <v>19</v>
+      </c>
+      <c r="I10" t="s">
+        <v>20</v>
+      </c>
+      <c r="J10" t="s">
         <v>20</v>
       </c>
       <c r="K10" s="2">
@@ -2177,35 +2596,35 @@
         <v>1190.72</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="0" t="s">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
         <v>54</v>
       </c>
-      <c r="B11" s="0" t="s">
+      <c r="B11" t="s">
         <v>55</v>
       </c>
-      <c r="C11" s="0" t="s">
+      <c r="C11" t="s">
         <v>56</v>
       </c>
-      <c r="D11" s="0" t="s">
+      <c r="D11" t="s">
         <v>27</v>
       </c>
-      <c r="E11" s="0" t="s">
+      <c r="E11" t="s">
         <v>28</v>
       </c>
-      <c r="F11" s="0" t="s">
+      <c r="F11" t="s">
         <v>57</v>
       </c>
-      <c r="G11" s="0" t="s">
+      <c r="G11" t="s">
         <v>58</v>
       </c>
-      <c r="H11" s="0" t="s">
-        <v>19</v>
-      </c>
-      <c r="I11" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="J11" s="0" t="s">
+      <c r="H11" t="s">
+        <v>19</v>
+      </c>
+      <c r="I11" t="s">
+        <v>20</v>
+      </c>
+      <c r="J11" t="s">
         <v>20</v>
       </c>
       <c r="K11" s="2">
@@ -2215,35 +2634,35 @@
         <v>1274.32</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="0" t="s">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
         <v>59</v>
       </c>
-      <c r="B12" s="0" t="s">
+      <c r="B12" t="s">
         <v>60</v>
       </c>
-      <c r="C12" s="0" t="s">
+      <c r="C12" t="s">
         <v>61</v>
       </c>
-      <c r="D12" s="0" t="s">
+      <c r="D12" t="s">
         <v>27</v>
       </c>
-      <c r="E12" s="0" t="s">
+      <c r="E12" t="s">
         <v>28</v>
       </c>
-      <c r="F12" s="0" t="s">
+      <c r="F12" t="s">
         <v>62</v>
       </c>
-      <c r="G12" s="0" t="s">
+      <c r="G12" t="s">
         <v>30</v>
       </c>
-      <c r="H12" s="0" t="s">
-        <v>19</v>
-      </c>
-      <c r="I12" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="J12" s="0" t="s">
+      <c r="H12" t="s">
+        <v>19</v>
+      </c>
+      <c r="I12" t="s">
+        <v>20</v>
+      </c>
+      <c r="J12" t="s">
         <v>20</v>
       </c>
       <c r="K12" s="2">
@@ -2253,35 +2672,35 @@
         <v>1814.72</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="0" t="s">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
         <v>63</v>
       </c>
-      <c r="B13" s="0" t="s">
+      <c r="B13" t="s">
         <v>64</v>
       </c>
-      <c r="C13" s="0" t="s">
+      <c r="C13" t="s">
         <v>64</v>
       </c>
-      <c r="D13" s="0" t="s">
+      <c r="D13" t="s">
         <v>27</v>
       </c>
-      <c r="E13" s="0" t="s">
+      <c r="E13" t="s">
         <v>65</v>
       </c>
-      <c r="F13" s="0" t="s">
+      <c r="F13" t="s">
         <v>66</v>
       </c>
-      <c r="G13" s="0" t="s">
+      <c r="G13" t="s">
         <v>67</v>
       </c>
-      <c r="H13" s="0" t="s">
-        <v>19</v>
-      </c>
-      <c r="I13" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="J13" s="0" t="s">
+      <c r="H13" t="s">
+        <v>19</v>
+      </c>
+      <c r="I13" t="s">
+        <v>20</v>
+      </c>
+      <c r="J13" t="s">
         <v>20</v>
       </c>
       <c r="K13" s="2">
@@ -2291,35 +2710,35 @@
         <v>231222.75</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="0" t="s">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
         <v>68</v>
       </c>
-      <c r="B14" s="0" t="s">
+      <c r="B14" t="s">
         <v>69</v>
       </c>
-      <c r="C14" s="0" t="s">
+      <c r="C14" t="s">
         <v>70</v>
       </c>
-      <c r="D14" s="0" t="s">
+      <c r="D14" t="s">
         <v>27</v>
       </c>
-      <c r="E14" s="0" t="s">
+      <c r="E14" t="s">
         <v>28</v>
       </c>
-      <c r="F14" s="0" t="s">
+      <c r="F14" t="s">
         <v>71</v>
       </c>
-      <c r="G14" s="0" t="s">
+      <c r="G14" t="s">
         <v>72</v>
       </c>
-      <c r="H14" s="0" t="s">
-        <v>19</v>
-      </c>
-      <c r="I14" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="J14" s="0" t="s">
+      <c r="H14" t="s">
+        <v>19</v>
+      </c>
+      <c r="I14" t="s">
+        <v>20</v>
+      </c>
+      <c r="J14" t="s">
         <v>20</v>
       </c>
       <c r="K14" s="2">
@@ -2329,35 +2748,35 @@
         <v>30805</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="0" t="s">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
         <v>73</v>
       </c>
-      <c r="B15" s="0" t="s">
+      <c r="B15" t="s">
         <v>74</v>
       </c>
-      <c r="C15" s="0" t="s">
+      <c r="C15" t="s">
         <v>75</v>
       </c>
-      <c r="D15" s="0" t="s">
+      <c r="D15" t="s">
         <v>27</v>
       </c>
-      <c r="E15" s="0" t="s">
+      <c r="E15" t="s">
         <v>76</v>
       </c>
-      <c r="F15" s="0" t="s">
+      <c r="F15" t="s">
         <v>77</v>
       </c>
-      <c r="G15" s="0" t="s">
+      <c r="G15" t="s">
         <v>78</v>
       </c>
-      <c r="H15" s="0" t="s">
-        <v>19</v>
-      </c>
-      <c r="I15" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="J15" s="0" t="s">
+      <c r="H15" t="s">
+        <v>19</v>
+      </c>
+      <c r="I15" t="s">
+        <v>20</v>
+      </c>
+      <c r="J15" t="s">
         <v>20</v>
       </c>
       <c r="K15" s="2">
@@ -2367,35 +2786,35 @@
         <v>567.84</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="0" t="s">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
         <v>79</v>
       </c>
-      <c r="B16" s="0" t="s">
+      <c r="B16" t="s">
         <v>80</v>
       </c>
-      <c r="C16" s="0" t="s">
+      <c r="C16" t="s">
         <v>81</v>
       </c>
-      <c r="D16" s="0" t="s">
+      <c r="D16" t="s">
         <v>27</v>
       </c>
-      <c r="E16" s="0" t="s">
+      <c r="E16" t="s">
         <v>28</v>
       </c>
-      <c r="F16" s="0" t="s">
+      <c r="F16" t="s">
         <v>82</v>
       </c>
-      <c r="G16" s="0" t="s">
+      <c r="G16" t="s">
         <v>72</v>
       </c>
-      <c r="H16" s="0" t="s">
-        <v>19</v>
-      </c>
-      <c r="I16" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="J16" s="0" t="s">
+      <c r="H16" t="s">
+        <v>19</v>
+      </c>
+      <c r="I16" t="s">
+        <v>20</v>
+      </c>
+      <c r="J16" t="s">
         <v>20</v>
       </c>
       <c r="K16" s="2">
@@ -2405,35 +2824,35 @@
         <v>3087.1</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="0" t="s">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
         <v>83</v>
       </c>
-      <c r="B17" s="0" t="s">
+      <c r="B17" t="s">
         <v>84</v>
       </c>
-      <c r="C17" s="0" t="s">
+      <c r="C17" t="s">
         <v>85</v>
       </c>
-      <c r="D17" s="0" t="s">
+      <c r="D17" t="s">
         <v>27</v>
       </c>
-      <c r="E17" s="0" t="s">
+      <c r="E17" t="s">
         <v>28</v>
       </c>
-      <c r="F17" s="0" t="s">
+      <c r="F17" t="s">
         <v>86</v>
       </c>
-      <c r="G17" s="0" t="s">
+      <c r="G17" t="s">
         <v>87</v>
       </c>
-      <c r="H17" s="0" t="s">
-        <v>19</v>
-      </c>
-      <c r="I17" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="J17" s="0" t="s">
+      <c r="H17" t="s">
+        <v>19</v>
+      </c>
+      <c r="I17" t="s">
+        <v>20</v>
+      </c>
+      <c r="J17" t="s">
         <v>20</v>
       </c>
       <c r="K17" s="2">
@@ -2443,35 +2862,35 @@
         <v>8857.9</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="0" t="s">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
         <v>88</v>
       </c>
-      <c r="B18" s="0" t="s">
+      <c r="B18" t="s">
         <v>89</v>
       </c>
-      <c r="C18" s="0" t="s">
+      <c r="C18" t="s">
         <v>90</v>
       </c>
-      <c r="D18" s="0" t="s">
+      <c r="D18" t="s">
         <v>27</v>
       </c>
-      <c r="E18" s="0" t="s">
+      <c r="E18" t="s">
         <v>28</v>
       </c>
-      <c r="F18" s="0" t="s">
+      <c r="F18" t="s">
         <v>91</v>
       </c>
-      <c r="G18" s="0" t="s">
+      <c r="G18" t="s">
         <v>92</v>
       </c>
-      <c r="H18" s="0" t="s">
-        <v>19</v>
-      </c>
-      <c r="I18" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="J18" s="0" t="s">
+      <c r="H18" t="s">
+        <v>19</v>
+      </c>
+      <c r="I18" t="s">
+        <v>20</v>
+      </c>
+      <c r="J18" t="s">
         <v>20</v>
       </c>
       <c r="K18" s="2">
@@ -2481,35 +2900,35 @@
         <v>7560.25</v>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="0" t="s">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
         <v>93</v>
       </c>
-      <c r="B19" s="0" t="s">
+      <c r="B19" t="s">
         <v>94</v>
       </c>
-      <c r="C19" s="0" t="s">
+      <c r="C19" t="s">
         <v>95</v>
       </c>
-      <c r="D19" s="0" t="s">
+      <c r="D19" t="s">
         <v>27</v>
       </c>
-      <c r="E19" s="0" t="s">
+      <c r="E19" t="s">
         <v>65</v>
       </c>
-      <c r="F19" s="0" t="s">
+      <c r="F19" t="s">
         <v>96</v>
       </c>
-      <c r="G19" s="0" t="s">
+      <c r="G19" t="s">
         <v>53</v>
       </c>
-      <c r="H19" s="0" t="s">
-        <v>19</v>
-      </c>
-      <c r="I19" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="J19" s="0" t="s">
+      <c r="H19" t="s">
+        <v>19</v>
+      </c>
+      <c r="I19" t="s">
+        <v>20</v>
+      </c>
+      <c r="J19" t="s">
         <v>20</v>
       </c>
       <c r="K19" s="2">
@@ -2519,35 +2938,35 @@
         <v>665.78</v>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="0" t="s">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
         <v>97</v>
       </c>
-      <c r="B20" s="0" t="s">
+      <c r="B20" t="s">
         <v>98</v>
       </c>
-      <c r="C20" s="0" t="s">
+      <c r="C20" t="s">
         <v>99</v>
       </c>
-      <c r="D20" s="0" t="s">
+      <c r="D20" t="s">
         <v>27</v>
       </c>
-      <c r="E20" s="0" t="s">
+      <c r="E20" t="s">
         <v>28</v>
       </c>
-      <c r="F20" s="0" t="s">
+      <c r="F20" t="s">
         <v>100</v>
       </c>
-      <c r="G20" s="0" t="s">
+      <c r="G20" t="s">
         <v>101</v>
       </c>
-      <c r="H20" s="0" t="s">
-        <v>19</v>
-      </c>
-      <c r="I20" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="J20" s="0" t="s">
+      <c r="H20" t="s">
+        <v>19</v>
+      </c>
+      <c r="I20" t="s">
+        <v>20</v>
+      </c>
+      <c r="J20" t="s">
         <v>23</v>
       </c>
       <c r="K20" s="2">
@@ -2557,35 +2976,35 @@
         <v>22016.01</v>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="0" t="s">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
         <v>102</v>
       </c>
-      <c r="B21" s="0" t="s">
+      <c r="B21" t="s">
         <v>103</v>
       </c>
-      <c r="C21" s="0" t="s">
+      <c r="C21" t="s">
         <v>104</v>
       </c>
-      <c r="D21" s="0" t="s">
+      <c r="D21" t="s">
         <v>40</v>
       </c>
-      <c r="E21" s="0" t="s">
+      <c r="E21" t="s">
         <v>65</v>
       </c>
-      <c r="F21" s="0" t="s">
+      <c r="F21" t="s">
         <v>105</v>
       </c>
-      <c r="G21" s="0" t="s">
+      <c r="G21" t="s">
         <v>106</v>
       </c>
-      <c r="H21" s="0" t="s">
-        <v>19</v>
-      </c>
-      <c r="I21" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="J21" s="0" t="s">
+      <c r="H21" t="s">
+        <v>19</v>
+      </c>
+      <c r="I21" t="s">
+        <v>20</v>
+      </c>
+      <c r="J21" t="s">
         <v>20</v>
       </c>
       <c r="K21" s="2">
@@ -2595,35 +3014,35 @@
         <v>2100</v>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="0" t="s">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
         <v>107</v>
       </c>
-      <c r="B22" s="0" t="s">
+      <c r="B22" t="s">
         <v>108</v>
       </c>
-      <c r="C22" s="0" t="s">
+      <c r="C22" t="s">
         <v>109</v>
       </c>
-      <c r="D22" s="0" t="s">
+      <c r="D22" t="s">
         <v>27</v>
       </c>
-      <c r="E22" s="0" t="s">
+      <c r="E22" t="s">
         <v>28</v>
       </c>
-      <c r="F22" s="0" t="s">
+      <c r="F22" t="s">
         <v>110</v>
       </c>
-      <c r="G22" s="0" t="s">
+      <c r="G22" t="s">
         <v>101</v>
       </c>
-      <c r="H22" s="0" t="s">
-        <v>19</v>
-      </c>
-      <c r="I22" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="J22" s="0" t="s">
+      <c r="H22" t="s">
+        <v>19</v>
+      </c>
+      <c r="I22" t="s">
+        <v>20</v>
+      </c>
+      <c r="J22" t="s">
         <v>20</v>
       </c>
       <c r="K22" s="2">
@@ -2633,35 +3052,35 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="0" t="s">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
         <v>111</v>
       </c>
-      <c r="B23" s="0" t="s">
+      <c r="B23" t="s">
         <v>112</v>
       </c>
-      <c r="C23" s="0" t="s">
+      <c r="C23" t="s">
         <v>113</v>
       </c>
-      <c r="D23" s="0" t="s">
+      <c r="D23" t="s">
         <v>27</v>
       </c>
-      <c r="E23" s="0" t="s">
+      <c r="E23" t="s">
         <v>76</v>
       </c>
-      <c r="F23" s="0" t="s">
+      <c r="F23" t="s">
         <v>114</v>
       </c>
-      <c r="G23" s="0" t="s">
+      <c r="G23" t="s">
         <v>30</v>
       </c>
-      <c r="H23" s="0" t="s">
-        <v>19</v>
-      </c>
-      <c r="I23" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="J23" s="0" t="s">
+      <c r="H23" t="s">
+        <v>19</v>
+      </c>
+      <c r="I23" t="s">
+        <v>20</v>
+      </c>
+      <c r="J23" t="s">
         <v>20</v>
       </c>
       <c r="K23" s="2">
@@ -2671,35 +3090,35 @@
         <v>30681</v>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="0" t="s">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
         <v>115</v>
       </c>
-      <c r="B24" s="0" t="s">
+      <c r="B24" t="s">
         <v>116</v>
       </c>
-      <c r="C24" s="0" t="s">
+      <c r="C24" t="s">
         <v>117</v>
       </c>
-      <c r="D24" s="0" t="s">
+      <c r="D24" t="s">
         <v>27</v>
       </c>
-      <c r="E24" s="0" t="s">
+      <c r="E24" t="s">
         <v>76</v>
       </c>
-      <c r="F24" s="0" t="s">
+      <c r="F24" t="s">
         <v>118</v>
       </c>
-      <c r="G24" s="0" t="s">
+      <c r="G24" t="s">
         <v>30</v>
       </c>
-      <c r="H24" s="0" t="s">
-        <v>19</v>
-      </c>
-      <c r="I24" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="J24" s="0" t="s">
+      <c r="H24" t="s">
+        <v>19</v>
+      </c>
+      <c r="I24" t="s">
+        <v>20</v>
+      </c>
+      <c r="J24" t="s">
         <v>20</v>
       </c>
       <c r="K24" s="2">
@@ -2709,73 +3128,73 @@
         <v>1570.56</v>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="0" t="s">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
         <v>119</v>
       </c>
-      <c r="B25" s="0" t="s">
+      <c r="B25" t="s">
         <v>120</v>
       </c>
-      <c r="C25" s="0" t="s">
+      <c r="C25" t="s">
         <v>121</v>
       </c>
-      <c r="D25" s="0" t="s">
+      <c r="D25" t="s">
         <v>27</v>
       </c>
-      <c r="E25" s="0" t="s">
+      <c r="E25" t="s">
         <v>76</v>
       </c>
-      <c r="F25" s="0" t="s">
+      <c r="F25" t="s">
         <v>122</v>
       </c>
-      <c r="G25" s="0" t="s">
+      <c r="G25" t="s">
         <v>53</v>
       </c>
-      <c r="H25" s="0" t="s">
-        <v>19</v>
-      </c>
-      <c r="I25" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="J25" s="0" t="s">
+      <c r="H25" t="s">
+        <v>19</v>
+      </c>
+      <c r="I25" t="s">
+        <v>20</v>
+      </c>
+      <c r="J25" t="s">
         <v>20</v>
       </c>
       <c r="K25" s="2">
         <v>2</v>
       </c>
       <c r="L25" s="2">
-        <v>1204.91</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="0" t="s">
+        <v>1204.9100000000001</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
         <v>123</v>
       </c>
-      <c r="B26" s="0" t="s">
+      <c r="B26" t="s">
         <v>120</v>
       </c>
-      <c r="C26" s="0" t="s">
+      <c r="C26" t="s">
         <v>120</v>
       </c>
-      <c r="D26" s="0" t="s">
+      <c r="D26" t="s">
         <v>27</v>
       </c>
-      <c r="E26" s="0" t="s">
+      <c r="E26" t="s">
         <v>76</v>
       </c>
-      <c r="F26" s="0" t="s">
+      <c r="F26" t="s">
         <v>124</v>
       </c>
-      <c r="G26" s="0" t="s">
+      <c r="G26" t="s">
         <v>30</v>
       </c>
-      <c r="H26" s="0" t="s">
-        <v>19</v>
-      </c>
-      <c r="I26" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="J26" s="0" t="s">
+      <c r="H26" t="s">
+        <v>19</v>
+      </c>
+      <c r="I26" t="s">
+        <v>20</v>
+      </c>
+      <c r="J26" t="s">
         <v>20</v>
       </c>
       <c r="K26" s="2">
@@ -2785,35 +3204,35 @@
         <v>4697.38</v>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="0" t="s">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
         <v>125</v>
       </c>
-      <c r="B27" s="0" t="s">
+      <c r="B27" t="s">
         <v>120</v>
       </c>
-      <c r="C27" s="0" t="s">
+      <c r="C27" t="s">
         <v>126</v>
       </c>
-      <c r="D27" s="0" t="s">
+      <c r="D27" t="s">
         <v>27</v>
       </c>
-      <c r="E27" s="0" t="s">
+      <c r="E27" t="s">
         <v>76</v>
       </c>
-      <c r="F27" s="0" t="s">
+      <c r="F27" t="s">
         <v>127</v>
       </c>
-      <c r="G27" s="0" t="s">
+      <c r="G27" t="s">
         <v>53</v>
       </c>
-      <c r="H27" s="0" t="s">
-        <v>19</v>
-      </c>
-      <c r="I27" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="J27" s="0" t="s">
+      <c r="H27" t="s">
+        <v>19</v>
+      </c>
+      <c r="I27" t="s">
+        <v>20</v>
+      </c>
+      <c r="J27" t="s">
         <v>20</v>
       </c>
       <c r="K27" s="2">
@@ -2823,35 +3242,35 @@
         <v>8992.89</v>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="0" t="s">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
         <v>128</v>
       </c>
-      <c r="B28" s="0" t="s">
+      <c r="B28" t="s">
         <v>129</v>
       </c>
-      <c r="C28" s="0" t="s">
+      <c r="C28" t="s">
         <v>130</v>
       </c>
-      <c r="D28" s="0" t="s">
+      <c r="D28" t="s">
         <v>27</v>
       </c>
-      <c r="E28" s="0" t="s">
+      <c r="E28" t="s">
         <v>76</v>
       </c>
-      <c r="F28" s="0" t="s">
+      <c r="F28" t="s">
         <v>131</v>
       </c>
-      <c r="G28" s="0" t="s">
+      <c r="G28" t="s">
         <v>53</v>
       </c>
-      <c r="H28" s="0" t="s">
-        <v>19</v>
-      </c>
-      <c r="I28" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="J28" s="0" t="s">
+      <c r="H28" t="s">
+        <v>19</v>
+      </c>
+      <c r="I28" t="s">
+        <v>20</v>
+      </c>
+      <c r="J28" t="s">
         <v>20</v>
       </c>
       <c r="K28" s="2">
@@ -2861,73 +3280,73 @@
         <v>2711.16</v>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="0" t="s">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
         <v>132</v>
       </c>
-      <c r="B29" s="0" t="s">
+      <c r="B29" t="s">
         <v>133</v>
       </c>
-      <c r="C29" s="0" t="s">
+      <c r="C29" t="s">
         <v>133</v>
       </c>
-      <c r="D29" s="0" t="s">
+      <c r="D29" t="s">
         <v>27</v>
       </c>
-      <c r="E29" s="0" t="s">
+      <c r="E29" t="s">
         <v>28</v>
       </c>
-      <c r="F29" s="0" t="s">
+      <c r="F29" t="s">
         <v>134</v>
       </c>
-      <c r="G29" s="0" t="s">
+      <c r="G29" t="s">
         <v>135</v>
       </c>
-      <c r="H29" s="0" t="s">
-        <v>19</v>
-      </c>
-      <c r="I29" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="J29" s="0" t="s">
+      <c r="H29" t="s">
+        <v>19</v>
+      </c>
+      <c r="I29" t="s">
+        <v>20</v>
+      </c>
+      <c r="J29" t="s">
         <v>20</v>
       </c>
       <c r="K29" s="2">
         <v>1</v>
       </c>
       <c r="L29" s="2">
-        <v>4497.69</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="0" t="s">
+        <v>4497.6899999999996</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
         <v>136</v>
       </c>
-      <c r="B30" s="0" t="s">
+      <c r="B30" t="s">
         <v>137</v>
       </c>
-      <c r="C30" s="0" t="s">
+      <c r="C30" t="s">
         <v>138</v>
       </c>
-      <c r="D30" s="0" t="s">
+      <c r="D30" t="s">
         <v>27</v>
       </c>
-      <c r="E30" s="0" t="s">
+      <c r="E30" t="s">
         <v>28</v>
       </c>
-      <c r="F30" s="0" t="s">
+      <c r="F30" t="s">
         <v>139</v>
       </c>
-      <c r="G30" s="0" t="s">
+      <c r="G30" t="s">
         <v>140</v>
       </c>
-      <c r="H30" s="0" t="s">
-        <v>19</v>
-      </c>
-      <c r="I30" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="J30" s="0" t="s">
+      <c r="H30" t="s">
+        <v>19</v>
+      </c>
+      <c r="I30" t="s">
+        <v>20</v>
+      </c>
+      <c r="J30" t="s">
         <v>20</v>
       </c>
       <c r="K30" s="2">
@@ -2937,35 +3356,35 @@
         <v>1945.61</v>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="0" t="s">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
         <v>141</v>
       </c>
-      <c r="B31" s="0" t="s">
+      <c r="B31" t="s">
         <v>142</v>
       </c>
-      <c r="C31" s="0" t="s">
+      <c r="C31" t="s">
         <v>143</v>
       </c>
-      <c r="D31" s="0" t="s">
+      <c r="D31" t="s">
         <v>27</v>
       </c>
-      <c r="E31" s="0" t="s">
+      <c r="E31" t="s">
         <v>76</v>
       </c>
-      <c r="F31" s="0" t="s">
+      <c r="F31" t="s">
         <v>144</v>
       </c>
-      <c r="G31" s="0" t="s">
+      <c r="G31" t="s">
         <v>30</v>
       </c>
-      <c r="H31" s="0" t="s">
-        <v>19</v>
-      </c>
-      <c r="I31" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="J31" s="0" t="s">
+      <c r="H31" t="s">
+        <v>19</v>
+      </c>
+      <c r="I31" t="s">
+        <v>20</v>
+      </c>
+      <c r="J31" t="s">
         <v>20</v>
       </c>
       <c r="K31" s="2">
@@ -2975,35 +3394,35 @@
         <v>1637.43</v>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="0" t="s">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
         <v>145</v>
       </c>
-      <c r="B32" s="0" t="s">
+      <c r="B32" t="s">
         <v>146</v>
       </c>
-      <c r="C32" s="0" t="s">
+      <c r="C32" t="s">
         <v>147</v>
       </c>
-      <c r="D32" s="0" t="s">
+      <c r="D32" t="s">
         <v>27</v>
       </c>
-      <c r="E32" s="0" t="s">
+      <c r="E32" t="s">
         <v>28</v>
       </c>
-      <c r="F32" s="0" t="s">
+      <c r="F32" t="s">
         <v>148</v>
       </c>
-      <c r="G32" s="0" t="s">
+      <c r="G32" t="s">
         <v>101</v>
       </c>
-      <c r="H32" s="0" t="s">
-        <v>19</v>
-      </c>
-      <c r="I32" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="J32" s="0" t="s">
+      <c r="H32" t="s">
+        <v>19</v>
+      </c>
+      <c r="I32" t="s">
+        <v>20</v>
+      </c>
+      <c r="J32" t="s">
         <v>20</v>
       </c>
       <c r="K32" s="2">
@@ -3013,35 +3432,35 @@
         <v>2851.7</v>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="0" t="s">
+    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
         <v>149</v>
       </c>
-      <c r="B33" s="0" t="s">
+      <c r="B33" t="s">
         <v>150</v>
       </c>
-      <c r="C33" s="0" t="s">
+      <c r="C33" t="s">
         <v>151</v>
       </c>
-      <c r="D33" s="0" t="s">
+      <c r="D33" t="s">
         <v>27</v>
       </c>
-      <c r="E33" s="0" t="s">
+      <c r="E33" t="s">
         <v>28</v>
       </c>
-      <c r="F33" s="0" t="s">
+      <c r="F33" t="s">
         <v>152</v>
       </c>
-      <c r="G33" s="0" t="s">
+      <c r="G33" t="s">
         <v>101</v>
       </c>
-      <c r="H33" s="0" t="s">
-        <v>19</v>
-      </c>
-      <c r="I33" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="J33" s="0" t="s">
+      <c r="H33" t="s">
+        <v>19</v>
+      </c>
+      <c r="I33" t="s">
+        <v>20</v>
+      </c>
+      <c r="J33" t="s">
         <v>20</v>
       </c>
       <c r="K33" s="2">
@@ -3051,73 +3470,73 @@
         <v>2483.85</v>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="0" t="s">
+    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
         <v>153</v>
       </c>
-      <c r="B34" s="0" t="s">
+      <c r="B34" t="s">
         <v>154</v>
       </c>
-      <c r="C34" s="0" t="s">
+      <c r="C34" t="s">
         <v>154</v>
       </c>
-      <c r="D34" s="0" t="s">
+      <c r="D34" t="s">
         <v>27</v>
       </c>
-      <c r="E34" s="0" t="s">
+      <c r="E34" t="s">
         <v>28</v>
       </c>
-      <c r="F34" s="0" t="s">
+      <c r="F34" t="s">
         <v>155</v>
       </c>
-      <c r="G34" s="0" t="s">
+      <c r="G34" t="s">
         <v>53</v>
       </c>
-      <c r="H34" s="0" t="s">
-        <v>19</v>
-      </c>
-      <c r="I34" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="J34" s="0" t="s">
+      <c r="H34" t="s">
+        <v>19</v>
+      </c>
+      <c r="I34" t="s">
+        <v>20</v>
+      </c>
+      <c r="J34" t="s">
         <v>20</v>
       </c>
       <c r="K34" s="2">
         <v>1</v>
       </c>
       <c r="L34" s="2">
-        <v>4373.27</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="0" t="s">
+        <v>4373.2700000000004</v>
+      </c>
+    </row>
+    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
         <v>156</v>
       </c>
-      <c r="B35" s="0" t="s">
+      <c r="B35" t="s">
         <v>157</v>
       </c>
-      <c r="C35" s="0" t="s">
+      <c r="C35" t="s">
         <v>157</v>
       </c>
-      <c r="D35" s="0" t="s">
+      <c r="D35" t="s">
         <v>40</v>
       </c>
-      <c r="E35" s="0" t="s">
+      <c r="E35" t="s">
         <v>28</v>
       </c>
-      <c r="F35" s="0" t="s">
+      <c r="F35" t="s">
         <v>158</v>
       </c>
-      <c r="G35" s="0" t="s">
+      <c r="G35" t="s">
         <v>159</v>
       </c>
-      <c r="H35" s="0" t="s">
-        <v>19</v>
-      </c>
-      <c r="I35" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="J35" s="0" t="s">
+      <c r="H35" t="s">
+        <v>19</v>
+      </c>
+      <c r="I35" t="s">
+        <v>20</v>
+      </c>
+      <c r="J35" t="s">
         <v>20</v>
       </c>
       <c r="K35" s="2">
@@ -3127,35 +3546,35 @@
         <v>127302.3</v>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="0" t="s">
+    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
         <v>160</v>
       </c>
-      <c r="B36" s="0" t="s">
+      <c r="B36" t="s">
         <v>161</v>
       </c>
-      <c r="C36" s="0" t="s">
+      <c r="C36" t="s">
         <v>162</v>
       </c>
-      <c r="D36" s="0" t="s">
+      <c r="D36" t="s">
         <v>27</v>
       </c>
-      <c r="E36" s="0" t="s">
+      <c r="E36" t="s">
         <v>163</v>
       </c>
-      <c r="F36" s="0" t="s">
+      <c r="F36" t="s">
         <v>164</v>
       </c>
-      <c r="G36" s="0" t="s">
+      <c r="G36" t="s">
         <v>165</v>
       </c>
-      <c r="H36" s="0" t="s">
-        <v>19</v>
-      </c>
-      <c r="I36" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="J36" s="0" t="s">
+      <c r="H36" t="s">
+        <v>19</v>
+      </c>
+      <c r="I36" t="s">
+        <v>20</v>
+      </c>
+      <c r="J36" t="s">
         <v>20</v>
       </c>
       <c r="K36" s="2">
@@ -3165,35 +3584,35 @@
         <v>2421.87</v>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="0" t="s">
+    <row r="37" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
         <v>166</v>
       </c>
-      <c r="B37" s="0" t="s">
+      <c r="B37" t="s">
         <v>167</v>
       </c>
-      <c r="C37" s="0" t="s">
+      <c r="C37" t="s">
         <v>168</v>
       </c>
-      <c r="D37" s="0" t="s">
+      <c r="D37" t="s">
         <v>27</v>
       </c>
-      <c r="E37" s="0" t="s">
+      <c r="E37" t="s">
         <v>28</v>
       </c>
-      <c r="F37" s="0" t="s">
+      <c r="F37" t="s">
         <v>169</v>
       </c>
-      <c r="G37" s="0" t="s">
+      <c r="G37" t="s">
         <v>101</v>
       </c>
-      <c r="H37" s="0" t="s">
-        <v>19</v>
-      </c>
-      <c r="I37" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="J37" s="0" t="s">
+      <c r="H37" t="s">
+        <v>19</v>
+      </c>
+      <c r="I37" t="s">
+        <v>20</v>
+      </c>
+      <c r="J37" t="s">
         <v>20</v>
       </c>
       <c r="K37" s="2">
@@ -3203,35 +3622,35 @@
         <v>8457.33</v>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="0" t="s">
+    <row r="38" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
         <v>170</v>
       </c>
-      <c r="B38" s="0" t="s">
+      <c r="B38" t="s">
         <v>171</v>
       </c>
-      <c r="C38" s="0" t="s">
+      <c r="C38" t="s">
         <v>172</v>
       </c>
-      <c r="D38" s="0" t="s">
+      <c r="D38" t="s">
         <v>27</v>
       </c>
-      <c r="E38" s="0" t="s">
+      <c r="E38" t="s">
         <v>28</v>
       </c>
-      <c r="F38" s="0" t="s">
+      <c r="F38" t="s">
         <v>173</v>
       </c>
-      <c r="G38" s="0" t="s">
+      <c r="G38" t="s">
         <v>53</v>
       </c>
-      <c r="H38" s="0" t="s">
-        <v>19</v>
-      </c>
-      <c r="I38" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="J38" s="0" t="s">
+      <c r="H38" t="s">
+        <v>19</v>
+      </c>
+      <c r="I38" t="s">
+        <v>20</v>
+      </c>
+      <c r="J38" t="s">
         <v>20</v>
       </c>
       <c r="K38" s="2">
@@ -3241,35 +3660,35 @@
         <v>3679.5</v>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="0" t="s">
+    <row r="39" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
         <v>174</v>
       </c>
-      <c r="B39" s="0" t="s">
+      <c r="B39" t="s">
         <v>175</v>
       </c>
-      <c r="C39" s="0" t="s">
+      <c r="C39" t="s">
         <v>176</v>
       </c>
-      <c r="D39" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="E39" s="0" t="s">
+      <c r="D39" t="s">
+        <v>15</v>
+      </c>
+      <c r="E39" t="s">
         <v>177</v>
       </c>
-      <c r="F39" s="0" t="s">
+      <c r="F39" t="s">
         <v>178</v>
       </c>
-      <c r="G39" s="0" t="s">
+      <c r="G39" t="s">
         <v>179</v>
       </c>
-      <c r="H39" s="0" t="s">
-        <v>19</v>
-      </c>
-      <c r="I39" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="J39" s="0" t="s">
+      <c r="H39" t="s">
+        <v>19</v>
+      </c>
+      <c r="I39" t="s">
+        <v>20</v>
+      </c>
+      <c r="J39" t="s">
         <v>23</v>
       </c>
       <c r="K39" s="2">
@@ -3279,35 +3698,35 @@
         <v>39.5</v>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="0" t="s">
+    <row r="40" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
         <v>174</v>
       </c>
-      <c r="B40" s="0" t="s">
+      <c r="B40" t="s">
         <v>175</v>
       </c>
-      <c r="C40" s="0" t="s">
+      <c r="C40" t="s">
         <v>176</v>
       </c>
-      <c r="D40" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="E40" s="0" t="s">
+      <c r="D40" t="s">
+        <v>15</v>
+      </c>
+      <c r="E40" t="s">
         <v>177</v>
       </c>
-      <c r="F40" s="0" t="s">
+      <c r="F40" t="s">
         <v>180</v>
       </c>
-      <c r="G40" s="0" t="s">
+      <c r="G40" t="s">
         <v>181</v>
       </c>
-      <c r="H40" s="0" t="s">
-        <v>19</v>
-      </c>
-      <c r="I40" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="J40" s="0" t="s">
+      <c r="H40" t="s">
+        <v>19</v>
+      </c>
+      <c r="I40" t="s">
+        <v>20</v>
+      </c>
+      <c r="J40" t="s">
         <v>23</v>
       </c>
       <c r="K40" s="2">
@@ -3317,35 +3736,35 @@
         <v>39.5</v>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="0" t="s">
+    <row r="41" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
         <v>174</v>
       </c>
-      <c r="B41" s="0" t="s">
+      <c r="B41" t="s">
         <v>175</v>
       </c>
-      <c r="C41" s="0" t="s">
+      <c r="C41" t="s">
         <v>176</v>
       </c>
-      <c r="D41" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="E41" s="0" t="s">
+      <c r="D41" t="s">
+        <v>15</v>
+      </c>
+      <c r="E41" t="s">
         <v>177</v>
       </c>
-      <c r="F41" s="0" t="s">
+      <c r="F41" t="s">
         <v>182</v>
       </c>
-      <c r="G41" s="0" t="s">
+      <c r="G41" t="s">
         <v>183</v>
       </c>
-      <c r="H41" s="0" t="s">
-        <v>19</v>
-      </c>
-      <c r="I41" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="J41" s="0" t="s">
+      <c r="H41" t="s">
+        <v>19</v>
+      </c>
+      <c r="I41" t="s">
+        <v>20</v>
+      </c>
+      <c r="J41" t="s">
         <v>23</v>
       </c>
       <c r="K41" s="2">
@@ -3355,35 +3774,35 @@
         <v>39.5</v>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="0" t="s">
+    <row r="42" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
         <v>174</v>
       </c>
-      <c r="B42" s="0" t="s">
+      <c r="B42" t="s">
         <v>175</v>
       </c>
-      <c r="C42" s="0" t="s">
+      <c r="C42" t="s">
         <v>176</v>
       </c>
-      <c r="D42" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="E42" s="0" t="s">
+      <c r="D42" t="s">
+        <v>15</v>
+      </c>
+      <c r="E42" t="s">
         <v>177</v>
       </c>
-      <c r="F42" s="0" t="s">
+      <c r="F42" t="s">
         <v>184</v>
       </c>
-      <c r="G42" s="0" t="s">
+      <c r="G42" t="s">
         <v>185</v>
       </c>
-      <c r="H42" s="0" t="s">
-        <v>19</v>
-      </c>
-      <c r="I42" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="J42" s="0" t="s">
+      <c r="H42" t="s">
+        <v>19</v>
+      </c>
+      <c r="I42" t="s">
+        <v>20</v>
+      </c>
+      <c r="J42" t="s">
         <v>23</v>
       </c>
       <c r="K42" s="2">
@@ -3393,35 +3812,35 @@
         <v>39.5</v>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="0" t="s">
+    <row r="43" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
         <v>174</v>
       </c>
-      <c r="B43" s="0" t="s">
+      <c r="B43" t="s">
         <v>175</v>
       </c>
-      <c r="C43" s="0" t="s">
+      <c r="C43" t="s">
         <v>176</v>
       </c>
-      <c r="D43" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="E43" s="0" t="s">
+      <c r="D43" t="s">
+        <v>15</v>
+      </c>
+      <c r="E43" t="s">
         <v>177</v>
       </c>
-      <c r="F43" s="0" t="s">
+      <c r="F43" t="s">
         <v>186</v>
       </c>
-      <c r="G43" s="0" t="s">
+      <c r="G43" t="s">
         <v>185</v>
       </c>
-      <c r="H43" s="0" t="s">
-        <v>19</v>
-      </c>
-      <c r="I43" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="J43" s="0" t="s">
+      <c r="H43" t="s">
+        <v>19</v>
+      </c>
+      <c r="I43" t="s">
+        <v>20</v>
+      </c>
+      <c r="J43" t="s">
         <v>23</v>
       </c>
       <c r="K43" s="2">
@@ -3431,35 +3850,35 @@
         <v>109623</v>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="0" t="s">
+    <row r="44" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
         <v>174</v>
       </c>
-      <c r="B44" s="0" t="s">
+      <c r="B44" t="s">
         <v>175</v>
       </c>
-      <c r="C44" s="0" t="s">
+      <c r="C44" t="s">
         <v>176</v>
       </c>
-      <c r="D44" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="E44" s="0" t="s">
+      <c r="D44" t="s">
+        <v>15</v>
+      </c>
+      <c r="E44" t="s">
         <v>177</v>
       </c>
-      <c r="F44" s="0" t="s">
+      <c r="F44" t="s">
         <v>187</v>
       </c>
-      <c r="G44" s="0" t="s">
+      <c r="G44" t="s">
         <v>185</v>
       </c>
-      <c r="H44" s="0" t="s">
-        <v>19</v>
-      </c>
-      <c r="I44" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="J44" s="0" t="s">
+      <c r="H44" t="s">
+        <v>19</v>
+      </c>
+      <c r="I44" t="s">
+        <v>20</v>
+      </c>
+      <c r="J44" t="s">
         <v>23</v>
       </c>
       <c r="K44" s="2">
@@ -3469,35 +3888,35 @@
         <v>39.5</v>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="0" t="s">
+    <row r="45" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
         <v>174</v>
       </c>
-      <c r="B45" s="0" t="s">
+      <c r="B45" t="s">
         <v>175</v>
       </c>
-      <c r="C45" s="0" t="s">
+      <c r="C45" t="s">
         <v>176</v>
       </c>
-      <c r="D45" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="E45" s="0" t="s">
+      <c r="D45" t="s">
+        <v>15</v>
+      </c>
+      <c r="E45" t="s">
         <v>177</v>
       </c>
-      <c r="F45" s="0" t="s">
+      <c r="F45" t="s">
         <v>188</v>
       </c>
-      <c r="G45" s="0" t="s">
+      <c r="G45" t="s">
         <v>181</v>
       </c>
-      <c r="H45" s="0" t="s">
-        <v>19</v>
-      </c>
-      <c r="I45" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="J45" s="0" t="s">
+      <c r="H45" t="s">
+        <v>19</v>
+      </c>
+      <c r="I45" t="s">
+        <v>20</v>
+      </c>
+      <c r="J45" t="s">
         <v>23</v>
       </c>
       <c r="K45" s="2">
@@ -3507,35 +3926,35 @@
         <v>39.5</v>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="0" t="s">
+    <row r="46" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
         <v>174</v>
       </c>
-      <c r="B46" s="0" t="s">
+      <c r="B46" t="s">
         <v>175</v>
       </c>
-      <c r="C46" s="0" t="s">
+      <c r="C46" t="s">
         <v>176</v>
       </c>
-      <c r="D46" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="E46" s="0" t="s">
+      <c r="D46" t="s">
+        <v>15</v>
+      </c>
+      <c r="E46" t="s">
         <v>177</v>
       </c>
-      <c r="F46" s="0" t="s">
+      <c r="F46" t="s">
         <v>189</v>
       </c>
-      <c r="G46" s="0" t="s">
+      <c r="G46" t="s">
         <v>179</v>
       </c>
-      <c r="H46" s="0" t="s">
-        <v>19</v>
-      </c>
-      <c r="I46" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="J46" s="0" t="s">
+      <c r="H46" t="s">
+        <v>19</v>
+      </c>
+      <c r="I46" t="s">
+        <v>20</v>
+      </c>
+      <c r="J46" t="s">
         <v>23</v>
       </c>
       <c r="K46" s="2">
@@ -3545,35 +3964,35 @@
         <v>39.5</v>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="0" t="s">
+    <row r="47" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
         <v>174</v>
       </c>
-      <c r="B47" s="0" t="s">
+      <c r="B47" t="s">
         <v>175</v>
       </c>
-      <c r="C47" s="0" t="s">
+      <c r="C47" t="s">
         <v>176</v>
       </c>
-      <c r="D47" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="E47" s="0" t="s">
+      <c r="D47" t="s">
+        <v>15</v>
+      </c>
+      <c r="E47" t="s">
         <v>177</v>
       </c>
-      <c r="F47" s="0" t="s">
+      <c r="F47" t="s">
         <v>190</v>
       </c>
-      <c r="G47" s="0" t="s">
+      <c r="G47" t="s">
         <v>179</v>
       </c>
-      <c r="H47" s="0" t="s">
-        <v>19</v>
-      </c>
-      <c r="I47" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="J47" s="0" t="s">
+      <c r="H47" t="s">
+        <v>19</v>
+      </c>
+      <c r="I47" t="s">
+        <v>20</v>
+      </c>
+      <c r="J47" t="s">
         <v>23</v>
       </c>
       <c r="K47" s="2">
@@ -3583,35 +4002,35 @@
         <v>39.5</v>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="0" t="s">
+    <row r="48" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
         <v>174</v>
       </c>
-      <c r="B48" s="0" t="s">
+      <c r="B48" t="s">
         <v>175</v>
       </c>
-      <c r="C48" s="0" t="s">
+      <c r="C48" t="s">
         <v>176</v>
       </c>
-      <c r="D48" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="E48" s="0" t="s">
+      <c r="D48" t="s">
+        <v>15</v>
+      </c>
+      <c r="E48" t="s">
         <v>177</v>
       </c>
-      <c r="F48" s="0" t="s">
+      <c r="F48" t="s">
         <v>191</v>
       </c>
-      <c r="G48" s="0" t="s">
+      <c r="G48" t="s">
         <v>192</v>
       </c>
-      <c r="H48" s="0" t="s">
-        <v>19</v>
-      </c>
-      <c r="I48" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="J48" s="0" t="s">
+      <c r="H48" t="s">
+        <v>19</v>
+      </c>
+      <c r="I48" t="s">
+        <v>20</v>
+      </c>
+      <c r="J48" t="s">
         <v>23</v>
       </c>
       <c r="K48" s="2">
@@ -3621,35 +4040,35 @@
         <v>90</v>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="0" t="s">
+    <row r="49" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
         <v>193</v>
       </c>
-      <c r="B49" s="0" t="s">
+      <c r="B49" t="s">
         <v>194</v>
       </c>
-      <c r="C49" s="0" t="s">
+      <c r="C49" t="s">
         <v>195</v>
       </c>
-      <c r="D49" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="E49" s="0" t="s">
+      <c r="D49" t="s">
+        <v>15</v>
+      </c>
+      <c r="E49" t="s">
         <v>177</v>
       </c>
-      <c r="F49" s="0" t="s">
+      <c r="F49" t="s">
         <v>196</v>
       </c>
-      <c r="G49" s="0" t="s">
+      <c r="G49" t="s">
         <v>181</v>
       </c>
-      <c r="H49" s="0" t="s">
-        <v>19</v>
-      </c>
-      <c r="I49" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="J49" s="0" t="s">
+      <c r="H49" t="s">
+        <v>19</v>
+      </c>
+      <c r="I49" t="s">
+        <v>20</v>
+      </c>
+      <c r="J49" t="s">
         <v>20</v>
       </c>
       <c r="K49" s="2">
@@ -3659,35 +4078,35 @@
         <v>5649.05</v>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="0" t="s">
+    <row r="50" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
         <v>197</v>
       </c>
-      <c r="B50" s="0" t="s">
+      <c r="B50" t="s">
         <v>198</v>
       </c>
-      <c r="C50" s="0" t="s">
+      <c r="C50" t="s">
         <v>176</v>
       </c>
-      <c r="D50" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="E50" s="0" t="s">
+      <c r="D50" t="s">
+        <v>15</v>
+      </c>
+      <c r="E50" t="s">
         <v>177</v>
       </c>
-      <c r="F50" s="0" t="s">
+      <c r="F50" t="s">
         <v>199</v>
       </c>
-      <c r="G50" s="0" t="s">
+      <c r="G50" t="s">
         <v>200</v>
       </c>
-      <c r="H50" s="0" t="s">
-        <v>19</v>
-      </c>
-      <c r="I50" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="J50" s="0" t="s">
+      <c r="H50" t="s">
+        <v>19</v>
+      </c>
+      <c r="I50" t="s">
+        <v>20</v>
+      </c>
+      <c r="J50" t="s">
         <v>20</v>
       </c>
       <c r="K50" s="2">
@@ -3697,35 +4116,35 @@
         <v>90</v>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="0" t="s">
+    <row r="51" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
         <v>197</v>
       </c>
-      <c r="B51" s="0" t="s">
+      <c r="B51" t="s">
         <v>198</v>
       </c>
-      <c r="C51" s="0" t="s">
+      <c r="C51" t="s">
         <v>176</v>
       </c>
-      <c r="D51" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="E51" s="0" t="s">
+      <c r="D51" t="s">
+        <v>15</v>
+      </c>
+      <c r="E51" t="s">
         <v>177</v>
       </c>
-      <c r="F51" s="0" t="s">
+      <c r="F51" t="s">
         <v>201</v>
       </c>
-      <c r="G51" s="0" t="s">
+      <c r="G51" t="s">
         <v>181</v>
       </c>
-      <c r="H51" s="0" t="s">
-        <v>19</v>
-      </c>
-      <c r="I51" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="J51" s="0" t="s">
+      <c r="H51" t="s">
+        <v>19</v>
+      </c>
+      <c r="I51" t="s">
+        <v>20</v>
+      </c>
+      <c r="J51" t="s">
         <v>20</v>
       </c>
       <c r="K51" s="2">
@@ -3735,35 +4154,35 @@
         <v>151.29</v>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="0" t="s">
+    <row r="52" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
         <v>202</v>
       </c>
-      <c r="B52" s="0" t="s">
+      <c r="B52" t="s">
         <v>203</v>
       </c>
-      <c r="C52" s="0" t="s">
+      <c r="C52" t="s">
         <v>204</v>
       </c>
-      <c r="D52" s="0" t="s">
+      <c r="D52" t="s">
         <v>27</v>
       </c>
-      <c r="E52" s="0" t="s">
+      <c r="E52" t="s">
         <v>28</v>
       </c>
-      <c r="F52" s="0" t="s">
+      <c r="F52" t="s">
         <v>205</v>
       </c>
-      <c r="G52" s="0" t="s">
+      <c r="G52" t="s">
         <v>87</v>
       </c>
-      <c r="H52" s="0" t="s">
-        <v>19</v>
-      </c>
-      <c r="I52" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="J52" s="0" t="s">
+      <c r="H52" t="s">
+        <v>19</v>
+      </c>
+      <c r="I52" t="s">
+        <v>20</v>
+      </c>
+      <c r="J52" t="s">
         <v>20</v>
       </c>
       <c r="K52" s="2">
@@ -3773,35 +4192,35 @@
         <v>4914.96</v>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="0" t="s">
+    <row r="53" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
         <v>206</v>
       </c>
-      <c r="B53" s="0" t="s">
+      <c r="B53" t="s">
         <v>207</v>
       </c>
-      <c r="C53" s="0" t="s">
+      <c r="C53" t="s">
         <v>208</v>
       </c>
-      <c r="D53" s="0" t="s">
+      <c r="D53" t="s">
         <v>27</v>
       </c>
-      <c r="E53" s="0" t="s">
+      <c r="E53" t="s">
         <v>28</v>
       </c>
-      <c r="F53" s="0" t="s">
+      <c r="F53" t="s">
         <v>209</v>
       </c>
-      <c r="G53" s="0" t="s">
+      <c r="G53" t="s">
         <v>210</v>
       </c>
-      <c r="H53" s="0" t="s">
+      <c r="H53" t="s">
         <v>23</v>
       </c>
-      <c r="I53" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="J53" s="0" t="s">
+      <c r="I53" t="s">
+        <v>20</v>
+      </c>
+      <c r="J53" t="s">
         <v>20</v>
       </c>
       <c r="K53" s="2">
@@ -3811,35 +4230,35 @@
         <v>770.9</v>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="0" t="s">
+    <row r="54" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
         <v>211</v>
       </c>
-      <c r="B54" s="0" t="s">
+      <c r="B54" t="s">
         <v>212</v>
       </c>
-      <c r="C54" s="0" t="s">
+      <c r="C54" t="s">
         <v>213</v>
       </c>
-      <c r="D54" s="0" t="s">
+      <c r="D54" t="s">
         <v>27</v>
       </c>
-      <c r="E54" s="0" t="s">
+      <c r="E54" t="s">
         <v>214</v>
       </c>
-      <c r="F54" s="0" t="s">
+      <c r="F54" t="s">
         <v>215</v>
       </c>
-      <c r="G54" s="0" t="s">
+      <c r="G54" t="s">
         <v>36</v>
       </c>
-      <c r="H54" s="0" t="s">
-        <v>19</v>
-      </c>
-      <c r="I54" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="J54" s="0" t="s">
+      <c r="H54" t="s">
+        <v>19</v>
+      </c>
+      <c r="I54" t="s">
+        <v>20</v>
+      </c>
+      <c r="J54" t="s">
         <v>20</v>
       </c>
       <c r="K54" s="2">
@@ -3849,35 +4268,35 @@
         <v>969638.48</v>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" s="0" t="s">
+    <row r="55" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
         <v>216</v>
       </c>
-      <c r="B55" s="0" t="s">
+      <c r="B55" t="s">
         <v>217</v>
       </c>
-      <c r="C55" s="0" t="s">
+      <c r="C55" t="s">
         <v>218</v>
       </c>
-      <c r="D55" s="0" t="s">
+      <c r="D55" t="s">
         <v>27</v>
       </c>
-      <c r="E55" s="0" t="s">
+      <c r="E55" t="s">
         <v>214</v>
       </c>
-      <c r="F55" s="0" t="s">
+      <c r="F55" t="s">
         <v>219</v>
       </c>
-      <c r="G55" s="0" t="s">
+      <c r="G55" t="s">
         <v>67</v>
       </c>
-      <c r="H55" s="0" t="s">
-        <v>19</v>
-      </c>
-      <c r="I55" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="J55" s="0" t="s">
+      <c r="H55" t="s">
+        <v>19</v>
+      </c>
+      <c r="I55" t="s">
+        <v>20</v>
+      </c>
+      <c r="J55" t="s">
         <v>20</v>
       </c>
       <c r="K55" s="2">
@@ -3887,73 +4306,73 @@
         <v>36377.64</v>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="0" t="s">
+    <row r="56" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
         <v>220</v>
       </c>
-      <c r="B56" s="0" t="s">
+      <c r="B56" t="s">
         <v>221</v>
       </c>
-      <c r="C56" s="0" t="s">
+      <c r="C56" t="s">
         <v>222</v>
       </c>
-      <c r="D56" s="0" t="s">
+      <c r="D56" t="s">
         <v>27</v>
       </c>
-      <c r="E56" s="0" t="s">
+      <c r="E56" t="s">
         <v>214</v>
       </c>
-      <c r="F56" s="0" t="s">
+      <c r="F56" t="s">
         <v>223</v>
       </c>
-      <c r="G56" s="0" t="s">
+      <c r="G56" t="s">
         <v>135</v>
       </c>
-      <c r="H56" s="0" t="s">
-        <v>19</v>
-      </c>
-      <c r="I56" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="J56" s="0" t="s">
+      <c r="H56" t="s">
+        <v>19</v>
+      </c>
+      <c r="I56" t="s">
+        <v>20</v>
+      </c>
+      <c r="J56" t="s">
         <v>20</v>
       </c>
       <c r="K56" s="2">
         <v>8</v>
       </c>
       <c r="L56" s="2">
-        <v>73107.01</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="0" t="s">
+        <v>73107.009999999995</v>
+      </c>
+    </row>
+    <row r="57" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
         <v>224</v>
       </c>
-      <c r="B57" s="0" t="s">
+      <c r="B57" t="s">
         <v>225</v>
       </c>
-      <c r="C57" s="0" t="s">
+      <c r="C57" t="s">
         <v>226</v>
       </c>
-      <c r="D57" s="0" t="s">
+      <c r="D57" t="s">
         <v>27</v>
       </c>
-      <c r="E57" s="0" t="s">
+      <c r="E57" t="s">
         <v>214</v>
       </c>
-      <c r="F57" s="0" t="s">
+      <c r="F57" t="s">
         <v>227</v>
       </c>
-      <c r="G57" s="0" t="s">
+      <c r="G57" t="s">
         <v>159</v>
       </c>
-      <c r="H57" s="0" t="s">
-        <v>19</v>
-      </c>
-      <c r="I57" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="J57" s="0" t="s">
+      <c r="H57" t="s">
+        <v>19</v>
+      </c>
+      <c r="I57" t="s">
+        <v>20</v>
+      </c>
+      <c r="J57" t="s">
         <v>20</v>
       </c>
       <c r="K57" s="2">
@@ -3963,35 +4382,35 @@
         <v>10944.2</v>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" s="0" t="s">
+    <row r="58" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
         <v>228</v>
       </c>
-      <c r="B58" s="0" t="s">
+      <c r="B58" t="s">
         <v>229</v>
       </c>
-      <c r="C58" s="0" t="s">
+      <c r="C58" t="s">
         <v>230</v>
       </c>
-      <c r="D58" s="0" t="s">
+      <c r="D58" t="s">
         <v>27</v>
       </c>
-      <c r="E58" s="0" t="s">
+      <c r="E58" t="s">
         <v>214</v>
       </c>
-      <c r="F58" s="0" t="s">
+      <c r="F58" t="s">
         <v>231</v>
       </c>
-      <c r="G58" s="0" t="s">
+      <c r="G58" t="s">
         <v>53</v>
       </c>
-      <c r="H58" s="0" t="s">
-        <v>19</v>
-      </c>
-      <c r="I58" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="J58" s="0" t="s">
+      <c r="H58" t="s">
+        <v>19</v>
+      </c>
+      <c r="I58" t="s">
+        <v>20</v>
+      </c>
+      <c r="J58" t="s">
         <v>20</v>
       </c>
       <c r="K58" s="2">
@@ -4001,35 +4420,35 @@
         <v>49066.37</v>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="0" t="s">
+    <row r="59" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
         <v>232</v>
       </c>
-      <c r="B59" s="0" t="s">
+      <c r="B59" t="s">
         <v>233</v>
       </c>
-      <c r="C59" s="0" t="s">
+      <c r="C59" t="s">
         <v>234</v>
       </c>
-      <c r="D59" s="0" t="s">
+      <c r="D59" t="s">
         <v>27</v>
       </c>
-      <c r="E59" s="0" t="s">
+      <c r="E59" t="s">
         <v>214</v>
       </c>
-      <c r="F59" s="0" t="s">
+      <c r="F59" t="s">
         <v>235</v>
       </c>
-      <c r="G59" s="0" t="s">
+      <c r="G59" t="s">
         <v>101</v>
       </c>
-      <c r="H59" s="0" t="s">
-        <v>19</v>
-      </c>
-      <c r="I59" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="J59" s="0" t="s">
+      <c r="H59" t="s">
+        <v>19</v>
+      </c>
+      <c r="I59" t="s">
+        <v>20</v>
+      </c>
+      <c r="J59" t="s">
         <v>20</v>
       </c>
       <c r="K59" s="2">
@@ -4039,35 +4458,35 @@
         <v>26219.78</v>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" s="0" t="s">
+    <row r="60" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
         <v>236</v>
       </c>
-      <c r="B60" s="0" t="s">
+      <c r="B60" t="s">
         <v>237</v>
       </c>
-      <c r="C60" s="0" t="s">
+      <c r="C60" t="s">
         <v>238</v>
       </c>
-      <c r="D60" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="E60" s="0" t="s">
+      <c r="D60" t="s">
+        <v>15</v>
+      </c>
+      <c r="E60" t="s">
         <v>16</v>
       </c>
-      <c r="F60" s="0" t="s">
+      <c r="F60" t="s">
         <v>239</v>
       </c>
-      <c r="G60" s="0" t="s">
+      <c r="G60" t="s">
         <v>240</v>
       </c>
-      <c r="H60" s="0" t="s">
+      <c r="H60" t="s">
         <v>23</v>
       </c>
-      <c r="I60" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="J60" s="0" t="s">
+      <c r="I60" t="s">
+        <v>20</v>
+      </c>
+      <c r="J60" t="s">
         <v>20</v>
       </c>
       <c r="K60" s="2">
@@ -4077,35 +4496,35 @@
         <v>1636.49</v>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" s="0" t="s">
+    <row r="61" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
         <v>236</v>
       </c>
-      <c r="B61" s="0" t="s">
+      <c r="B61" t="s">
         <v>237</v>
       </c>
-      <c r="C61" s="0" t="s">
+      <c r="C61" t="s">
         <v>238</v>
       </c>
-      <c r="D61" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="E61" s="0" t="s">
+      <c r="D61" t="s">
+        <v>15</v>
+      </c>
+      <c r="E61" t="s">
         <v>16</v>
       </c>
-      <c r="F61" s="0" t="s">
+      <c r="F61" t="s">
         <v>241</v>
       </c>
-      <c r="G61" s="0" t="s">
+      <c r="G61" t="s">
         <v>42</v>
       </c>
-      <c r="H61" s="0" t="s">
-        <v>19</v>
-      </c>
-      <c r="I61" s="0" t="s">
+      <c r="H61" t="s">
+        <v>19</v>
+      </c>
+      <c r="I61" t="s">
         <v>23</v>
       </c>
-      <c r="J61" s="0" t="s">
+      <c r="J61" t="s">
         <v>23</v>
       </c>
       <c r="K61" s="2">
@@ -4115,35 +4534,35 @@
         <v>1636.49</v>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" s="0" t="s">
+    <row r="62" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
         <v>242</v>
       </c>
-      <c r="B62" s="0" t="s">
+      <c r="B62" t="s">
         <v>243</v>
       </c>
-      <c r="C62" s="0" t="s">
+      <c r="C62" t="s">
         <v>244</v>
       </c>
-      <c r="D62" s="0" t="s">
+      <c r="D62" t="s">
         <v>27</v>
       </c>
-      <c r="E62" s="0" t="s">
+      <c r="E62" t="s">
         <v>28</v>
       </c>
-      <c r="F62" s="0" t="s">
+      <c r="F62" t="s">
         <v>245</v>
       </c>
-      <c r="G62" s="0" t="s">
+      <c r="G62" t="s">
         <v>101</v>
       </c>
-      <c r="H62" s="0" t="s">
-        <v>19</v>
-      </c>
-      <c r="I62" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="J62" s="0" t="s">
+      <c r="H62" t="s">
+        <v>19</v>
+      </c>
+      <c r="I62" t="s">
+        <v>20</v>
+      </c>
+      <c r="J62" t="s">
         <v>20</v>
       </c>
       <c r="K62" s="2">
@@ -4153,35 +4572,35 @@
         <v>264.17</v>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" s="0" t="s">
+    <row r="63" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
         <v>246</v>
       </c>
-      <c r="B63" s="0" t="s">
+      <c r="B63" t="s">
         <v>247</v>
       </c>
-      <c r="C63" s="0" t="s">
+      <c r="C63" t="s">
         <v>248</v>
       </c>
-      <c r="D63" s="0" t="s">
+      <c r="D63" t="s">
         <v>27</v>
       </c>
-      <c r="E63" s="0" t="s">
+      <c r="E63" t="s">
         <v>28</v>
       </c>
-      <c r="F63" s="0" t="s">
+      <c r="F63" t="s">
         <v>249</v>
       </c>
-      <c r="G63" s="0" t="s">
+      <c r="G63" t="s">
         <v>250</v>
       </c>
-      <c r="H63" s="0" t="s">
-        <v>19</v>
-      </c>
-      <c r="I63" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="J63" s="0" t="s">
+      <c r="H63" t="s">
+        <v>19</v>
+      </c>
+      <c r="I63" t="s">
+        <v>20</v>
+      </c>
+      <c r="J63" t="s">
         <v>20</v>
       </c>
       <c r="K63" s="2">
@@ -4191,35 +4610,35 @@
         <v>12939.76</v>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" s="0" t="s">
+    <row r="64" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
         <v>251</v>
       </c>
-      <c r="B64" s="0" t="s">
+      <c r="B64" t="s">
         <v>252</v>
       </c>
-      <c r="C64" s="0" t="s">
+      <c r="C64" t="s">
         <v>252</v>
       </c>
-      <c r="D64" s="0" t="s">
+      <c r="D64" t="s">
         <v>27</v>
       </c>
-      <c r="E64" s="0" t="s">
+      <c r="E64" t="s">
         <v>253</v>
       </c>
-      <c r="F64" s="0" t="s">
+      <c r="F64" t="s">
         <v>254</v>
       </c>
-      <c r="G64" s="0" t="s">
+      <c r="G64" t="s">
         <v>101</v>
       </c>
-      <c r="H64" s="0" t="s">
-        <v>19</v>
-      </c>
-      <c r="I64" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="J64" s="0" t="s">
+      <c r="H64" t="s">
+        <v>19</v>
+      </c>
+      <c r="I64" t="s">
+        <v>20</v>
+      </c>
+      <c r="J64" t="s">
         <v>20</v>
       </c>
       <c r="K64" s="2">
@@ -4229,35 +4648,35 @@
         <v>110826.5</v>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" s="0" t="s">
+    <row r="65" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
         <v>255</v>
       </c>
-      <c r="B65" s="0" t="s">
+      <c r="B65" t="s">
         <v>256</v>
       </c>
-      <c r="C65" s="0" t="s">
+      <c r="C65" t="s">
         <v>257</v>
       </c>
-      <c r="D65" s="0" t="s">
+      <c r="D65" t="s">
         <v>27</v>
       </c>
-      <c r="E65" s="0" t="s">
+      <c r="E65" t="s">
         <v>28</v>
       </c>
-      <c r="F65" s="0" t="s">
+      <c r="F65" t="s">
         <v>258</v>
       </c>
-      <c r="G65" s="0" t="s">
+      <c r="G65" t="s">
         <v>72</v>
       </c>
-      <c r="H65" s="0" t="s">
-        <v>19</v>
-      </c>
-      <c r="I65" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="J65" s="0" t="s">
+      <c r="H65" t="s">
+        <v>19</v>
+      </c>
+      <c r="I65" t="s">
+        <v>20</v>
+      </c>
+      <c r="J65" t="s">
         <v>20</v>
       </c>
       <c r="K65" s="2">
@@ -4267,35 +4686,35 @@
         <v>2825.75</v>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" s="0" t="s">
+    <row r="66" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
         <v>259</v>
       </c>
-      <c r="B66" s="0" t="s">
+      <c r="B66" t="s">
         <v>260</v>
       </c>
-      <c r="C66" s="0" t="s">
+      <c r="C66" t="s">
         <v>261</v>
       </c>
-      <c r="D66" s="0" t="s">
+      <c r="D66" t="s">
         <v>27</v>
       </c>
-      <c r="E66" s="0" t="s">
+      <c r="E66" t="s">
         <v>163</v>
       </c>
-      <c r="F66" s="0" t="s">
+      <c r="F66" t="s">
         <v>262</v>
       </c>
-      <c r="G66" s="0" t="s">
+      <c r="G66" t="s">
         <v>67</v>
       </c>
-      <c r="H66" s="0" t="s">
-        <v>19</v>
-      </c>
-      <c r="I66" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="J66" s="0" t="s">
+      <c r="H66" t="s">
+        <v>19</v>
+      </c>
+      <c r="I66" t="s">
+        <v>20</v>
+      </c>
+      <c r="J66" t="s">
         <v>20</v>
       </c>
       <c r="K66" s="2">
@@ -4305,35 +4724,35 @@
         <v>5348.01</v>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" s="0" t="s">
+    <row r="67" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
         <v>263</v>
       </c>
-      <c r="B67" s="0" t="s">
+      <c r="B67" t="s">
         <v>264</v>
       </c>
-      <c r="C67" s="0" t="s">
+      <c r="C67" t="s">
         <v>265</v>
       </c>
-      <c r="D67" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="E67" s="0" t="s">
+      <c r="D67" t="s">
+        <v>15</v>
+      </c>
+      <c r="E67" t="s">
         <v>16</v>
       </c>
-      <c r="F67" s="0" t="s">
+      <c r="F67" t="s">
         <v>266</v>
       </c>
-      <c r="G67" s="0" t="s">
+      <c r="G67" t="s">
         <v>267</v>
       </c>
-      <c r="H67" s="0" t="s">
-        <v>19</v>
-      </c>
-      <c r="I67" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="J67" s="0" t="s">
+      <c r="H67" t="s">
+        <v>19</v>
+      </c>
+      <c r="I67" t="s">
+        <v>20</v>
+      </c>
+      <c r="J67" t="s">
         <v>20</v>
       </c>
       <c r="K67" s="2">
@@ -4343,35 +4762,35 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" s="0" t="s">
+    <row r="68" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
         <v>263</v>
       </c>
-      <c r="B68" s="0" t="s">
+      <c r="B68" t="s">
         <v>264</v>
       </c>
-      <c r="C68" s="0" t="s">
+      <c r="C68" t="s">
         <v>265</v>
       </c>
-      <c r="D68" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="E68" s="0" t="s">
+      <c r="D68" t="s">
+        <v>15</v>
+      </c>
+      <c r="E68" t="s">
         <v>16</v>
       </c>
-      <c r="F68" s="0" t="s">
+      <c r="F68" t="s">
         <v>268</v>
       </c>
-      <c r="G68" s="0" t="s">
+      <c r="G68" t="s">
         <v>269</v>
       </c>
-      <c r="H68" s="0" t="s">
-        <v>19</v>
-      </c>
-      <c r="I68" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="J68" s="0" t="s">
+      <c r="H68" t="s">
+        <v>19</v>
+      </c>
+      <c r="I68" t="s">
+        <v>20</v>
+      </c>
+      <c r="J68" t="s">
         <v>20</v>
       </c>
       <c r="K68" s="2">
@@ -4381,35 +4800,35 @@
         <v>2500</v>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" s="0" t="s">
+    <row r="69" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
         <v>263</v>
       </c>
-      <c r="B69" s="0" t="s">
+      <c r="B69" t="s">
         <v>264</v>
       </c>
-      <c r="C69" s="0" t="s">
+      <c r="C69" t="s">
         <v>265</v>
       </c>
-      <c r="D69" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="E69" s="0" t="s">
+      <c r="D69" t="s">
+        <v>15</v>
+      </c>
+      <c r="E69" t="s">
         <v>16</v>
       </c>
-      <c r="F69" s="0" t="s">
+      <c r="F69" t="s">
         <v>270</v>
       </c>
-      <c r="G69" s="0" t="s">
+      <c r="G69" t="s">
         <v>271</v>
       </c>
-      <c r="H69" s="0" t="s">
-        <v>19</v>
-      </c>
-      <c r="I69" s="0" t="s">
+      <c r="H69" t="s">
+        <v>19</v>
+      </c>
+      <c r="I69" t="s">
         <v>23</v>
       </c>
-      <c r="J69" s="0" t="s">
+      <c r="J69" t="s">
         <v>23</v>
       </c>
       <c r="K69" s="2">
@@ -4419,35 +4838,35 @@
         <v>7000</v>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" s="0" t="s">
+    <row r="70" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
         <v>272</v>
       </c>
-      <c r="B70" s="0" t="s">
+      <c r="B70" t="s">
         <v>273</v>
       </c>
-      <c r="C70" s="0" t="s">
+      <c r="C70" t="s">
         <v>274</v>
       </c>
-      <c r="D70" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="E70" s="0" t="s">
+      <c r="D70" t="s">
+        <v>15</v>
+      </c>
+      <c r="E70" t="s">
         <v>16</v>
       </c>
-      <c r="F70" s="0" t="s">
+      <c r="F70" t="s">
         <v>275</v>
       </c>
-      <c r="G70" s="0" t="s">
+      <c r="G70" t="s">
         <v>276</v>
       </c>
-      <c r="H70" s="0" t="s">
+      <c r="H70" t="s">
         <v>23</v>
       </c>
-      <c r="I70" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="J70" s="0" t="s">
+      <c r="I70" t="s">
+        <v>20</v>
+      </c>
+      <c r="J70" t="s">
         <v>20</v>
       </c>
       <c r="K70" s="2">
@@ -4457,35 +4876,35 @@
         <v>165</v>
       </c>
     </row>
-    <row r="71">
-      <c r="A71" s="0" t="s">
+    <row r="71" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
         <v>277</v>
       </c>
-      <c r="B71" s="0" t="s">
+      <c r="B71" t="s">
         <v>278</v>
       </c>
-      <c r="C71" s="0" t="s">
+      <c r="C71" t="s">
         <v>279</v>
       </c>
-      <c r="D71" s="0" t="s">
+      <c r="D71" t="s">
         <v>27</v>
       </c>
-      <c r="E71" s="0" t="s">
+      <c r="E71" t="s">
         <v>28</v>
       </c>
-      <c r="F71" s="0" t="s">
+      <c r="F71" t="s">
         <v>280</v>
       </c>
-      <c r="G71" s="0" t="s">
+      <c r="G71" t="s">
         <v>72</v>
       </c>
-      <c r="H71" s="0" t="s">
-        <v>19</v>
-      </c>
-      <c r="I71" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="J71" s="0" t="s">
+      <c r="H71" t="s">
+        <v>19</v>
+      </c>
+      <c r="I71" t="s">
+        <v>20</v>
+      </c>
+      <c r="J71" t="s">
         <v>20</v>
       </c>
       <c r="K71" s="2">
@@ -4495,35 +4914,35 @@
         <v>8400</v>
       </c>
     </row>
-    <row r="72">
-      <c r="A72" s="0" t="s">
+    <row r="72" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
         <v>281</v>
       </c>
-      <c r="B72" s="0" t="s">
+      <c r="B72" t="s">
         <v>282</v>
       </c>
-      <c r="C72" s="0" t="s">
+      <c r="C72" t="s">
         <v>283</v>
       </c>
-      <c r="D72" s="0" t="s">
+      <c r="D72" t="s">
         <v>27</v>
       </c>
-      <c r="E72" s="0" t="s">
+      <c r="E72" t="s">
         <v>28</v>
       </c>
-      <c r="F72" s="0" t="s">
+      <c r="F72" t="s">
         <v>284</v>
       </c>
-      <c r="G72" s="0" t="s">
+      <c r="G72" t="s">
         <v>210</v>
       </c>
-      <c r="H72" s="0" t="s">
-        <v>19</v>
-      </c>
-      <c r="I72" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="J72" s="0" t="s">
+      <c r="H72" t="s">
+        <v>19</v>
+      </c>
+      <c r="I72" t="s">
+        <v>20</v>
+      </c>
+      <c r="J72" t="s">
         <v>20</v>
       </c>
       <c r="K72" s="2">
@@ -4533,35 +4952,35 @@
         <v>3742</v>
       </c>
     </row>
-    <row r="73">
-      <c r="A73" s="0" t="s">
+    <row r="73" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
         <v>285</v>
       </c>
-      <c r="B73" s="0" t="s">
+      <c r="B73" t="s">
         <v>286</v>
       </c>
-      <c r="C73" s="0" t="s">
+      <c r="C73" t="s">
         <v>287</v>
       </c>
-      <c r="D73" s="0" t="s">
+      <c r="D73" t="s">
         <v>27</v>
       </c>
-      <c r="E73" s="0" t="s">
+      <c r="E73" t="s">
         <v>28</v>
       </c>
-      <c r="F73" s="0" t="s">
+      <c r="F73" t="s">
         <v>288</v>
       </c>
-      <c r="G73" s="0" t="s">
+      <c r="G73" t="s">
         <v>30</v>
       </c>
-      <c r="H73" s="0" t="s">
-        <v>19</v>
-      </c>
-      <c r="I73" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="J73" s="0" t="s">
+      <c r="H73" t="s">
+        <v>19</v>
+      </c>
+      <c r="I73" t="s">
+        <v>20</v>
+      </c>
+      <c r="J73" t="s">
         <v>20</v>
       </c>
       <c r="K73" s="2">
@@ -4571,35 +4990,35 @@
         <v>41313.75</v>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" s="0" t="s">
+    <row r="74" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
         <v>289</v>
       </c>
-      <c r="B74" s="0" t="s">
+      <c r="B74" t="s">
         <v>290</v>
       </c>
-      <c r="C74" s="0" t="s">
+      <c r="C74" t="s">
         <v>291</v>
       </c>
-      <c r="D74" s="0" t="s">
+      <c r="D74" t="s">
         <v>27</v>
       </c>
-      <c r="E74" s="0" t="s">
+      <c r="E74" t="s">
         <v>253</v>
       </c>
-      <c r="F74" s="0" t="s">
+      <c r="F74" t="s">
         <v>292</v>
       </c>
-      <c r="G74" s="0" t="s">
+      <c r="G74" t="s">
         <v>30</v>
       </c>
-      <c r="H74" s="0" t="s">
-        <v>19</v>
-      </c>
-      <c r="I74" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="J74" s="0" t="s">
+      <c r="H74" t="s">
+        <v>19</v>
+      </c>
+      <c r="I74" t="s">
+        <v>20</v>
+      </c>
+      <c r="J74" t="s">
         <v>20</v>
       </c>
       <c r="K74" s="2">
@@ -4609,35 +5028,35 @@
         <v>47399.85</v>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" s="0" t="s">
+    <row r="75" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
         <v>293</v>
       </c>
-      <c r="B75" s="0" t="s">
+      <c r="B75" t="s">
         <v>294</v>
       </c>
-      <c r="C75" s="0" t="s">
+      <c r="C75" t="s">
         <v>295</v>
       </c>
-      <c r="D75" s="0" t="s">
+      <c r="D75" t="s">
         <v>27</v>
       </c>
-      <c r="E75" s="0" t="s">
+      <c r="E75" t="s">
         <v>253</v>
       </c>
-      <c r="F75" s="0" t="s">
+      <c r="F75" t="s">
         <v>296</v>
       </c>
-      <c r="G75" s="0" t="s">
+      <c r="G75" t="s">
         <v>30</v>
       </c>
-      <c r="H75" s="0" t="s">
-        <v>19</v>
-      </c>
-      <c r="I75" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="J75" s="0" t="s">
+      <c r="H75" t="s">
+        <v>19</v>
+      </c>
+      <c r="I75" t="s">
+        <v>20</v>
+      </c>
+      <c r="J75" t="s">
         <v>20</v>
       </c>
       <c r="K75" s="2">
@@ -4647,35 +5066,35 @@
         <v>46348.03</v>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" s="0" t="s">
+    <row r="76" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
         <v>297</v>
       </c>
-      <c r="B76" s="0" t="s">
+      <c r="B76" t="s">
         <v>298</v>
       </c>
-      <c r="C76" s="0" t="s">
+      <c r="C76" t="s">
         <v>299</v>
       </c>
-      <c r="D76" s="0" t="s">
+      <c r="D76" t="s">
         <v>27</v>
       </c>
-      <c r="E76" s="0" t="s">
+      <c r="E76" t="s">
         <v>28</v>
       </c>
-      <c r="F76" s="0" t="s">
+      <c r="F76" t="s">
         <v>300</v>
       </c>
-      <c r="G76" s="0" t="s">
+      <c r="G76" t="s">
         <v>101</v>
       </c>
-      <c r="H76" s="0" t="s">
-        <v>19</v>
-      </c>
-      <c r="I76" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="J76" s="0" t="s">
+      <c r="H76" t="s">
+        <v>19</v>
+      </c>
+      <c r="I76" t="s">
+        <v>20</v>
+      </c>
+      <c r="J76" t="s">
         <v>20</v>
       </c>
       <c r="K76" s="2">
@@ -4685,35 +5104,35 @@
         <v>4064.95</v>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" s="0" t="s">
+    <row r="77" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
         <v>301</v>
       </c>
-      <c r="B77" s="0" t="s">
+      <c r="B77" t="s">
         <v>302</v>
       </c>
-      <c r="C77" s="0" t="s">
+      <c r="C77" t="s">
         <v>303</v>
       </c>
-      <c r="D77" s="0" t="s">
+      <c r="D77" t="s">
         <v>27</v>
       </c>
-      <c r="E77" s="0" t="s">
+      <c r="E77" t="s">
         <v>28</v>
       </c>
-      <c r="F77" s="0" t="s">
+      <c r="F77" t="s">
         <v>304</v>
       </c>
-      <c r="G77" s="0" t="s">
+      <c r="G77" t="s">
         <v>101</v>
       </c>
-      <c r="H77" s="0" t="s">
-        <v>19</v>
-      </c>
-      <c r="I77" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="J77" s="0" t="s">
+      <c r="H77" t="s">
+        <v>19</v>
+      </c>
+      <c r="I77" t="s">
+        <v>20</v>
+      </c>
+      <c r="J77" t="s">
         <v>20</v>
       </c>
       <c r="K77" s="2">
@@ -4723,35 +5142,35 @@
         <v>35520</v>
       </c>
     </row>
-    <row r="78">
-      <c r="A78" s="0" t="s">
+    <row r="78" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
         <v>305</v>
       </c>
-      <c r="B78" s="0" t="s">
+      <c r="B78" t="s">
         <v>306</v>
       </c>
-      <c r="C78" s="0" t="s">
+      <c r="C78" t="s">
         <v>307</v>
       </c>
-      <c r="D78" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="E78" s="0" t="s">
+      <c r="D78" t="s">
+        <v>15</v>
+      </c>
+      <c r="E78" t="s">
         <v>16</v>
       </c>
-      <c r="F78" s="0" t="s">
+      <c r="F78" t="s">
         <v>308</v>
       </c>
-      <c r="G78" s="0" t="s">
+      <c r="G78" t="s">
         <v>309</v>
       </c>
-      <c r="H78" s="0" t="s">
+      <c r="H78" t="s">
         <v>23</v>
       </c>
-      <c r="I78" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="J78" s="0" t="s">
+      <c r="I78" t="s">
+        <v>20</v>
+      </c>
+      <c r="J78" t="s">
         <v>20</v>
       </c>
       <c r="K78" s="2">
@@ -4761,35 +5180,35 @@
         <v>3350</v>
       </c>
     </row>
-    <row r="79">
-      <c r="A79" s="0" t="s">
+    <row r="79" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
         <v>305</v>
       </c>
-      <c r="B79" s="0" t="s">
+      <c r="B79" t="s">
         <v>306</v>
       </c>
-      <c r="C79" s="0" t="s">
+      <c r="C79" t="s">
         <v>307</v>
       </c>
-      <c r="D79" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="E79" s="0" t="s">
+      <c r="D79" t="s">
+        <v>15</v>
+      </c>
+      <c r="E79" t="s">
         <v>16</v>
       </c>
-      <c r="F79" s="0" t="s">
+      <c r="F79" t="s">
         <v>310</v>
       </c>
-      <c r="G79" s="0" t="s">
+      <c r="G79" t="s">
         <v>311</v>
       </c>
-      <c r="H79" s="0" t="s">
-        <v>19</v>
-      </c>
-      <c r="I79" s="0" t="s">
+      <c r="H79" t="s">
+        <v>19</v>
+      </c>
+      <c r="I79" t="s">
         <v>23</v>
       </c>
-      <c r="J79" s="0" t="s">
+      <c r="J79" t="s">
         <v>23</v>
       </c>
       <c r="K79" s="2">
@@ -4799,35 +5218,35 @@
         <v>1150</v>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" s="0" t="s">
+    <row r="80" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
         <v>305</v>
       </c>
-      <c r="B80" s="0" t="s">
+      <c r="B80" t="s">
         <v>306</v>
       </c>
-      <c r="C80" s="0" t="s">
+      <c r="C80" t="s">
         <v>307</v>
       </c>
-      <c r="D80" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="E80" s="0" t="s">
+      <c r="D80" t="s">
+        <v>15</v>
+      </c>
+      <c r="E80" t="s">
         <v>16</v>
       </c>
-      <c r="F80" s="0" t="s">
+      <c r="F80" t="s">
         <v>312</v>
       </c>
-      <c r="G80" s="0" t="s">
+      <c r="G80" t="s">
         <v>311</v>
       </c>
-      <c r="H80" s="0" t="s">
-        <v>19</v>
-      </c>
-      <c r="I80" s="0" t="s">
+      <c r="H80" t="s">
+        <v>19</v>
+      </c>
+      <c r="I80" t="s">
         <v>23</v>
       </c>
-      <c r="J80" s="0" t="s">
+      <c r="J80" t="s">
         <v>23</v>
       </c>
       <c r="K80" s="2">
@@ -4837,35 +5256,35 @@
         <v>2800</v>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" s="0" t="s">
+    <row r="81" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
         <v>313</v>
       </c>
-      <c r="B81" s="0" t="s">
+      <c r="B81" t="s">
         <v>314</v>
       </c>
-      <c r="C81" s="0" t="s">
+      <c r="C81" t="s">
         <v>315</v>
       </c>
-      <c r="D81" s="0" t="s">
+      <c r="D81" t="s">
         <v>27</v>
       </c>
-      <c r="E81" s="0" t="s">
+      <c r="E81" t="s">
         <v>163</v>
       </c>
-      <c r="F81" s="0" t="s">
+      <c r="F81" t="s">
         <v>316</v>
       </c>
-      <c r="G81" s="0" t="s">
+      <c r="G81" t="s">
         <v>44</v>
       </c>
-      <c r="H81" s="0" t="s">
-        <v>19</v>
-      </c>
-      <c r="I81" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="J81" s="0" t="s">
+      <c r="H81" t="s">
+        <v>19</v>
+      </c>
+      <c r="I81" t="s">
+        <v>20</v>
+      </c>
+      <c r="J81" t="s">
         <v>20</v>
       </c>
       <c r="K81" s="2">
@@ -4875,35 +5294,35 @@
         <v>12920.5</v>
       </c>
     </row>
-    <row r="82">
-      <c r="A82" s="0" t="s">
+    <row r="82" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
         <v>317</v>
       </c>
-      <c r="B82" s="0" t="s">
+      <c r="B82" t="s">
         <v>318</v>
       </c>
-      <c r="C82" s="0" t="s">
+      <c r="C82" t="s">
         <v>319</v>
       </c>
-      <c r="D82" s="0" t="s">
+      <c r="D82" t="s">
         <v>27</v>
       </c>
-      <c r="E82" s="0" t="s">
+      <c r="E82" t="s">
         <v>65</v>
       </c>
-      <c r="F82" s="0" t="s">
+      <c r="F82" t="s">
         <v>320</v>
       </c>
-      <c r="G82" s="0" t="s">
+      <c r="G82" t="s">
         <v>30</v>
       </c>
-      <c r="H82" s="0" t="s">
-        <v>19</v>
-      </c>
-      <c r="I82" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="J82" s="0" t="s">
+      <c r="H82" t="s">
+        <v>19</v>
+      </c>
+      <c r="I82" t="s">
+        <v>20</v>
+      </c>
+      <c r="J82" t="s">
         <v>20</v>
       </c>
       <c r="K82" s="2">
@@ -4913,35 +5332,35 @@
         <v>147135.71</v>
       </c>
     </row>
-    <row r="83">
-      <c r="A83" s="0" t="s">
+    <row r="83" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
         <v>321</v>
       </c>
-      <c r="B83" s="0" t="s">
+      <c r="B83" t="s">
         <v>322</v>
       </c>
-      <c r="C83" s="0" t="s">
+      <c r="C83" t="s">
         <v>323</v>
       </c>
-      <c r="D83" s="0" t="s">
+      <c r="D83" t="s">
         <v>27</v>
       </c>
-      <c r="E83" s="0" t="s">
+      <c r="E83" t="s">
         <v>65</v>
       </c>
-      <c r="F83" s="0" t="s">
+      <c r="F83" t="s">
         <v>324</v>
       </c>
-      <c r="G83" s="0" t="s">
+      <c r="G83" t="s">
         <v>92</v>
       </c>
-      <c r="H83" s="0" t="s">
-        <v>19</v>
-      </c>
-      <c r="I83" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="J83" s="0" t="s">
+      <c r="H83" t="s">
+        <v>19</v>
+      </c>
+      <c r="I83" t="s">
+        <v>20</v>
+      </c>
+      <c r="J83" t="s">
         <v>20</v>
       </c>
       <c r="K83" s="2">
@@ -4951,35 +5370,35 @@
         <v>18202.13</v>
       </c>
     </row>
-    <row r="84">
-      <c r="A84" s="0" t="s">
+    <row r="84" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
         <v>325</v>
       </c>
-      <c r="B84" s="0" t="s">
+      <c r="B84" t="s">
         <v>326</v>
       </c>
-      <c r="C84" s="0" t="s">
+      <c r="C84" t="s">
         <v>327</v>
       </c>
-      <c r="D84" s="0" t="s">
+      <c r="D84" t="s">
         <v>27</v>
       </c>
-      <c r="E84" s="0" t="s">
+      <c r="E84" t="s">
         <v>65</v>
       </c>
-      <c r="F84" s="0" t="s">
+      <c r="F84" t="s">
         <v>328</v>
       </c>
-      <c r="G84" s="0" t="s">
+      <c r="G84" t="s">
         <v>101</v>
       </c>
-      <c r="H84" s="0" t="s">
-        <v>19</v>
-      </c>
-      <c r="I84" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="J84" s="0" t="s">
+      <c r="H84" t="s">
+        <v>19</v>
+      </c>
+      <c r="I84" t="s">
+        <v>20</v>
+      </c>
+      <c r="J84" t="s">
         <v>20</v>
       </c>
       <c r="K84" s="2">
@@ -4989,35 +5408,35 @@
         <v>218993.56</v>
       </c>
     </row>
-    <row r="85">
-      <c r="A85" s="0" t="s">
+    <row r="85" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
         <v>329</v>
       </c>
-      <c r="B85" s="0" t="s">
+      <c r="B85" t="s">
         <v>330</v>
       </c>
-      <c r="C85" s="0" t="s">
+      <c r="C85" t="s">
         <v>331</v>
       </c>
-      <c r="D85" s="0" t="s">
+      <c r="D85" t="s">
         <v>27</v>
       </c>
-      <c r="E85" s="0" t="s">
+      <c r="E85" t="s">
         <v>65</v>
       </c>
-      <c r="F85" s="0" t="s">
+      <c r="F85" t="s">
         <v>332</v>
       </c>
-      <c r="G85" s="0" t="s">
+      <c r="G85" t="s">
         <v>101</v>
       </c>
-      <c r="H85" s="0" t="s">
-        <v>19</v>
-      </c>
-      <c r="I85" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="J85" s="0" t="s">
+      <c r="H85" t="s">
+        <v>19</v>
+      </c>
+      <c r="I85" t="s">
+        <v>20</v>
+      </c>
+      <c r="J85" t="s">
         <v>20</v>
       </c>
       <c r="K85" s="2">
@@ -5027,35 +5446,35 @@
         <v>582276.34</v>
       </c>
     </row>
-    <row r="86">
-      <c r="A86" s="0" t="s">
+    <row r="86" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
         <v>333</v>
       </c>
-      <c r="B86" s="0" t="s">
+      <c r="B86" t="s">
         <v>334</v>
       </c>
-      <c r="C86" s="0" t="s">
+      <c r="C86" t="s">
         <v>335</v>
       </c>
-      <c r="D86" s="0" t="s">
+      <c r="D86" t="s">
         <v>27</v>
       </c>
-      <c r="E86" s="0" t="s">
+      <c r="E86" t="s">
         <v>28</v>
       </c>
-      <c r="F86" s="0" t="s">
+      <c r="F86" t="s">
         <v>336</v>
       </c>
-      <c r="G86" s="0" t="s">
+      <c r="G86" t="s">
         <v>53</v>
       </c>
-      <c r="H86" s="0" t="s">
-        <v>19</v>
-      </c>
-      <c r="I86" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="J86" s="0" t="s">
+      <c r="H86" t="s">
+        <v>19</v>
+      </c>
+      <c r="I86" t="s">
+        <v>20</v>
+      </c>
+      <c r="J86" t="s">
         <v>20</v>
       </c>
       <c r="K86" s="2">
@@ -5065,35 +5484,35 @@
         <v>7260.77</v>
       </c>
     </row>
-    <row r="87">
-      <c r="A87" s="0" t="s">
+    <row r="87" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
         <v>337</v>
       </c>
-      <c r="B87" s="0" t="s">
+      <c r="B87" t="s">
         <v>338</v>
       </c>
-      <c r="C87" s="0" t="s">
+      <c r="C87" t="s">
         <v>339</v>
       </c>
-      <c r="D87" s="0" t="s">
+      <c r="D87" t="s">
         <v>27</v>
       </c>
-      <c r="E87" s="0" t="s">
+      <c r="E87" t="s">
         <v>28</v>
       </c>
-      <c r="F87" s="0" t="s">
+      <c r="F87" t="s">
         <v>340</v>
       </c>
-      <c r="G87" s="0" t="s">
+      <c r="G87" t="s">
         <v>30</v>
       </c>
-      <c r="H87" s="0" t="s">
-        <v>19</v>
-      </c>
-      <c r="I87" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="J87" s="0" t="s">
+      <c r="H87" t="s">
+        <v>19</v>
+      </c>
+      <c r="I87" t="s">
+        <v>20</v>
+      </c>
+      <c r="J87" t="s">
         <v>20</v>
       </c>
       <c r="K87" s="2">
@@ -5103,35 +5522,35 @@
         <v>5821.71</v>
       </c>
     </row>
-    <row r="88">
-      <c r="A88" s="0" t="s">
+    <row r="88" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
         <v>341</v>
       </c>
-      <c r="B88" s="0" t="s">
+      <c r="B88" t="s">
         <v>342</v>
       </c>
-      <c r="C88" s="0" t="s">
+      <c r="C88" t="s">
         <v>343</v>
       </c>
-      <c r="D88" s="0" t="s">
+      <c r="D88" t="s">
         <v>27</v>
       </c>
-      <c r="E88" s="0" t="s">
+      <c r="E88" t="s">
         <v>76</v>
       </c>
-      <c r="F88" s="0" t="s">
+      <c r="F88" t="s">
         <v>344</v>
       </c>
-      <c r="G88" s="0" t="s">
+      <c r="G88" t="s">
         <v>30</v>
       </c>
-      <c r="H88" s="0" t="s">
-        <v>19</v>
-      </c>
-      <c r="I88" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="J88" s="0" t="s">
+      <c r="H88" t="s">
+        <v>19</v>
+      </c>
+      <c r="I88" t="s">
+        <v>20</v>
+      </c>
+      <c r="J88" t="s">
         <v>20</v>
       </c>
       <c r="K88" s="2">
@@ -5141,35 +5560,35 @@
         <v>74489.72</v>
       </c>
     </row>
-    <row r="89">
-      <c r="A89" s="0" t="s">
+    <row r="89" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
         <v>345</v>
       </c>
-      <c r="B89" s="0" t="s">
+      <c r="B89" t="s">
         <v>346</v>
       </c>
-      <c r="C89" s="0" t="s">
+      <c r="C89" t="s">
         <v>346</v>
       </c>
-      <c r="D89" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="E89" s="0" t="s">
+      <c r="D89" t="s">
+        <v>15</v>
+      </c>
+      <c r="E89" t="s">
         <v>177</v>
       </c>
-      <c r="F89" s="0" t="s">
+      <c r="F89" t="s">
         <v>347</v>
       </c>
-      <c r="G89" s="0" t="s">
+      <c r="G89" t="s">
         <v>22</v>
       </c>
-      <c r="H89" s="0" t="s">
-        <v>19</v>
-      </c>
-      <c r="I89" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="J89" s="0" t="s">
+      <c r="H89" t="s">
+        <v>19</v>
+      </c>
+      <c r="I89" t="s">
+        <v>20</v>
+      </c>
+      <c r="J89" t="s">
         <v>20</v>
       </c>
       <c r="K89" s="2">
@@ -5179,35 +5598,35 @@
         <v>57.5</v>
       </c>
     </row>
-    <row r="90">
-      <c r="A90" s="0" t="s">
+    <row r="90" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
         <v>345</v>
       </c>
-      <c r="B90" s="0" t="s">
+      <c r="B90" t="s">
         <v>346</v>
       </c>
-      <c r="C90" s="0" t="s">
+      <c r="C90" t="s">
         <v>346</v>
       </c>
-      <c r="D90" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="E90" s="0" t="s">
+      <c r="D90" t="s">
+        <v>15</v>
+      </c>
+      <c r="E90" t="s">
         <v>177</v>
       </c>
-      <c r="F90" s="0" t="s">
+      <c r="F90" t="s">
         <v>348</v>
       </c>
-      <c r="G90" s="0" t="s">
+      <c r="G90" t="s">
         <v>22</v>
       </c>
-      <c r="H90" s="0" t="s">
-        <v>19</v>
-      </c>
-      <c r="I90" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="J90" s="0" t="s">
+      <c r="H90" t="s">
+        <v>19</v>
+      </c>
+      <c r="I90" t="s">
+        <v>20</v>
+      </c>
+      <c r="J90" t="s">
         <v>20</v>
       </c>
       <c r="K90" s="2">
@@ -5217,35 +5636,35 @@
         <v>57.5</v>
       </c>
     </row>
-    <row r="91">
-      <c r="A91" s="0" t="s">
+    <row r="91" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
         <v>345</v>
       </c>
-      <c r="B91" s="0" t="s">
+      <c r="B91" t="s">
         <v>346</v>
       </c>
-      <c r="C91" s="0" t="s">
+      <c r="C91" t="s">
         <v>346</v>
       </c>
-      <c r="D91" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="E91" s="0" t="s">
+      <c r="D91" t="s">
+        <v>15</v>
+      </c>
+      <c r="E91" t="s">
         <v>177</v>
       </c>
-      <c r="F91" s="0" t="s">
+      <c r="F91" t="s">
         <v>349</v>
       </c>
-      <c r="G91" s="0" t="s">
+      <c r="G91" t="s">
         <v>22</v>
       </c>
-      <c r="H91" s="0" t="s">
-        <v>19</v>
-      </c>
-      <c r="I91" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="J91" s="0" t="s">
+      <c r="H91" t="s">
+        <v>19</v>
+      </c>
+      <c r="I91" t="s">
+        <v>20</v>
+      </c>
+      <c r="J91" t="s">
         <v>20</v>
       </c>
       <c r="K91" s="2">
@@ -5255,35 +5674,35 @@
         <v>57.5</v>
       </c>
     </row>
-    <row r="92">
-      <c r="A92" s="0" t="s">
+    <row r="92" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
         <v>345</v>
       </c>
-      <c r="B92" s="0" t="s">
+      <c r="B92" t="s">
         <v>346</v>
       </c>
-      <c r="C92" s="0" t="s">
+      <c r="C92" t="s">
         <v>346</v>
       </c>
-      <c r="D92" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="E92" s="0" t="s">
+      <c r="D92" t="s">
+        <v>15</v>
+      </c>
+      <c r="E92" t="s">
         <v>177</v>
       </c>
-      <c r="F92" s="0" t="s">
+      <c r="F92" t="s">
         <v>350</v>
       </c>
-      <c r="G92" s="0" t="s">
+      <c r="G92" t="s">
         <v>22</v>
       </c>
-      <c r="H92" s="0" t="s">
-        <v>19</v>
-      </c>
-      <c r="I92" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="J92" s="0" t="s">
+      <c r="H92" t="s">
+        <v>19</v>
+      </c>
+      <c r="I92" t="s">
+        <v>20</v>
+      </c>
+      <c r="J92" t="s">
         <v>20</v>
       </c>
       <c r="K92" s="2">
@@ -5293,35 +5712,35 @@
         <v>57.5</v>
       </c>
     </row>
-    <row r="93">
-      <c r="A93" s="0" t="s">
+    <row r="93" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
         <v>345</v>
       </c>
-      <c r="B93" s="0" t="s">
+      <c r="B93" t="s">
         <v>346</v>
       </c>
-      <c r="C93" s="0" t="s">
+      <c r="C93" t="s">
         <v>346</v>
       </c>
-      <c r="D93" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="E93" s="0" t="s">
+      <c r="D93" t="s">
+        <v>15</v>
+      </c>
+      <c r="E93" t="s">
         <v>177</v>
       </c>
-      <c r="F93" s="0" t="s">
+      <c r="F93" t="s">
         <v>351</v>
       </c>
-      <c r="G93" s="0" t="s">
+      <c r="G93" t="s">
         <v>22</v>
       </c>
-      <c r="H93" s="0" t="s">
-        <v>19</v>
-      </c>
-      <c r="I93" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="J93" s="0" t="s">
+      <c r="H93" t="s">
+        <v>19</v>
+      </c>
+      <c r="I93" t="s">
+        <v>20</v>
+      </c>
+      <c r="J93" t="s">
         <v>20</v>
       </c>
       <c r="K93" s="2">
@@ -5331,35 +5750,35 @@
         <v>57.5</v>
       </c>
     </row>
-    <row r="94">
-      <c r="A94" s="0" t="s">
+    <row r="94" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
         <v>345</v>
       </c>
-      <c r="B94" s="0" t="s">
+      <c r="B94" t="s">
         <v>346</v>
       </c>
-      <c r="C94" s="0" t="s">
+      <c r="C94" t="s">
         <v>346</v>
       </c>
-      <c r="D94" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="E94" s="0" t="s">
+      <c r="D94" t="s">
+        <v>15</v>
+      </c>
+      <c r="E94" t="s">
         <v>177</v>
       </c>
-      <c r="F94" s="0" t="s">
+      <c r="F94" t="s">
         <v>352</v>
       </c>
-      <c r="G94" s="0" t="s">
+      <c r="G94" t="s">
         <v>22</v>
       </c>
-      <c r="H94" s="0" t="s">
-        <v>19</v>
-      </c>
-      <c r="I94" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="J94" s="0" t="s">
+      <c r="H94" t="s">
+        <v>19</v>
+      </c>
+      <c r="I94" t="s">
+        <v>20</v>
+      </c>
+      <c r="J94" t="s">
         <v>20</v>
       </c>
       <c r="K94" s="2">
@@ -5369,35 +5788,35 @@
         <v>57.5</v>
       </c>
     </row>
-    <row r="95">
-      <c r="A95" s="0" t="s">
+    <row r="95" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
         <v>345</v>
       </c>
-      <c r="B95" s="0" t="s">
+      <c r="B95" t="s">
         <v>346</v>
       </c>
-      <c r="C95" s="0" t="s">
+      <c r="C95" t="s">
         <v>346</v>
       </c>
-      <c r="D95" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="E95" s="0" t="s">
+      <c r="D95" t="s">
+        <v>15</v>
+      </c>
+      <c r="E95" t="s">
         <v>177</v>
       </c>
-      <c r="F95" s="0" t="s">
+      <c r="F95" t="s">
         <v>353</v>
       </c>
-      <c r="G95" s="0" t="s">
+      <c r="G95" t="s">
         <v>22</v>
       </c>
-      <c r="H95" s="0" t="s">
-        <v>19</v>
-      </c>
-      <c r="I95" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="J95" s="0" t="s">
+      <c r="H95" t="s">
+        <v>19</v>
+      </c>
+      <c r="I95" t="s">
+        <v>20</v>
+      </c>
+      <c r="J95" t="s">
         <v>20</v>
       </c>
       <c r="K95" s="2">
@@ -5407,35 +5826,35 @@
         <v>57.5</v>
       </c>
     </row>
-    <row r="96">
-      <c r="A96" s="0" t="s">
+    <row r="96" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
         <v>345</v>
       </c>
-      <c r="B96" s="0" t="s">
+      <c r="B96" t="s">
         <v>346</v>
       </c>
-      <c r="C96" s="0" t="s">
+      <c r="C96" t="s">
         <v>346</v>
       </c>
-      <c r="D96" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="E96" s="0" t="s">
+      <c r="D96" t="s">
+        <v>15</v>
+      </c>
+      <c r="E96" t="s">
         <v>177</v>
       </c>
-      <c r="F96" s="0" t="s">
+      <c r="F96" t="s">
         <v>354</v>
       </c>
-      <c r="G96" s="0" t="s">
+      <c r="G96" t="s">
         <v>22</v>
       </c>
-      <c r="H96" s="0" t="s">
-        <v>19</v>
-      </c>
-      <c r="I96" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="J96" s="0" t="s">
+      <c r="H96" t="s">
+        <v>19</v>
+      </c>
+      <c r="I96" t="s">
+        <v>20</v>
+      </c>
+      <c r="J96" t="s">
         <v>20</v>
       </c>
       <c r="K96" s="2">
@@ -5445,35 +5864,35 @@
         <v>57.5</v>
       </c>
     </row>
-    <row r="97">
-      <c r="A97" s="0" t="s">
+    <row r="97" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
         <v>355</v>
       </c>
-      <c r="B97" s="0" t="s">
+      <c r="B97" t="s">
         <v>356</v>
       </c>
-      <c r="C97" s="0" t="s">
+      <c r="C97" t="s">
         <v>357</v>
       </c>
-      <c r="D97" s="0" t="s">
+      <c r="D97" t="s">
         <v>27</v>
       </c>
-      <c r="E97" s="0" t="s">
+      <c r="E97" t="s">
         <v>163</v>
       </c>
-      <c r="F97" s="0" t="s">
+      <c r="F97" t="s">
         <v>358</v>
       </c>
-      <c r="G97" s="0" t="s">
+      <c r="G97" t="s">
         <v>67</v>
       </c>
-      <c r="H97" s="0" t="s">
-        <v>19</v>
-      </c>
-      <c r="I97" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="J97" s="0" t="s">
+      <c r="H97" t="s">
+        <v>19</v>
+      </c>
+      <c r="I97" t="s">
+        <v>20</v>
+      </c>
+      <c r="J97" t="s">
         <v>20</v>
       </c>
       <c r="K97" s="2">
@@ -5483,35 +5902,35 @@
         <v>1203.54</v>
       </c>
     </row>
-    <row r="98">
-      <c r="A98" s="0" t="s">
+    <row r="98" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
         <v>359</v>
       </c>
-      <c r="B98" s="0" t="s">
+      <c r="B98" t="s">
         <v>360</v>
       </c>
-      <c r="C98" s="0" t="s">
+      <c r="C98" t="s">
         <v>360</v>
       </c>
-      <c r="D98" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="E98" s="0" t="s">
+      <c r="D98" t="s">
+        <v>15</v>
+      </c>
+      <c r="E98" t="s">
         <v>16</v>
       </c>
-      <c r="F98" s="0" t="s">
+      <c r="F98" t="s">
         <v>361</v>
       </c>
-      <c r="G98" s="0" t="s">
+      <c r="G98" t="s">
         <v>362</v>
       </c>
-      <c r="H98" s="0" t="s">
+      <c r="H98" t="s">
         <v>23</v>
       </c>
-      <c r="I98" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="J98" s="0" t="s">
+      <c r="I98" t="s">
+        <v>20</v>
+      </c>
+      <c r="J98" t="s">
         <v>20</v>
       </c>
       <c r="K98" s="2">
@@ -5521,35 +5940,35 @@
         <v>2625</v>
       </c>
     </row>
-    <row r="99">
-      <c r="A99" s="0" t="s">
+    <row r="99" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
         <v>363</v>
       </c>
-      <c r="B99" s="0" t="s">
+      <c r="B99" t="s">
         <v>364</v>
       </c>
-      <c r="C99" s="0" t="s">
+      <c r="C99" t="s">
         <v>365</v>
       </c>
-      <c r="D99" s="0" t="s">
+      <c r="D99" t="s">
         <v>27</v>
       </c>
-      <c r="E99" s="0" t="s">
+      <c r="E99" t="s">
         <v>28</v>
       </c>
-      <c r="F99" s="0" t="s">
+      <c r="F99" t="s">
         <v>366</v>
       </c>
-      <c r="G99" s="0" t="s">
+      <c r="G99" t="s">
         <v>367</v>
       </c>
-      <c r="H99" s="0" t="s">
-        <v>19</v>
-      </c>
-      <c r="I99" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="J99" s="0" t="s">
+      <c r="H99" t="s">
+        <v>19</v>
+      </c>
+      <c r="I99" t="s">
+        <v>20</v>
+      </c>
+      <c r="J99" t="s">
         <v>20</v>
       </c>
       <c r="K99" s="2">
@@ -5559,35 +5978,35 @@
         <v>15000</v>
       </c>
     </row>
-    <row r="100">
-      <c r="A100" s="0" t="s">
+    <row r="100" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
         <v>368</v>
       </c>
-      <c r="B100" s="0" t="s">
+      <c r="B100" t="s">
         <v>369</v>
       </c>
-      <c r="C100" s="0" t="s">
+      <c r="C100" t="s">
         <v>369</v>
       </c>
-      <c r="D100" s="0" t="s">
+      <c r="D100" t="s">
         <v>27</v>
       </c>
-      <c r="E100" s="0" t="s">
+      <c r="E100" t="s">
         <v>28</v>
       </c>
-      <c r="F100" s="0" t="s">
+      <c r="F100" t="s">
         <v>370</v>
       </c>
-      <c r="G100" s="0" t="s">
+      <c r="G100" t="s">
         <v>101</v>
       </c>
-      <c r="H100" s="0" t="s">
-        <v>19</v>
-      </c>
-      <c r="I100" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="J100" s="0" t="s">
+      <c r="H100" t="s">
+        <v>19</v>
+      </c>
+      <c r="I100" t="s">
+        <v>20</v>
+      </c>
+      <c r="J100" t="s">
         <v>20</v>
       </c>
       <c r="K100" s="2">
@@ -5597,35 +6016,35 @@
         <v>438590.79</v>
       </c>
     </row>
-    <row r="101">
-      <c r="A101" s="0" t="s">
+    <row r="101" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
         <v>371</v>
       </c>
-      <c r="B101" s="0" t="s">
+      <c r="B101" t="s">
         <v>372</v>
       </c>
-      <c r="C101" s="0" t="s">
+      <c r="C101" t="s">
         <v>373</v>
       </c>
-      <c r="D101" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="E101" s="0" t="s">
+      <c r="D101" t="s">
+        <v>15</v>
+      </c>
+      <c r="E101" t="s">
         <v>16</v>
       </c>
-      <c r="F101" s="0" t="s">
+      <c r="F101" t="s">
         <v>374</v>
       </c>
-      <c r="G101" s="0" t="s">
+      <c r="G101" t="s">
         <v>375</v>
       </c>
-      <c r="H101" s="0" t="s">
-        <v>19</v>
-      </c>
-      <c r="I101" s="0" t="s">
+      <c r="H101" t="s">
+        <v>19</v>
+      </c>
+      <c r="I101" t="s">
         <v>23</v>
       </c>
-      <c r="J101" s="0" t="s">
+      <c r="J101" t="s">
         <v>23</v>
       </c>
       <c r="K101" s="2">
@@ -5635,35 +6054,35 @@
         <v>10357.77</v>
       </c>
     </row>
-    <row r="102">
-      <c r="A102" s="0" t="s">
+    <row r="102" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
         <v>371</v>
       </c>
-      <c r="B102" s="0" t="s">
+      <c r="B102" t="s">
         <v>372</v>
       </c>
-      <c r="C102" s="0" t="s">
+      <c r="C102" t="s">
         <v>373</v>
       </c>
-      <c r="D102" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="E102" s="0" t="s">
+      <c r="D102" t="s">
+        <v>15</v>
+      </c>
+      <c r="E102" t="s">
         <v>16</v>
       </c>
-      <c r="F102" s="0" t="s">
+      <c r="F102" t="s">
         <v>376</v>
       </c>
-      <c r="G102" s="0" t="s">
+      <c r="G102" t="s">
         <v>375</v>
       </c>
-      <c r="H102" s="0" t="s">
-        <v>19</v>
-      </c>
-      <c r="I102" s="0" t="s">
+      <c r="H102" t="s">
+        <v>19</v>
+      </c>
+      <c r="I102" t="s">
         <v>23</v>
       </c>
-      <c r="J102" s="0" t="s">
+      <c r="J102" t="s">
         <v>23</v>
       </c>
       <c r="K102" s="2">
@@ -5673,35 +6092,35 @@
         <v>9575</v>
       </c>
     </row>
-    <row r="103">
-      <c r="A103" s="0" t="s">
+    <row r="103" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
         <v>377</v>
       </c>
-      <c r="B103" s="0" t="s">
+      <c r="B103" t="s">
         <v>378</v>
       </c>
-      <c r="C103" s="0" t="s">
+      <c r="C103" t="s">
         <v>379</v>
       </c>
-      <c r="D103" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="E103" s="0" t="s">
+      <c r="D103" t="s">
+        <v>15</v>
+      </c>
+      <c r="E103" t="s">
         <v>16</v>
       </c>
-      <c r="F103" s="0" t="s">
+      <c r="F103" t="s">
         <v>380</v>
       </c>
-      <c r="G103" s="0" t="s">
+      <c r="G103" t="s">
         <v>18</v>
       </c>
-      <c r="H103" s="0" t="s">
+      <c r="H103" t="s">
         <v>23</v>
       </c>
-      <c r="I103" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="J103" s="0" t="s">
+      <c r="I103" t="s">
+        <v>20</v>
+      </c>
+      <c r="J103" t="s">
         <v>20</v>
       </c>
       <c r="K103" s="2">
@@ -5711,35 +6130,35 @@
         <v>9000</v>
       </c>
     </row>
-    <row r="104">
-      <c r="A104" s="0" t="s">
+    <row r="104" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
         <v>381</v>
       </c>
-      <c r="B104" s="0" t="s">
+      <c r="B104" t="s">
         <v>382</v>
       </c>
-      <c r="C104" s="0" t="s">
+      <c r="C104" t="s">
         <v>383</v>
       </c>
-      <c r="D104" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="E104" s="0" t="s">
+      <c r="D104" t="s">
+        <v>15</v>
+      </c>
+      <c r="E104" t="s">
         <v>16</v>
       </c>
-      <c r="F104" s="0" t="s">
+      <c r="F104" t="s">
         <v>384</v>
       </c>
-      <c r="G104" s="0" t="s">
+      <c r="G104" t="s">
         <v>385</v>
       </c>
-      <c r="H104" s="0" t="s">
+      <c r="H104" t="s">
         <v>23</v>
       </c>
-      <c r="I104" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="J104" s="0" t="s">
+      <c r="I104" t="s">
+        <v>20</v>
+      </c>
+      <c r="J104" t="s">
         <v>20</v>
       </c>
       <c r="K104" s="2">
@@ -5749,35 +6168,35 @@
         <v>74400</v>
       </c>
     </row>
-    <row r="105">
-      <c r="A105" s="0" t="s">
+    <row r="105" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
         <v>386</v>
       </c>
-      <c r="B105" s="0" t="s">
+      <c r="B105" t="s">
         <v>387</v>
       </c>
-      <c r="C105" s="0" t="s">
+      <c r="C105" t="s">
         <v>388</v>
       </c>
-      <c r="D105" s="0" t="s">
+      <c r="D105" t="s">
         <v>40</v>
       </c>
-      <c r="E105" s="0" t="s">
+      <c r="E105" t="s">
         <v>28</v>
       </c>
-      <c r="F105" s="0" t="s">
+      <c r="F105" t="s">
         <v>389</v>
       </c>
-      <c r="G105" s="0" t="s">
+      <c r="G105" t="s">
         <v>210</v>
       </c>
-      <c r="H105" s="0" t="s">
-        <v>19</v>
-      </c>
-      <c r="I105" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="J105" s="0" t="s">
+      <c r="H105" t="s">
+        <v>19</v>
+      </c>
+      <c r="I105" t="s">
+        <v>20</v>
+      </c>
+      <c r="J105" t="s">
         <v>20</v>
       </c>
       <c r="K105" s="2">
@@ -5787,35 +6206,35 @@
         <v>53310</v>
       </c>
     </row>
-    <row r="106">
-      <c r="A106" s="0" t="s">
+    <row r="106" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
         <v>390</v>
       </c>
-      <c r="B106" s="0" t="s">
+      <c r="B106" t="s">
         <v>391</v>
       </c>
-      <c r="C106" s="0" t="s">
+      <c r="C106" t="s">
         <v>392</v>
       </c>
-      <c r="D106" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="E106" s="0" t="s">
+      <c r="D106" t="s">
+        <v>15</v>
+      </c>
+      <c r="E106" t="s">
         <v>177</v>
       </c>
-      <c r="F106" s="0" t="s">
+      <c r="F106" t="s">
         <v>393</v>
       </c>
-      <c r="G106" s="0" t="s">
+      <c r="G106" t="s">
         <v>394</v>
       </c>
-      <c r="H106" s="0" t="s">
-        <v>19</v>
-      </c>
-      <c r="I106" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="J106" s="0" t="s">
+      <c r="H106" t="s">
+        <v>19</v>
+      </c>
+      <c r="I106" t="s">
+        <v>20</v>
+      </c>
+      <c r="J106" t="s">
         <v>23</v>
       </c>
       <c r="K106" s="2">
@@ -5825,35 +6244,35 @@
         <v>11600</v>
       </c>
     </row>
-    <row r="107">
-      <c r="A107" s="0" t="s">
+    <row r="107" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
         <v>390</v>
       </c>
-      <c r="B107" s="0" t="s">
+      <c r="B107" t="s">
         <v>391</v>
       </c>
-      <c r="C107" s="0" t="s">
+      <c r="C107" t="s">
         <v>392</v>
       </c>
-      <c r="D107" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="E107" s="0" t="s">
+      <c r="D107" t="s">
+        <v>15</v>
+      </c>
+      <c r="E107" t="s">
         <v>177</v>
       </c>
-      <c r="F107" s="0" t="s">
+      <c r="F107" t="s">
         <v>395</v>
       </c>
-      <c r="G107" s="0" t="s">
+      <c r="G107" t="s">
         <v>185</v>
       </c>
-      <c r="H107" s="0" t="s">
-        <v>19</v>
-      </c>
-      <c r="I107" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="J107" s="0" t="s">
+      <c r="H107" t="s">
+        <v>19</v>
+      </c>
+      <c r="I107" t="s">
+        <v>20</v>
+      </c>
+      <c r="J107" t="s">
         <v>23</v>
       </c>
       <c r="K107" s="2">
@@ -5863,35 +6282,35 @@
         <v>17400</v>
       </c>
     </row>
-    <row r="108">
-      <c r="A108" s="0" t="s">
+    <row r="108" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
         <v>390</v>
       </c>
-      <c r="B108" s="0" t="s">
+      <c r="B108" t="s">
         <v>391</v>
       </c>
-      <c r="C108" s="0" t="s">
+      <c r="C108" t="s">
         <v>392</v>
       </c>
-      <c r="D108" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="E108" s="0" t="s">
+      <c r="D108" t="s">
+        <v>15</v>
+      </c>
+      <c r="E108" t="s">
         <v>177</v>
       </c>
-      <c r="F108" s="0" t="s">
+      <c r="F108" t="s">
         <v>396</v>
       </c>
-      <c r="G108" s="0" t="s">
+      <c r="G108" t="s">
         <v>185</v>
       </c>
-      <c r="H108" s="0" t="s">
-        <v>19</v>
-      </c>
-      <c r="I108" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="J108" s="0" t="s">
+      <c r="H108" t="s">
+        <v>19</v>
+      </c>
+      <c r="I108" t="s">
+        <v>20</v>
+      </c>
+      <c r="J108" t="s">
         <v>23</v>
       </c>
       <c r="K108" s="2">
@@ -5901,35 +6320,35 @@
         <v>9970.83</v>
       </c>
     </row>
-    <row r="109">
-      <c r="A109" s="0" t="s">
+    <row r="109" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
         <v>390</v>
       </c>
-      <c r="B109" s="0" t="s">
+      <c r="B109" t="s">
         <v>391</v>
       </c>
-      <c r="C109" s="0" t="s">
+      <c r="C109" t="s">
         <v>392</v>
       </c>
-      <c r="D109" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="E109" s="0" t="s">
+      <c r="D109" t="s">
+        <v>15</v>
+      </c>
+      <c r="E109" t="s">
         <v>177</v>
       </c>
-      <c r="F109" s="0" t="s">
+      <c r="F109" t="s">
         <v>397</v>
       </c>
-      <c r="G109" s="0" t="s">
+      <c r="G109" t="s">
         <v>185</v>
       </c>
-      <c r="H109" s="0" t="s">
-        <v>19</v>
-      </c>
-      <c r="I109" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="J109" s="0" t="s">
+      <c r="H109" t="s">
+        <v>19</v>
+      </c>
+      <c r="I109" t="s">
+        <v>20</v>
+      </c>
+      <c r="J109" t="s">
         <v>23</v>
       </c>
       <c r="K109" s="2">
@@ -5939,35 +6358,35 @@
         <v>11556</v>
       </c>
     </row>
-    <row r="110">
-      <c r="A110" s="0" t="s">
+    <row r="110" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
         <v>390</v>
       </c>
-      <c r="B110" s="0" t="s">
+      <c r="B110" t="s">
         <v>391</v>
       </c>
-      <c r="C110" s="0" t="s">
+      <c r="C110" t="s">
         <v>392</v>
       </c>
-      <c r="D110" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="E110" s="0" t="s">
+      <c r="D110" t="s">
+        <v>15</v>
+      </c>
+      <c r="E110" t="s">
         <v>177</v>
       </c>
-      <c r="F110" s="0" t="s">
+      <c r="F110" t="s">
         <v>398</v>
       </c>
-      <c r="G110" s="0" t="s">
+      <c r="G110" t="s">
         <v>185</v>
       </c>
-      <c r="H110" s="0" t="s">
-        <v>19</v>
-      </c>
-      <c r="I110" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="J110" s="0" t="s">
+      <c r="H110" t="s">
+        <v>19</v>
+      </c>
+      <c r="I110" t="s">
+        <v>20</v>
+      </c>
+      <c r="J110" t="s">
         <v>23</v>
       </c>
       <c r="K110" s="2">
@@ -5977,35 +6396,35 @@
         <v>18033.2</v>
       </c>
     </row>
-    <row r="111">
-      <c r="A111" s="0" t="s">
+    <row r="111" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
         <v>390</v>
       </c>
-      <c r="B111" s="0" t="s">
+      <c r="B111" t="s">
         <v>391</v>
       </c>
-      <c r="C111" s="0" t="s">
+      <c r="C111" t="s">
         <v>392</v>
       </c>
-      <c r="D111" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="E111" s="0" t="s">
+      <c r="D111" t="s">
+        <v>15</v>
+      </c>
+      <c r="E111" t="s">
         <v>177</v>
       </c>
-      <c r="F111" s="0" t="s">
+      <c r="F111" t="s">
         <v>399</v>
       </c>
-      <c r="G111" s="0" t="s">
+      <c r="G111" t="s">
         <v>400</v>
       </c>
-      <c r="H111" s="0" t="s">
-        <v>19</v>
-      </c>
-      <c r="I111" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="J111" s="0" t="s">
+      <c r="H111" t="s">
+        <v>19</v>
+      </c>
+      <c r="I111" t="s">
+        <v>20</v>
+      </c>
+      <c r="J111" t="s">
         <v>23</v>
       </c>
       <c r="K111" s="2">
@@ -6015,35 +6434,35 @@
         <v>12050</v>
       </c>
     </row>
-    <row r="112">
-      <c r="A112" s="0" t="s">
+    <row r="112" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
         <v>390</v>
       </c>
-      <c r="B112" s="0" t="s">
+      <c r="B112" t="s">
         <v>391</v>
       </c>
-      <c r="C112" s="0" t="s">
+      <c r="C112" t="s">
         <v>392</v>
       </c>
-      <c r="D112" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="E112" s="0" t="s">
+      <c r="D112" t="s">
+        <v>15</v>
+      </c>
+      <c r="E112" t="s">
         <v>177</v>
       </c>
-      <c r="F112" s="0" t="s">
+      <c r="F112" t="s">
         <v>401</v>
       </c>
-      <c r="G112" s="0" t="s">
+      <c r="G112" t="s">
         <v>402</v>
       </c>
-      <c r="H112" s="0" t="s">
-        <v>19</v>
-      </c>
-      <c r="I112" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="J112" s="0" t="s">
+      <c r="H112" t="s">
+        <v>19</v>
+      </c>
+      <c r="I112" t="s">
+        <v>20</v>
+      </c>
+      <c r="J112" t="s">
         <v>23</v>
       </c>
       <c r="K112" s="2">
@@ -6053,111 +6472,111 @@
         <v>9970.83</v>
       </c>
     </row>
-    <row r="113">
-      <c r="A113" s="0" t="s">
+    <row r="113" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
         <v>390</v>
       </c>
-      <c r="B113" s="0" t="s">
+      <c r="B113" t="s">
         <v>391</v>
       </c>
-      <c r="C113" s="0" t="s">
+      <c r="C113" t="s">
         <v>392</v>
       </c>
-      <c r="D113" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="E113" s="0" t="s">
+      <c r="D113" t="s">
+        <v>15</v>
+      </c>
+      <c r="E113" t="s">
         <v>177</v>
       </c>
-      <c r="F113" s="0" t="s">
+      <c r="F113" t="s">
         <v>403</v>
       </c>
-      <c r="G113" s="0" t="s">
+      <c r="G113" t="s">
         <v>271</v>
       </c>
-      <c r="H113" s="0" t="s">
-        <v>19</v>
-      </c>
-      <c r="I113" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="J113" s="0" t="s">
+      <c r="H113" t="s">
+        <v>19</v>
+      </c>
+      <c r="I113" t="s">
+        <v>20</v>
+      </c>
+      <c r="J113" t="s">
         <v>23</v>
       </c>
       <c r="K113" s="2">
         <v>9</v>
       </c>
       <c r="L113" s="2">
-        <v>10428.37</v>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" s="0" t="s">
+        <v>10428.370000000001</v>
+      </c>
+    </row>
+    <row r="114" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A114" t="s">
         <v>390</v>
       </c>
-      <c r="B114" s="0" t="s">
+      <c r="B114" t="s">
         <v>391</v>
       </c>
-      <c r="C114" s="0" t="s">
+      <c r="C114" t="s">
         <v>392</v>
       </c>
-      <c r="D114" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="E114" s="0" t="s">
+      <c r="D114" t="s">
+        <v>15</v>
+      </c>
+      <c r="E114" t="s">
         <v>177</v>
       </c>
-      <c r="F114" s="0" t="s">
+      <c r="F114" t="s">
         <v>404</v>
       </c>
-      <c r="G114" s="0" t="s">
+      <c r="G114" t="s">
         <v>185</v>
       </c>
-      <c r="H114" s="0" t="s">
-        <v>19</v>
-      </c>
-      <c r="I114" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="J114" s="0" t="s">
+      <c r="H114" t="s">
+        <v>19</v>
+      </c>
+      <c r="I114" t="s">
+        <v>20</v>
+      </c>
+      <c r="J114" t="s">
         <v>23</v>
       </c>
       <c r="K114" s="2">
         <v>9</v>
       </c>
       <c r="L114" s="2">
-        <v>10428.37</v>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" s="0" t="s">
+        <v>10428.370000000001</v>
+      </c>
+    </row>
+    <row r="115" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A115" t="s">
         <v>405</v>
       </c>
-      <c r="B115" s="0" t="s">
+      <c r="B115" t="s">
         <v>391</v>
       </c>
-      <c r="C115" s="0" t="s">
+      <c r="C115" t="s">
         <v>406</v>
       </c>
-      <c r="D115" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="E115" s="0" t="s">
+      <c r="D115" t="s">
+        <v>15</v>
+      </c>
+      <c r="E115" t="s">
         <v>177</v>
       </c>
-      <c r="F115" s="0" t="s">
+      <c r="F115" t="s">
         <v>407</v>
       </c>
-      <c r="G115" s="0" t="s">
+      <c r="G115" t="s">
         <v>185</v>
       </c>
-      <c r="H115" s="0" t="s">
-        <v>19</v>
-      </c>
-      <c r="I115" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="J115" s="0" t="s">
+      <c r="H115" t="s">
+        <v>19</v>
+      </c>
+      <c r="I115" t="s">
+        <v>20</v>
+      </c>
+      <c r="J115" t="s">
         <v>20</v>
       </c>
       <c r="K115" s="2">
@@ -6167,35 +6586,35 @@
         <v>4666.8</v>
       </c>
     </row>
-    <row r="116">
-      <c r="A116" s="0" t="s">
+    <row r="116" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A116" t="s">
         <v>405</v>
       </c>
-      <c r="B116" s="0" t="s">
+      <c r="B116" t="s">
         <v>391</v>
       </c>
-      <c r="C116" s="0" t="s">
+      <c r="C116" t="s">
         <v>406</v>
       </c>
-      <c r="D116" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="E116" s="0" t="s">
+      <c r="D116" t="s">
+        <v>15</v>
+      </c>
+      <c r="E116" t="s">
         <v>177</v>
       </c>
-      <c r="F116" s="0" t="s">
+      <c r="F116" t="s">
         <v>408</v>
       </c>
-      <c r="G116" s="0" t="s">
+      <c r="G116" t="s">
         <v>185</v>
       </c>
-      <c r="H116" s="0" t="s">
-        <v>19</v>
-      </c>
-      <c r="I116" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="J116" s="0" t="s">
+      <c r="H116" t="s">
+        <v>19</v>
+      </c>
+      <c r="I116" t="s">
+        <v>20</v>
+      </c>
+      <c r="J116" t="s">
         <v>20</v>
       </c>
       <c r="K116" s="2">
@@ -6205,35 +6624,35 @@
         <v>4666.8</v>
       </c>
     </row>
-    <row r="117">
-      <c r="A117" s="0" t="s">
+    <row r="117" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A117" t="s">
         <v>405</v>
       </c>
-      <c r="B117" s="0" t="s">
+      <c r="B117" t="s">
         <v>391</v>
       </c>
-      <c r="C117" s="0" t="s">
+      <c r="C117" t="s">
         <v>406</v>
       </c>
-      <c r="D117" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="E117" s="0" t="s">
+      <c r="D117" t="s">
+        <v>15</v>
+      </c>
+      <c r="E117" t="s">
         <v>177</v>
       </c>
-      <c r="F117" s="0" t="s">
+      <c r="F117" t="s">
         <v>409</v>
       </c>
-      <c r="G117" s="0" t="s">
+      <c r="G117" t="s">
         <v>276</v>
       </c>
-      <c r="H117" s="0" t="s">
-        <v>19</v>
-      </c>
-      <c r="I117" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="J117" s="0" t="s">
+      <c r="H117" t="s">
+        <v>19</v>
+      </c>
+      <c r="I117" t="s">
+        <v>20</v>
+      </c>
+      <c r="J117" t="s">
         <v>20</v>
       </c>
       <c r="K117" s="2">
@@ -6243,35 +6662,35 @@
         <v>64.94</v>
       </c>
     </row>
-    <row r="118">
-      <c r="A118" s="0" t="s">
+    <row r="118" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A118" t="s">
         <v>405</v>
       </c>
-      <c r="B118" s="0" t="s">
+      <c r="B118" t="s">
         <v>391</v>
       </c>
-      <c r="C118" s="0" t="s">
+      <c r="C118" t="s">
         <v>406</v>
       </c>
-      <c r="D118" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="E118" s="0" t="s">
+      <c r="D118" t="s">
+        <v>15</v>
+      </c>
+      <c r="E118" t="s">
         <v>177</v>
       </c>
-      <c r="F118" s="0" t="s">
+      <c r="F118" t="s">
         <v>410</v>
       </c>
-      <c r="G118" s="0" t="s">
+      <c r="G118" t="s">
         <v>276</v>
       </c>
-      <c r="H118" s="0" t="s">
+      <c r="H118" t="s">
         <v>23</v>
       </c>
-      <c r="I118" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="J118" s="0" t="s">
+      <c r="I118" t="s">
+        <v>20</v>
+      </c>
+      <c r="J118" t="s">
         <v>20</v>
       </c>
       <c r="K118" s="2">
@@ -6281,35 +6700,35 @@
         <v>64.94</v>
       </c>
     </row>
-    <row r="119">
-      <c r="A119" s="0" t="s">
+    <row r="119" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A119" t="s">
         <v>405</v>
       </c>
-      <c r="B119" s="0" t="s">
+      <c r="B119" t="s">
         <v>391</v>
       </c>
-      <c r="C119" s="0" t="s">
+      <c r="C119" t="s">
         <v>406</v>
       </c>
-      <c r="D119" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="E119" s="0" t="s">
+      <c r="D119" t="s">
+        <v>15</v>
+      </c>
+      <c r="E119" t="s">
         <v>177</v>
       </c>
-      <c r="F119" s="0" t="s">
+      <c r="F119" t="s">
         <v>411</v>
       </c>
-      <c r="G119" s="0" t="s">
+      <c r="G119" t="s">
         <v>276</v>
       </c>
-      <c r="H119" s="0" t="s">
+      <c r="H119" t="s">
         <v>23</v>
       </c>
-      <c r="I119" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="J119" s="0" t="s">
+      <c r="I119" t="s">
+        <v>20</v>
+      </c>
+      <c r="J119" t="s">
         <v>20</v>
       </c>
       <c r="K119" s="2">
@@ -6319,35 +6738,35 @@
         <v>64.94</v>
       </c>
     </row>
-    <row r="120">
-      <c r="A120" s="0" t="s">
+    <row r="120" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A120" t="s">
         <v>405</v>
       </c>
-      <c r="B120" s="0" t="s">
+      <c r="B120" t="s">
         <v>391</v>
       </c>
-      <c r="C120" s="0" t="s">
+      <c r="C120" t="s">
         <v>406</v>
       </c>
-      <c r="D120" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="E120" s="0" t="s">
+      <c r="D120" t="s">
+        <v>15</v>
+      </c>
+      <c r="E120" t="s">
         <v>177</v>
       </c>
-      <c r="F120" s="0" t="s">
+      <c r="F120" t="s">
         <v>412</v>
       </c>
-      <c r="G120" s="0" t="s">
+      <c r="G120" t="s">
         <v>276</v>
       </c>
-      <c r="H120" s="0" t="s">
+      <c r="H120" t="s">
         <v>23</v>
       </c>
-      <c r="I120" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="J120" s="0" t="s">
+      <c r="I120" t="s">
+        <v>20</v>
+      </c>
+      <c r="J120" t="s">
         <v>20</v>
       </c>
       <c r="K120" s="2">
@@ -6357,35 +6776,35 @@
         <v>64.94</v>
       </c>
     </row>
-    <row r="121">
-      <c r="A121" s="0" t="s">
+    <row r="121" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A121" t="s">
         <v>405</v>
       </c>
-      <c r="B121" s="0" t="s">
+      <c r="B121" t="s">
         <v>391</v>
       </c>
-      <c r="C121" s="0" t="s">
+      <c r="C121" t="s">
         <v>406</v>
       </c>
-      <c r="D121" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="E121" s="0" t="s">
+      <c r="D121" t="s">
+        <v>15</v>
+      </c>
+      <c r="E121" t="s">
         <v>177</v>
       </c>
-      <c r="F121" s="0" t="s">
+      <c r="F121" t="s">
         <v>413</v>
       </c>
-      <c r="G121" s="0" t="s">
+      <c r="G121" t="s">
         <v>276</v>
       </c>
-      <c r="H121" s="0" t="s">
+      <c r="H121" t="s">
         <v>23</v>
       </c>
-      <c r="I121" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="J121" s="0" t="s">
+      <c r="I121" t="s">
+        <v>20</v>
+      </c>
+      <c r="J121" t="s">
         <v>20</v>
       </c>
       <c r="K121" s="2">
@@ -6395,35 +6814,35 @@
         <v>64.94</v>
       </c>
     </row>
-    <row r="122">
-      <c r="A122" s="0" t="s">
+    <row r="122" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A122" t="s">
         <v>405</v>
       </c>
-      <c r="B122" s="0" t="s">
+      <c r="B122" t="s">
         <v>391</v>
       </c>
-      <c r="C122" s="0" t="s">
+      <c r="C122" t="s">
         <v>406</v>
       </c>
-      <c r="D122" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="E122" s="0" t="s">
+      <c r="D122" t="s">
+        <v>15</v>
+      </c>
+      <c r="E122" t="s">
         <v>177</v>
       </c>
-      <c r="F122" s="0" t="s">
+      <c r="F122" t="s">
         <v>414</v>
       </c>
-      <c r="G122" s="0" t="s">
+      <c r="G122" t="s">
         <v>276</v>
       </c>
-      <c r="H122" s="0" t="s">
+      <c r="H122" t="s">
         <v>23</v>
       </c>
-      <c r="I122" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="J122" s="0" t="s">
+      <c r="I122" t="s">
+        <v>20</v>
+      </c>
+      <c r="J122" t="s">
         <v>20</v>
       </c>
       <c r="K122" s="2">
@@ -6433,35 +6852,35 @@
         <v>64.94</v>
       </c>
     </row>
-    <row r="123">
-      <c r="A123" s="0" t="s">
+    <row r="123" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A123" t="s">
         <v>405</v>
       </c>
-      <c r="B123" s="0" t="s">
+      <c r="B123" t="s">
         <v>391</v>
       </c>
-      <c r="C123" s="0" t="s">
+      <c r="C123" t="s">
         <v>406</v>
       </c>
-      <c r="D123" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="E123" s="0" t="s">
+      <c r="D123" t="s">
+        <v>15</v>
+      </c>
+      <c r="E123" t="s">
         <v>177</v>
       </c>
-      <c r="F123" s="0" t="s">
+      <c r="F123" t="s">
         <v>415</v>
       </c>
-      <c r="G123" s="0" t="s">
+      <c r="G123" t="s">
         <v>394</v>
       </c>
-      <c r="H123" s="0" t="s">
-        <v>19</v>
-      </c>
-      <c r="I123" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="J123" s="0" t="s">
+      <c r="H123" t="s">
+        <v>19</v>
+      </c>
+      <c r="I123" t="s">
+        <v>20</v>
+      </c>
+      <c r="J123" t="s">
         <v>20</v>
       </c>
       <c r="K123" s="2">
@@ -6471,35 +6890,35 @@
         <v>800</v>
       </c>
     </row>
-    <row r="124">
-      <c r="A124" s="0" t="s">
+    <row r="124" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A124" t="s">
         <v>405</v>
       </c>
-      <c r="B124" s="0" t="s">
+      <c r="B124" t="s">
         <v>391</v>
       </c>
-      <c r="C124" s="0" t="s">
+      <c r="C124" t="s">
         <v>406</v>
       </c>
-      <c r="D124" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="E124" s="0" t="s">
+      <c r="D124" t="s">
+        <v>15</v>
+      </c>
+      <c r="E124" t="s">
         <v>177</v>
       </c>
-      <c r="F124" s="0" t="s">
+      <c r="F124" t="s">
         <v>416</v>
       </c>
-      <c r="G124" s="0" t="s">
+      <c r="G124" t="s">
         <v>276</v>
       </c>
-      <c r="H124" s="0" t="s">
+      <c r="H124" t="s">
         <v>23</v>
       </c>
-      <c r="I124" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="J124" s="0" t="s">
+      <c r="I124" t="s">
+        <v>20</v>
+      </c>
+      <c r="J124" t="s">
         <v>20</v>
       </c>
       <c r="K124" s="2">
@@ -6509,35 +6928,35 @@
         <v>64.94</v>
       </c>
     </row>
-    <row r="125">
-      <c r="A125" s="0" t="s">
+    <row r="125" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A125" t="s">
         <v>405</v>
       </c>
-      <c r="B125" s="0" t="s">
+      <c r="B125" t="s">
         <v>391</v>
       </c>
-      <c r="C125" s="0" t="s">
+      <c r="C125" t="s">
         <v>406</v>
       </c>
-      <c r="D125" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="E125" s="0" t="s">
+      <c r="D125" t="s">
+        <v>15</v>
+      </c>
+      <c r="E125" t="s">
         <v>177</v>
       </c>
-      <c r="F125" s="0" t="s">
+      <c r="F125" t="s">
         <v>417</v>
       </c>
-      <c r="G125" s="0" t="s">
+      <c r="G125" t="s">
         <v>200</v>
       </c>
-      <c r="H125" s="0" t="s">
-        <v>19</v>
-      </c>
-      <c r="I125" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="J125" s="0" t="s">
+      <c r="H125" t="s">
+        <v>19</v>
+      </c>
+      <c r="I125" t="s">
+        <v>20</v>
+      </c>
+      <c r="J125" t="s">
         <v>20</v>
       </c>
       <c r="K125" s="2">
@@ -6547,35 +6966,35 @@
         <v>5518</v>
       </c>
     </row>
-    <row r="126">
-      <c r="A126" s="0" t="s">
+    <row r="126" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A126" t="s">
         <v>405</v>
       </c>
-      <c r="B126" s="0" t="s">
+      <c r="B126" t="s">
         <v>391</v>
       </c>
-      <c r="C126" s="0" t="s">
+      <c r="C126" t="s">
         <v>406</v>
       </c>
-      <c r="D126" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="E126" s="0" t="s">
+      <c r="D126" t="s">
+        <v>15</v>
+      </c>
+      <c r="E126" t="s">
         <v>177</v>
       </c>
-      <c r="F126" s="0" t="s">
+      <c r="F126" t="s">
         <v>418</v>
       </c>
-      <c r="G126" s="0" t="s">
+      <c r="G126" t="s">
         <v>276</v>
       </c>
-      <c r="H126" s="0" t="s">
-        <v>19</v>
-      </c>
-      <c r="I126" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="J126" s="0" t="s">
+      <c r="H126" t="s">
+        <v>19</v>
+      </c>
+      <c r="I126" t="s">
+        <v>20</v>
+      </c>
+      <c r="J126" t="s">
         <v>20</v>
       </c>
       <c r="K126" s="2">
@@ -6585,35 +7004,35 @@
         <v>64.94</v>
       </c>
     </row>
-    <row r="127">
-      <c r="A127" s="0" t="s">
+    <row r="127" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A127" t="s">
         <v>405</v>
       </c>
-      <c r="B127" s="0" t="s">
+      <c r="B127" t="s">
         <v>391</v>
       </c>
-      <c r="C127" s="0" t="s">
+      <c r="C127" t="s">
         <v>406</v>
       </c>
-      <c r="D127" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="E127" s="0" t="s">
+      <c r="D127" t="s">
+        <v>15</v>
+      </c>
+      <c r="E127" t="s">
         <v>177</v>
       </c>
-      <c r="F127" s="0" t="s">
+      <c r="F127" t="s">
         <v>419</v>
       </c>
-      <c r="G127" s="0" t="s">
+      <c r="G127" t="s">
         <v>200</v>
       </c>
-      <c r="H127" s="0" t="s">
-        <v>19</v>
-      </c>
-      <c r="I127" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="J127" s="0" t="s">
+      <c r="H127" t="s">
+        <v>19</v>
+      </c>
+      <c r="I127" t="s">
+        <v>20</v>
+      </c>
+      <c r="J127" t="s">
         <v>20</v>
       </c>
       <c r="K127" s="2">
@@ -6623,35 +7042,35 @@
         <v>5518</v>
       </c>
     </row>
-    <row r="128">
-      <c r="A128" s="0" t="s">
+    <row r="128" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A128" t="s">
         <v>405</v>
       </c>
-      <c r="B128" s="0" t="s">
+      <c r="B128" t="s">
         <v>391</v>
       </c>
-      <c r="C128" s="0" t="s">
+      <c r="C128" t="s">
         <v>406</v>
       </c>
-      <c r="D128" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="E128" s="0" t="s">
+      <c r="D128" t="s">
+        <v>15</v>
+      </c>
+      <c r="E128" t="s">
         <v>177</v>
       </c>
-      <c r="F128" s="0" t="s">
+      <c r="F128" t="s">
         <v>420</v>
       </c>
-      <c r="G128" s="0" t="s">
+      <c r="G128" t="s">
         <v>185</v>
       </c>
-      <c r="H128" s="0" t="s">
-        <v>19</v>
-      </c>
-      <c r="I128" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="J128" s="0" t="s">
+      <c r="H128" t="s">
+        <v>19</v>
+      </c>
+      <c r="I128" t="s">
+        <v>20</v>
+      </c>
+      <c r="J128" t="s">
         <v>20</v>
       </c>
       <c r="K128" s="2">
@@ -6661,35 +7080,35 @@
         <v>800</v>
       </c>
     </row>
-    <row r="129">
-      <c r="A129" s="0" t="s">
+    <row r="129" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A129" t="s">
         <v>405</v>
       </c>
-      <c r="B129" s="0" t="s">
+      <c r="B129" t="s">
         <v>391</v>
       </c>
-      <c r="C129" s="0" t="s">
+      <c r="C129" t="s">
         <v>406</v>
       </c>
-      <c r="D129" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="E129" s="0" t="s">
+      <c r="D129" t="s">
+        <v>15</v>
+      </c>
+      <c r="E129" t="s">
         <v>177</v>
       </c>
-      <c r="F129" s="0" t="s">
+      <c r="F129" t="s">
         <v>421</v>
       </c>
-      <c r="G129" s="0" t="s">
+      <c r="G129" t="s">
         <v>185</v>
       </c>
-      <c r="H129" s="0" t="s">
-        <v>19</v>
-      </c>
-      <c r="I129" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="J129" s="0" t="s">
+      <c r="H129" t="s">
+        <v>19</v>
+      </c>
+      <c r="I129" t="s">
+        <v>20</v>
+      </c>
+      <c r="J129" t="s">
         <v>20</v>
       </c>
       <c r="K129" s="2">
@@ -6699,35 +7118,35 @@
         <v>800</v>
       </c>
     </row>
-    <row r="130">
-      <c r="A130" s="0" t="s">
+    <row r="130" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A130" t="s">
         <v>405</v>
       </c>
-      <c r="B130" s="0" t="s">
+      <c r="B130" t="s">
         <v>391</v>
       </c>
-      <c r="C130" s="0" t="s">
+      <c r="C130" t="s">
         <v>406</v>
       </c>
-      <c r="D130" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="E130" s="0" t="s">
+      <c r="D130" t="s">
+        <v>15</v>
+      </c>
+      <c r="E130" t="s">
         <v>177</v>
       </c>
-      <c r="F130" s="0" t="s">
+      <c r="F130" t="s">
         <v>422</v>
       </c>
-      <c r="G130" s="0" t="s">
+      <c r="G130" t="s">
         <v>185</v>
       </c>
-      <c r="H130" s="0" t="s">
-        <v>19</v>
-      </c>
-      <c r="I130" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="J130" s="0" t="s">
+      <c r="H130" t="s">
+        <v>19</v>
+      </c>
+      <c r="I130" t="s">
+        <v>20</v>
+      </c>
+      <c r="J130" t="s">
         <v>20</v>
       </c>
       <c r="K130" s="2">
@@ -6737,35 +7156,35 @@
         <v>1595</v>
       </c>
     </row>
-    <row r="131">
-      <c r="A131" s="0" t="s">
+    <row r="131" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A131" t="s">
         <v>423</v>
       </c>
-      <c r="B131" s="0" t="s">
+      <c r="B131" t="s">
         <v>424</v>
       </c>
-      <c r="C131" s="0" t="s">
+      <c r="C131" t="s">
         <v>425</v>
       </c>
-      <c r="D131" s="0" t="s">
+      <c r="D131" t="s">
         <v>27</v>
       </c>
-      <c r="E131" s="0" t="s">
+      <c r="E131" t="s">
         <v>65</v>
       </c>
-      <c r="F131" s="0" t="s">
+      <c r="F131" t="s">
         <v>426</v>
       </c>
-      <c r="G131" s="0" t="s">
+      <c r="G131" t="s">
         <v>427</v>
       </c>
-      <c r="H131" s="0" t="s">
-        <v>19</v>
-      </c>
-      <c r="I131" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="J131" s="0" t="s">
+      <c r="H131" t="s">
+        <v>19</v>
+      </c>
+      <c r="I131" t="s">
+        <v>20</v>
+      </c>
+      <c r="J131" t="s">
         <v>20</v>
       </c>
       <c r="K131" s="2">
@@ -6775,35 +7194,35 @@
         <v>648370.73</v>
       </c>
     </row>
-    <row r="132">
-      <c r="A132" s="0" t="s">
+    <row r="132" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A132" t="s">
         <v>428</v>
       </c>
-      <c r="B132" s="0" t="s">
+      <c r="B132" t="s">
         <v>429</v>
       </c>
-      <c r="C132" s="0" t="s">
+      <c r="C132" t="s">
         <v>430</v>
       </c>
-      <c r="D132" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="E132" s="0" t="s">
+      <c r="D132" t="s">
+        <v>15</v>
+      </c>
+      <c r="E132" t="s">
         <v>16</v>
       </c>
-      <c r="F132" s="0" t="s">
+      <c r="F132" t="s">
         <v>431</v>
       </c>
-      <c r="G132" s="0" t="s">
+      <c r="G132" t="s">
         <v>269</v>
       </c>
-      <c r="H132" s="0" t="s">
-        <v>19</v>
-      </c>
-      <c r="I132" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="J132" s="0" t="s">
+      <c r="H132" t="s">
+        <v>19</v>
+      </c>
+      <c r="I132" t="s">
+        <v>20</v>
+      </c>
+      <c r="J132" t="s">
         <v>20</v>
       </c>
       <c r="K132" s="2">
@@ -6813,35 +7232,35 @@
         <v>13140</v>
       </c>
     </row>
-    <row r="133">
-      <c r="A133" s="0" t="s">
+    <row r="133" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A133" t="s">
         <v>428</v>
       </c>
-      <c r="B133" s="0" t="s">
+      <c r="B133" t="s">
         <v>429</v>
       </c>
-      <c r="C133" s="0" t="s">
+      <c r="C133" t="s">
         <v>430</v>
       </c>
-      <c r="D133" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="E133" s="0" t="s">
+      <c r="D133" t="s">
+        <v>15</v>
+      </c>
+      <c r="E133" t="s">
         <v>16</v>
       </c>
-      <c r="F133" s="0" t="s">
+      <c r="F133" t="s">
         <v>432</v>
       </c>
-      <c r="G133" s="0" t="s">
+      <c r="G133" t="s">
         <v>269</v>
       </c>
-      <c r="H133" s="0" t="s">
-        <v>19</v>
-      </c>
-      <c r="I133" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="J133" s="0" t="s">
+      <c r="H133" t="s">
+        <v>19</v>
+      </c>
+      <c r="I133" t="s">
+        <v>20</v>
+      </c>
+      <c r="J133" t="s">
         <v>20</v>
       </c>
       <c r="K133" s="2">
@@ -6851,35 +7270,35 @@
         <v>3200</v>
       </c>
     </row>
-    <row r="134">
-      <c r="A134" s="0" t="s">
+    <row r="134" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A134" t="s">
         <v>428</v>
       </c>
-      <c r="B134" s="0" t="s">
+      <c r="B134" t="s">
         <v>429</v>
       </c>
-      <c r="C134" s="0" t="s">
+      <c r="C134" t="s">
         <v>430</v>
       </c>
-      <c r="D134" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="E134" s="0" t="s">
+      <c r="D134" t="s">
+        <v>15</v>
+      </c>
+      <c r="E134" t="s">
         <v>16</v>
       </c>
-      <c r="F134" s="0" t="s">
+      <c r="F134" t="s">
         <v>433</v>
       </c>
-      <c r="G134" s="0" t="s">
+      <c r="G134" t="s">
         <v>309</v>
       </c>
-      <c r="H134" s="0" t="s">
-        <v>19</v>
-      </c>
-      <c r="I134" s="0" t="s">
+      <c r="H134" t="s">
+        <v>19</v>
+      </c>
+      <c r="I134" t="s">
         <v>23</v>
       </c>
-      <c r="J134" s="0" t="s">
+      <c r="J134" t="s">
         <v>23</v>
       </c>
       <c r="K134" s="2">
@@ -6889,35 +7308,35 @@
         <v>41869.75</v>
       </c>
     </row>
-    <row r="135">
-      <c r="A135" s="0" t="s">
+    <row r="135" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A135" t="s">
         <v>434</v>
       </c>
-      <c r="B135" s="0" t="s">
+      <c r="B135" t="s">
         <v>435</v>
       </c>
-      <c r="C135" s="0" t="s">
+      <c r="C135" t="s">
         <v>436</v>
       </c>
-      <c r="D135" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="E135" s="0" t="s">
+      <c r="D135" t="s">
+        <v>15</v>
+      </c>
+      <c r="E135" t="s">
         <v>16</v>
       </c>
-      <c r="F135" s="0" t="s">
+      <c r="F135" t="s">
         <v>437</v>
       </c>
-      <c r="G135" s="0" t="s">
+      <c r="G135" t="s">
         <v>311</v>
       </c>
-      <c r="H135" s="0" t="s">
-        <v>19</v>
-      </c>
-      <c r="I135" s="0" t="s">
+      <c r="H135" t="s">
+        <v>19</v>
+      </c>
+      <c r="I135" t="s">
         <v>23</v>
       </c>
-      <c r="J135" s="0" t="s">
+      <c r="J135" t="s">
         <v>23</v>
       </c>
       <c r="K135" s="2">
@@ -6927,35 +7346,35 @@
         <v>26900</v>
       </c>
     </row>
-    <row r="136">
-      <c r="A136" s="0" t="s">
+    <row r="136" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A136" t="s">
         <v>438</v>
       </c>
-      <c r="B136" s="0" t="s">
+      <c r="B136" t="s">
         <v>439</v>
       </c>
-      <c r="C136" s="0" t="s">
+      <c r="C136" t="s">
         <v>440</v>
       </c>
-      <c r="D136" s="0" t="s">
+      <c r="D136" t="s">
         <v>27</v>
       </c>
-      <c r="E136" s="0" t="s">
+      <c r="E136" t="s">
         <v>28</v>
       </c>
-      <c r="F136" s="0" t="s">
+      <c r="F136" t="s">
         <v>441</v>
       </c>
-      <c r="G136" s="0" t="s">
+      <c r="G136" t="s">
         <v>30</v>
       </c>
-      <c r="H136" s="0" t="s">
-        <v>19</v>
-      </c>
-      <c r="I136" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="J136" s="0" t="s">
+      <c r="H136" t="s">
+        <v>19</v>
+      </c>
+      <c r="I136" t="s">
+        <v>20</v>
+      </c>
+      <c r="J136" t="s">
         <v>20</v>
       </c>
       <c r="K136" s="2">
@@ -6965,35 +7384,35 @@
         <v>16937.41</v>
       </c>
     </row>
-    <row r="137">
-      <c r="A137" s="0" t="s">
+    <row r="137" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A137" t="s">
         <v>442</v>
       </c>
-      <c r="B137" s="0" t="s">
+      <c r="B137" t="s">
         <v>443</v>
       </c>
-      <c r="C137" s="0" t="s">
+      <c r="C137" t="s">
         <v>444</v>
       </c>
-      <c r="D137" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="E137" s="0" t="s">
+      <c r="D137" t="s">
+        <v>15</v>
+      </c>
+      <c r="E137" t="s">
         <v>16</v>
       </c>
-      <c r="F137" s="0" t="s">
+      <c r="F137" t="s">
         <v>445</v>
       </c>
-      <c r="G137" s="0" t="s">
+      <c r="G137" t="s">
         <v>446</v>
       </c>
-      <c r="H137" s="0" t="s">
+      <c r="H137" t="s">
         <v>23</v>
       </c>
-      <c r="I137" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="J137" s="0" t="s">
+      <c r="I137" t="s">
+        <v>20</v>
+      </c>
+      <c r="J137" t="s">
         <v>20</v>
       </c>
       <c r="K137" s="2">
@@ -7003,35 +7422,35 @@
         <v>1900</v>
       </c>
     </row>
-    <row r="138">
-      <c r="A138" s="0" t="s">
+    <row r="138" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A138" t="s">
         <v>442</v>
       </c>
-      <c r="B138" s="0" t="s">
+      <c r="B138" t="s">
         <v>443</v>
       </c>
-      <c r="C138" s="0" t="s">
+      <c r="C138" t="s">
         <v>444</v>
       </c>
-      <c r="D138" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="E138" s="0" t="s">
+      <c r="D138" t="s">
+        <v>15</v>
+      </c>
+      <c r="E138" t="s">
         <v>16</v>
       </c>
-      <c r="F138" s="0" t="s">
+      <c r="F138" t="s">
         <v>447</v>
       </c>
-      <c r="G138" s="0" t="s">
+      <c r="G138" t="s">
         <v>448</v>
       </c>
-      <c r="H138" s="0" t="s">
-        <v>19</v>
-      </c>
-      <c r="I138" s="0" t="s">
+      <c r="H138" t="s">
+        <v>19</v>
+      </c>
+      <c r="I138" t="s">
         <v>23</v>
       </c>
-      <c r="J138" s="0" t="s">
+      <c r="J138" t="s">
         <v>23</v>
       </c>
       <c r="K138" s="2">
@@ -7041,35 +7460,35 @@
         <v>11850</v>
       </c>
     </row>
-    <row r="139">
-      <c r="A139" s="0" t="s">
+    <row r="139" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A139" t="s">
         <v>442</v>
       </c>
-      <c r="B139" s="0" t="s">
+      <c r="B139" t="s">
         <v>443</v>
       </c>
-      <c r="C139" s="0" t="s">
+      <c r="C139" t="s">
         <v>444</v>
       </c>
-      <c r="D139" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="E139" s="0" t="s">
+      <c r="D139" t="s">
+        <v>15</v>
+      </c>
+      <c r="E139" t="s">
         <v>16</v>
       </c>
-      <c r="F139" s="0" t="s">
+      <c r="F139" t="s">
         <v>449</v>
       </c>
-      <c r="G139" s="0" t="s">
+      <c r="G139" t="s">
         <v>450</v>
       </c>
-      <c r="H139" s="0" t="s">
-        <v>19</v>
-      </c>
-      <c r="I139" s="0" t="s">
+      <c r="H139" t="s">
+        <v>19</v>
+      </c>
+      <c r="I139" t="s">
         <v>23</v>
       </c>
-      <c r="J139" s="0" t="s">
+      <c r="J139" t="s">
         <v>23</v>
       </c>
       <c r="K139" s="2">
@@ -7079,35 +7498,35 @@
         <v>15690</v>
       </c>
     </row>
-    <row r="140">
-      <c r="A140" s="0" t="s">
+    <row r="140" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A140" t="s">
         <v>442</v>
       </c>
-      <c r="B140" s="0" t="s">
+      <c r="B140" t="s">
         <v>443</v>
       </c>
-      <c r="C140" s="0" t="s">
+      <c r="C140" t="s">
         <v>444</v>
       </c>
-      <c r="D140" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="E140" s="0" t="s">
+      <c r="D140" t="s">
+        <v>15</v>
+      </c>
+      <c r="E140" t="s">
         <v>16</v>
       </c>
-      <c r="F140" s="0" t="s">
+      <c r="F140" t="s">
         <v>451</v>
       </c>
-      <c r="G140" s="0" t="s">
+      <c r="G140" t="s">
         <v>452</v>
       </c>
-      <c r="H140" s="0" t="s">
-        <v>19</v>
-      </c>
-      <c r="I140" s="0" t="s">
+      <c r="H140" t="s">
+        <v>19</v>
+      </c>
+      <c r="I140" t="s">
         <v>23</v>
       </c>
-      <c r="J140" s="0" t="s">
+      <c r="J140" t="s">
         <v>23</v>
       </c>
       <c r="K140" s="2">
@@ -7117,35 +7536,35 @@
         <v>16200</v>
       </c>
     </row>
-    <row r="141">
-      <c r="A141" s="0" t="s">
+    <row r="141" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A141" t="s">
         <v>453</v>
       </c>
-      <c r="B141" s="0" t="s">
+      <c r="B141" t="s">
         <v>454</v>
       </c>
-      <c r="C141" s="0" t="s">
+      <c r="C141" t="s">
         <v>455</v>
       </c>
-      <c r="D141" s="0" t="s">
+      <c r="D141" t="s">
         <v>27</v>
       </c>
-      <c r="E141" s="0" t="s">
+      <c r="E141" t="s">
         <v>65</v>
       </c>
-      <c r="F141" s="0" t="s">
+      <c r="F141" t="s">
         <v>456</v>
       </c>
-      <c r="G141" s="0" t="s">
+      <c r="G141" t="s">
         <v>250</v>
       </c>
-      <c r="H141" s="0" t="s">
-        <v>19</v>
-      </c>
-      <c r="I141" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="J141" s="0" t="s">
+      <c r="H141" t="s">
+        <v>19</v>
+      </c>
+      <c r="I141" t="s">
+        <v>20</v>
+      </c>
+      <c r="J141" t="s">
         <v>20</v>
       </c>
       <c r="K141" s="2">
@@ -7155,35 +7574,35 @@
         <v>32242.11</v>
       </c>
     </row>
-    <row r="142">
-      <c r="A142" s="0" t="s">
+    <row r="142" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A142" t="s">
         <v>457</v>
       </c>
-      <c r="B142" s="0" t="s">
+      <c r="B142" t="s">
         <v>458</v>
       </c>
-      <c r="C142" s="0" t="s">
+      <c r="C142" t="s">
         <v>458</v>
       </c>
-      <c r="D142" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="E142" s="0" t="s">
+      <c r="D142" t="s">
+        <v>15</v>
+      </c>
+      <c r="E142" t="s">
         <v>16</v>
       </c>
-      <c r="F142" s="0" t="s">
+      <c r="F142" t="s">
         <v>459</v>
       </c>
-      <c r="G142" s="0" t="s">
+      <c r="G142" t="s">
         <v>36</v>
       </c>
-      <c r="H142" s="0" t="s">
+      <c r="H142" t="s">
         <v>23</v>
       </c>
-      <c r="I142" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="J142" s="0" t="s">
+      <c r="I142" t="s">
+        <v>20</v>
+      </c>
+      <c r="J142" t="s">
         <v>20</v>
       </c>
       <c r="K142" s="2">
@@ -7193,35 +7612,35 @@
         <v>2440.5</v>
       </c>
     </row>
-    <row r="143">
-      <c r="A143" s="0" t="s">
+    <row r="143" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A143" t="s">
         <v>460</v>
       </c>
-      <c r="B143" s="0" t="s">
+      <c r="B143" t="s">
         <v>461</v>
       </c>
-      <c r="C143" s="0" t="s">
+      <c r="C143" t="s">
         <v>462</v>
       </c>
-      <c r="D143" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="E143" s="0" t="s">
+      <c r="D143" t="s">
+        <v>15</v>
+      </c>
+      <c r="E143" t="s">
         <v>16</v>
       </c>
-      <c r="F143" s="0" t="s">
+      <c r="F143" t="s">
         <v>463</v>
       </c>
-      <c r="G143" s="0" t="s">
+      <c r="G143" t="s">
         <v>464</v>
       </c>
-      <c r="H143" s="0" t="s">
+      <c r="H143" t="s">
         <v>23</v>
       </c>
-      <c r="I143" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="J143" s="0" t="s">
+      <c r="I143" t="s">
+        <v>20</v>
+      </c>
+      <c r="J143" t="s">
         <v>20</v>
       </c>
       <c r="K143" s="2">
@@ -7231,35 +7650,35 @@
         <v>150</v>
       </c>
     </row>
-    <row r="144">
-      <c r="A144" s="0" t="s">
+    <row r="144" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A144" t="s">
         <v>465</v>
       </c>
-      <c r="B144" s="0" t="s">
+      <c r="B144" t="s">
         <v>466</v>
       </c>
-      <c r="C144" s="0" t="s">
+      <c r="C144" t="s">
         <v>467</v>
       </c>
-      <c r="D144" s="0" t="s">
+      <c r="D144" t="s">
         <v>27</v>
       </c>
-      <c r="E144" s="0" t="s">
+      <c r="E144" t="s">
         <v>28</v>
       </c>
-      <c r="F144" s="0" t="s">
+      <c r="F144" t="s">
         <v>266</v>
       </c>
-      <c r="G144" s="0" t="s">
+      <c r="G144" t="s">
         <v>135</v>
       </c>
-      <c r="H144" s="0" t="s">
-        <v>19</v>
-      </c>
-      <c r="I144" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="J144" s="0" t="s">
+      <c r="H144" t="s">
+        <v>19</v>
+      </c>
+      <c r="I144" t="s">
+        <v>20</v>
+      </c>
+      <c r="J144" t="s">
         <v>20</v>
       </c>
       <c r="K144" s="2">
@@ -7269,35 +7688,35 @@
         <v>208</v>
       </c>
     </row>
-    <row r="145">
-      <c r="A145" s="0" t="s">
+    <row r="145" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A145" t="s">
         <v>468</v>
       </c>
-      <c r="B145" s="0" t="s">
+      <c r="B145" t="s">
         <v>469</v>
       </c>
-      <c r="C145" s="0" t="s">
+      <c r="C145" t="s">
         <v>470</v>
       </c>
-      <c r="D145" s="0" t="s">
+      <c r="D145" t="s">
         <v>27</v>
       </c>
-      <c r="E145" s="0" t="s">
+      <c r="E145" t="s">
         <v>28</v>
       </c>
-      <c r="F145" s="0" t="s">
+      <c r="F145" t="s">
         <v>471</v>
       </c>
-      <c r="G145" s="0" t="s">
+      <c r="G145" t="s">
         <v>472</v>
       </c>
-      <c r="H145" s="0" t="s">
-        <v>19</v>
-      </c>
-      <c r="I145" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="J145" s="0" t="s">
+      <c r="H145" t="s">
+        <v>19</v>
+      </c>
+      <c r="I145" t="s">
+        <v>20</v>
+      </c>
+      <c r="J145" t="s">
         <v>20</v>
       </c>
       <c r="K145" s="2">
@@ -7307,111 +7726,111 @@
         <v>15819.32</v>
       </c>
     </row>
-    <row r="146">
-      <c r="A146" s="0" t="s">
+    <row r="146" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A146" t="s">
         <v>473</v>
       </c>
-      <c r="B146" s="0" t="s">
+      <c r="B146" t="s">
         <v>474</v>
       </c>
-      <c r="C146" s="0" t="s">
+      <c r="C146" t="s">
         <v>475</v>
       </c>
-      <c r="D146" s="0" t="s">
+      <c r="D146" t="s">
         <v>27</v>
       </c>
-      <c r="E146" s="0" t="s">
+      <c r="E146" t="s">
         <v>28</v>
       </c>
-      <c r="F146" s="0" t="s">
+      <c r="F146" t="s">
         <v>476</v>
       </c>
-      <c r="G146" s="0" t="s">
+      <c r="G146" t="s">
         <v>250</v>
       </c>
-      <c r="H146" s="0" t="s">
-        <v>19</v>
-      </c>
-      <c r="I146" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="J146" s="0" t="s">
+      <c r="H146" t="s">
+        <v>19</v>
+      </c>
+      <c r="I146" t="s">
+        <v>20</v>
+      </c>
+      <c r="J146" t="s">
         <v>20</v>
       </c>
       <c r="K146" s="2">
         <v>6</v>
       </c>
       <c r="L146" s="2">
-        <v>2478.76</v>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" s="0" t="s">
+        <v>2478.7600000000002</v>
+      </c>
+    </row>
+    <row r="147" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A147" t="s">
         <v>477</v>
       </c>
-      <c r="B147" s="0" t="s">
+      <c r="B147" t="s">
         <v>478</v>
       </c>
-      <c r="C147" s="0" t="s">
+      <c r="C147" t="s">
         <v>479</v>
       </c>
-      <c r="D147" s="0" t="s">
+      <c r="D147" t="s">
         <v>27</v>
       </c>
-      <c r="E147" s="0" t="s">
+      <c r="E147" t="s">
         <v>28</v>
       </c>
-      <c r="F147" s="0" t="s">
+      <c r="F147" t="s">
         <v>480</v>
       </c>
-      <c r="G147" s="0" t="s">
+      <c r="G147" t="s">
         <v>78</v>
       </c>
-      <c r="H147" s="0" t="s">
-        <v>19</v>
-      </c>
-      <c r="I147" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="J147" s="0" t="s">
+      <c r="H147" t="s">
+        <v>19</v>
+      </c>
+      <c r="I147" t="s">
+        <v>20</v>
+      </c>
+      <c r="J147" t="s">
         <v>20</v>
       </c>
       <c r="K147" s="2">
         <v>4</v>
       </c>
       <c r="L147" s="2">
-        <v>10358.88</v>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" s="0" t="s">
+        <v>10358.879999999999</v>
+      </c>
+    </row>
+    <row r="148" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A148" t="s">
         <v>481</v>
       </c>
-      <c r="B148" s="0" t="s">
+      <c r="B148" t="s">
         <v>482</v>
       </c>
-      <c r="C148" s="0" t="s">
+      <c r="C148" t="s">
         <v>482</v>
       </c>
-      <c r="D148" s="0" t="s">
+      <c r="D148" t="s">
         <v>27</v>
       </c>
-      <c r="E148" s="0" t="s">
+      <c r="E148" t="s">
         <v>28</v>
       </c>
-      <c r="F148" s="0" t="s">
+      <c r="F148" t="s">
         <v>483</v>
       </c>
-      <c r="G148" s="0" t="s">
+      <c r="G148" t="s">
         <v>53</v>
       </c>
-      <c r="H148" s="0" t="s">
-        <v>19</v>
-      </c>
-      <c r="I148" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="J148" s="0" t="s">
+      <c r="H148" t="s">
+        <v>19</v>
+      </c>
+      <c r="I148" t="s">
+        <v>20</v>
+      </c>
+      <c r="J148" t="s">
         <v>20</v>
       </c>
       <c r="K148" s="2">
@@ -7421,35 +7840,35 @@
         <v>1193.52</v>
       </c>
     </row>
-    <row r="149">
-      <c r="A149" s="0" t="s">
+    <row r="149" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A149" t="s">
         <v>484</v>
       </c>
-      <c r="B149" s="0" t="s">
+      <c r="B149" t="s">
         <v>485</v>
       </c>
-      <c r="C149" s="0" t="s">
+      <c r="C149" t="s">
         <v>486</v>
       </c>
-      <c r="D149" s="0" t="s">
+      <c r="D149" t="s">
         <v>27</v>
       </c>
-      <c r="E149" s="0" t="s">
+      <c r="E149" t="s">
         <v>163</v>
       </c>
-      <c r="F149" s="0" t="s">
+      <c r="F149" t="s">
         <v>209</v>
       </c>
-      <c r="G149" s="0" t="s">
+      <c r="G149" t="s">
         <v>72</v>
       </c>
-      <c r="H149" s="0" t="s">
-        <v>19</v>
-      </c>
-      <c r="I149" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="J149" s="0" t="s">
+      <c r="H149" t="s">
+        <v>19</v>
+      </c>
+      <c r="I149" t="s">
+        <v>20</v>
+      </c>
+      <c r="J149" t="s">
         <v>20</v>
       </c>
       <c r="K149" s="2">
@@ -7459,73 +7878,73 @@
         <v>6557.39</v>
       </c>
     </row>
-    <row r="150">
-      <c r="A150" s="0" t="s">
+    <row r="150" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A150" t="s">
         <v>487</v>
       </c>
-      <c r="B150" s="0" t="s">
+      <c r="B150" t="s">
         <v>488</v>
       </c>
-      <c r="C150" s="0" t="s">
+      <c r="C150" t="s">
         <v>488</v>
       </c>
-      <c r="D150" s="0" t="s">
+      <c r="D150" t="s">
         <v>27</v>
       </c>
-      <c r="E150" s="0" t="s">
+      <c r="E150" t="s">
         <v>65</v>
       </c>
-      <c r="F150" s="0" t="s">
+      <c r="F150" t="s">
         <v>489</v>
       </c>
-      <c r="G150" s="0" t="s">
+      <c r="G150" t="s">
         <v>311</v>
       </c>
-      <c r="H150" s="0" t="s">
-        <v>19</v>
-      </c>
-      <c r="I150" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="J150" s="0" t="s">
+      <c r="H150" t="s">
+        <v>19</v>
+      </c>
+      <c r="I150" t="s">
+        <v>20</v>
+      </c>
+      <c r="J150" t="s">
         <v>20</v>
       </c>
       <c r="K150" s="2">
         <v>57</v>
       </c>
       <c r="L150" s="2">
-        <v>545850.81</v>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" s="0" t="s">
+        <v>545850.81000000006</v>
+      </c>
+    </row>
+    <row r="151" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A151" t="s">
         <v>490</v>
       </c>
-      <c r="B151" s="0" t="s">
+      <c r="B151" t="s">
         <v>491</v>
       </c>
-      <c r="C151" s="0" t="s">
+      <c r="C151" t="s">
         <v>492</v>
       </c>
-      <c r="D151" s="0" t="s">
+      <c r="D151" t="s">
         <v>27</v>
       </c>
-      <c r="E151" s="0" t="s">
+      <c r="E151" t="s">
         <v>65</v>
       </c>
-      <c r="F151" s="0" t="s">
+      <c r="F151" t="s">
         <v>493</v>
       </c>
-      <c r="G151" s="0" t="s">
+      <c r="G151" t="s">
         <v>140</v>
       </c>
-      <c r="H151" s="0" t="s">
-        <v>19</v>
-      </c>
-      <c r="I151" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="J151" s="0" t="s">
+      <c r="H151" t="s">
+        <v>19</v>
+      </c>
+      <c r="I151" t="s">
+        <v>20</v>
+      </c>
+      <c r="J151" t="s">
         <v>20</v>
       </c>
       <c r="K151" s="2">
@@ -7535,35 +7954,35 @@
         <v>10838.94</v>
       </c>
     </row>
-    <row r="152">
-      <c r="A152" s="0" t="s">
+    <row r="152" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A152" t="s">
         <v>494</v>
       </c>
-      <c r="B152" s="0" t="s">
+      <c r="B152" t="s">
         <v>495</v>
       </c>
-      <c r="C152" s="0" t="s">
+      <c r="C152" t="s">
         <v>496</v>
       </c>
-      <c r="D152" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="E152" s="0" t="s">
+      <c r="D152" t="s">
+        <v>15</v>
+      </c>
+      <c r="E152" t="s">
         <v>16</v>
       </c>
-      <c r="F152" s="0" t="s">
+      <c r="F152" t="s">
         <v>497</v>
       </c>
-      <c r="G152" s="0" t="s">
+      <c r="G152" t="s">
         <v>450</v>
       </c>
-      <c r="H152" s="0" t="s">
+      <c r="H152" t="s">
         <v>23</v>
       </c>
-      <c r="I152" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="J152" s="0" t="s">
+      <c r="I152" t="s">
+        <v>20</v>
+      </c>
+      <c r="J152" t="s">
         <v>20</v>
       </c>
       <c r="K152" s="2">
@@ -7573,35 +7992,35 @@
         <v>1200</v>
       </c>
     </row>
-    <row r="153">
-      <c r="A153" s="0" t="s">
+    <row r="153" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A153" t="s">
         <v>498</v>
       </c>
-      <c r="B153" s="0" t="s">
+      <c r="B153" t="s">
         <v>499</v>
       </c>
-      <c r="C153" s="0" t="s">
+      <c r="C153" t="s">
         <v>500</v>
       </c>
-      <c r="D153" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="E153" s="0" t="s">
+      <c r="D153" t="s">
+        <v>15</v>
+      </c>
+      <c r="E153" t="s">
         <v>16</v>
       </c>
-      <c r="F153" s="0" t="s">
+      <c r="F153" t="s">
         <v>501</v>
       </c>
-      <c r="G153" s="0" t="s">
+      <c r="G153" t="s">
         <v>36</v>
       </c>
-      <c r="H153" s="0" t="s">
+      <c r="H153" t="s">
         <v>23</v>
       </c>
-      <c r="I153" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="J153" s="0" t="s">
+      <c r="I153" t="s">
+        <v>20</v>
+      </c>
+      <c r="J153" t="s">
         <v>20</v>
       </c>
       <c r="K153" s="2">
@@ -7611,35 +8030,35 @@
         <v>4800</v>
       </c>
     </row>
-    <row r="154">
-      <c r="A154" s="0" t="s">
+    <row r="154" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A154" t="s">
         <v>498</v>
       </c>
-      <c r="B154" s="0" t="s">
+      <c r="B154" t="s">
         <v>499</v>
       </c>
-      <c r="C154" s="0" t="s">
+      <c r="C154" t="s">
         <v>500</v>
       </c>
-      <c r="D154" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="E154" s="0" t="s">
+      <c r="D154" t="s">
+        <v>15</v>
+      </c>
+      <c r="E154" t="s">
         <v>16</v>
       </c>
-      <c r="F154" s="0" t="s">
+      <c r="F154" t="s">
         <v>502</v>
       </c>
-      <c r="G154" s="0" t="s">
+      <c r="G154" t="s">
         <v>269</v>
       </c>
-      <c r="H154" s="0" t="s">
+      <c r="H154" t="s">
         <v>23</v>
       </c>
-      <c r="I154" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="J154" s="0" t="s">
+      <c r="I154" t="s">
+        <v>20</v>
+      </c>
+      <c r="J154" t="s">
         <v>20</v>
       </c>
       <c r="K154" s="2">
@@ -7649,35 +8068,35 @@
         <v>1800</v>
       </c>
     </row>
-    <row r="155">
-      <c r="A155" s="0" t="s">
+    <row r="155" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A155" t="s">
         <v>498</v>
       </c>
-      <c r="B155" s="0" t="s">
+      <c r="B155" t="s">
         <v>499</v>
       </c>
-      <c r="C155" s="0" t="s">
+      <c r="C155" t="s">
         <v>500</v>
       </c>
-      <c r="D155" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="E155" s="0" t="s">
+      <c r="D155" t="s">
+        <v>15</v>
+      </c>
+      <c r="E155" t="s">
         <v>16</v>
       </c>
-      <c r="F155" s="0" t="s">
+      <c r="F155" t="s">
         <v>503</v>
       </c>
-      <c r="G155" s="0" t="s">
+      <c r="G155" t="s">
         <v>269</v>
       </c>
-      <c r="H155" s="0" t="s">
+      <c r="H155" t="s">
         <v>23</v>
       </c>
-      <c r="I155" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="J155" s="0" t="s">
+      <c r="I155" t="s">
+        <v>20</v>
+      </c>
+      <c r="J155" t="s">
         <v>20</v>
       </c>
       <c r="K155" s="2">
@@ -7687,35 +8106,35 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="156">
-      <c r="A156" s="0" t="s">
+    <row r="156" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A156" t="s">
         <v>498</v>
       </c>
-      <c r="B156" s="0" t="s">
+      <c r="B156" t="s">
         <v>499</v>
       </c>
-      <c r="C156" s="0" t="s">
+      <c r="C156" t="s">
         <v>500</v>
       </c>
-      <c r="D156" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="E156" s="0" t="s">
+      <c r="D156" t="s">
+        <v>15</v>
+      </c>
+      <c r="E156" t="s">
         <v>16</v>
       </c>
-      <c r="F156" s="0" t="s">
+      <c r="F156" t="s">
         <v>504</v>
       </c>
-      <c r="G156" s="0" t="s">
+      <c r="G156" t="s">
         <v>267</v>
       </c>
-      <c r="H156" s="0" t="s">
+      <c r="H156" t="s">
         <v>23</v>
       </c>
-      <c r="I156" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="J156" s="0" t="s">
+      <c r="I156" t="s">
+        <v>20</v>
+      </c>
+      <c r="J156" t="s">
         <v>20</v>
       </c>
       <c r="K156" s="2">
@@ -7725,35 +8144,35 @@
         <v>2400</v>
       </c>
     </row>
-    <row r="157">
-      <c r="A157" s="0" t="s">
+    <row r="157" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A157" t="s">
         <v>505</v>
       </c>
-      <c r="B157" s="0" t="s">
+      <c r="B157" t="s">
         <v>506</v>
       </c>
-      <c r="C157" s="0" t="s">
+      <c r="C157" t="s">
         <v>507</v>
       </c>
-      <c r="D157" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="E157" s="0" t="s">
+      <c r="D157" t="s">
+        <v>15</v>
+      </c>
+      <c r="E157" t="s">
         <v>177</v>
       </c>
-      <c r="F157" s="0" t="s">
+      <c r="F157" t="s">
         <v>508</v>
       </c>
-      <c r="G157" s="0" t="s">
+      <c r="G157" t="s">
         <v>271</v>
       </c>
-      <c r="H157" s="0" t="s">
+      <c r="H157" t="s">
         <v>23</v>
       </c>
-      <c r="I157" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="J157" s="0" t="s">
+      <c r="I157" t="s">
+        <v>20</v>
+      </c>
+      <c r="J157" t="s">
         <v>20</v>
       </c>
       <c r="K157" s="2">
@@ -7763,35 +8182,35 @@
         <v>3078</v>
       </c>
     </row>
-    <row r="158">
-      <c r="A158" s="0" t="s">
+    <row r="158" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A158" t="s">
         <v>505</v>
       </c>
-      <c r="B158" s="0" t="s">
+      <c r="B158" t="s">
         <v>506</v>
       </c>
-      <c r="C158" s="0" t="s">
+      <c r="C158" t="s">
         <v>507</v>
       </c>
-      <c r="D158" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="E158" s="0" t="s">
+      <c r="D158" t="s">
+        <v>15</v>
+      </c>
+      <c r="E158" t="s">
         <v>177</v>
       </c>
-      <c r="F158" s="0" t="s">
+      <c r="F158" t="s">
         <v>509</v>
       </c>
-      <c r="G158" s="0" t="s">
+      <c r="G158" t="s">
         <v>271</v>
       </c>
-      <c r="H158" s="0" t="s">
+      <c r="H158" t="s">
         <v>23</v>
       </c>
-      <c r="I158" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="J158" s="0" t="s">
+      <c r="I158" t="s">
+        <v>20</v>
+      </c>
+      <c r="J158" t="s">
         <v>20</v>
       </c>
       <c r="K158" s="2">
@@ -7801,35 +8220,35 @@
         <v>1872</v>
       </c>
     </row>
-    <row r="159">
-      <c r="A159" s="0" t="s">
+    <row r="159" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A159" t="s">
         <v>505</v>
       </c>
-      <c r="B159" s="0" t="s">
+      <c r="B159" t="s">
         <v>506</v>
       </c>
-      <c r="C159" s="0" t="s">
+      <c r="C159" t="s">
         <v>507</v>
       </c>
-      <c r="D159" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="E159" s="0" t="s">
+      <c r="D159" t="s">
+        <v>15</v>
+      </c>
+      <c r="E159" t="s">
         <v>177</v>
       </c>
-      <c r="F159" s="0" t="s">
+      <c r="F159" t="s">
         <v>510</v>
       </c>
-      <c r="G159" s="0" t="s">
+      <c r="G159" t="s">
         <v>72</v>
       </c>
-      <c r="H159" s="0" t="s">
-        <v>19</v>
-      </c>
-      <c r="I159" s="0" t="s">
+      <c r="H159" t="s">
+        <v>19</v>
+      </c>
+      <c r="I159" t="s">
         <v>23</v>
       </c>
-      <c r="J159" s="0" t="s">
+      <c r="J159" t="s">
         <v>23</v>
       </c>
       <c r="K159" s="2">
@@ -7839,35 +8258,35 @@
         <v>3078</v>
       </c>
     </row>
-    <row r="160">
-      <c r="A160" s="0" t="s">
+    <row r="160" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A160" t="s">
         <v>505</v>
       </c>
-      <c r="B160" s="0" t="s">
+      <c r="B160" t="s">
         <v>506</v>
       </c>
-      <c r="C160" s="0" t="s">
+      <c r="C160" t="s">
         <v>507</v>
       </c>
-      <c r="D160" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="E160" s="0" t="s">
+      <c r="D160" t="s">
+        <v>15</v>
+      </c>
+      <c r="E160" t="s">
         <v>177</v>
       </c>
-      <c r="F160" s="0" t="s">
+      <c r="F160" t="s">
         <v>511</v>
       </c>
-      <c r="G160" s="0" t="s">
+      <c r="G160" t="s">
         <v>512</v>
       </c>
-      <c r="H160" s="0" t="s">
-        <v>19</v>
-      </c>
-      <c r="I160" s="0" t="s">
+      <c r="H160" t="s">
+        <v>19</v>
+      </c>
+      <c r="I160" t="s">
         <v>23</v>
       </c>
-      <c r="J160" s="0" t="s">
+      <c r="J160" t="s">
         <v>23</v>
       </c>
       <c r="K160" s="2">
@@ -7877,35 +8296,35 @@
         <v>1872</v>
       </c>
     </row>
-    <row r="161">
-      <c r="A161" s="0" t="s">
+    <row r="161" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A161" t="s">
         <v>513</v>
       </c>
-      <c r="B161" s="0" t="s">
+      <c r="B161" t="s">
         <v>514</v>
       </c>
-      <c r="C161" s="0" t="s">
+      <c r="C161" t="s">
         <v>515</v>
       </c>
-      <c r="D161" s="0" t="s">
+      <c r="D161" t="s">
         <v>516</v>
       </c>
-      <c r="E161" s="0" t="s">
+      <c r="E161" t="s">
         <v>28</v>
       </c>
-      <c r="F161" s="0" t="s">
+      <c r="F161" t="s">
         <v>517</v>
       </c>
-      <c r="G161" s="0" t="s">
+      <c r="G161" t="s">
         <v>30</v>
       </c>
-      <c r="H161" s="0" t="s">
-        <v>19</v>
-      </c>
-      <c r="I161" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="J161" s="0" t="s">
+      <c r="H161" t="s">
+        <v>19</v>
+      </c>
+      <c r="I161" t="s">
+        <v>20</v>
+      </c>
+      <c r="J161" t="s">
         <v>23</v>
       </c>
       <c r="K161" s="2">
@@ -7915,35 +8334,35 @@
         <v>5274.99</v>
       </c>
     </row>
-    <row r="162">
-      <c r="A162" s="0" t="s">
+    <row r="162" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A162" t="s">
         <v>518</v>
       </c>
-      <c r="B162" s="0" t="s">
+      <c r="B162" t="s">
         <v>519</v>
       </c>
-      <c r="C162" s="0" t="s">
+      <c r="C162" t="s">
         <v>520</v>
       </c>
-      <c r="D162" s="0" t="s">
+      <c r="D162" t="s">
         <v>27</v>
       </c>
-      <c r="E162" s="0" t="s">
+      <c r="E162" t="s">
         <v>28</v>
       </c>
-      <c r="F162" s="0" t="s">
+      <c r="F162" t="s">
         <v>521</v>
       </c>
-      <c r="G162" s="0" t="s">
+      <c r="G162" t="s">
         <v>30</v>
       </c>
-      <c r="H162" s="0" t="s">
-        <v>19</v>
-      </c>
-      <c r="I162" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="J162" s="0" t="s">
+      <c r="H162" t="s">
+        <v>19</v>
+      </c>
+      <c r="I162" t="s">
+        <v>20</v>
+      </c>
+      <c r="J162" t="s">
         <v>20</v>
       </c>
       <c r="K162" s="2">
@@ -7953,35 +8372,35 @@
         <v>122120.39</v>
       </c>
     </row>
-    <row r="163">
-      <c r="A163" s="0" t="s">
+    <row r="163" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A163" t="s">
         <v>522</v>
       </c>
-      <c r="B163" s="0" t="s">
+      <c r="B163" t="s">
         <v>523</v>
       </c>
-      <c r="C163" s="0" t="s">
+      <c r="C163" t="s">
         <v>520</v>
       </c>
-      <c r="D163" s="0" t="s">
+      <c r="D163" t="s">
         <v>27</v>
       </c>
-      <c r="E163" s="0" t="s">
+      <c r="E163" t="s">
         <v>28</v>
       </c>
-      <c r="F163" s="0" t="s">
+      <c r="F163" t="s">
         <v>524</v>
       </c>
-      <c r="G163" s="0" t="s">
+      <c r="G163" t="s">
         <v>210</v>
       </c>
-      <c r="H163" s="0" t="s">
-        <v>19</v>
-      </c>
-      <c r="I163" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="J163" s="0" t="s">
+      <c r="H163" t="s">
+        <v>19</v>
+      </c>
+      <c r="I163" t="s">
+        <v>20</v>
+      </c>
+      <c r="J163" t="s">
         <v>20</v>
       </c>
       <c r="K163" s="2">
@@ -7991,35 +8410,35 @@
         <v>3016</v>
       </c>
     </row>
-    <row r="164">
-      <c r="A164" s="0" t="s">
+    <row r="164" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A164" t="s">
         <v>525</v>
       </c>
-      <c r="B164" s="0" t="s">
+      <c r="B164" t="s">
         <v>526</v>
       </c>
-      <c r="C164" s="0" t="s">
+      <c r="C164" t="s">
         <v>527</v>
       </c>
-      <c r="D164" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="E164" s="0" t="s">
+      <c r="D164" t="s">
+        <v>15</v>
+      </c>
+      <c r="E164" t="s">
         <v>177</v>
       </c>
-      <c r="F164" s="0" t="s">
+      <c r="F164" t="s">
         <v>528</v>
       </c>
-      <c r="G164" s="0" t="s">
+      <c r="G164" t="s">
         <v>452</v>
       </c>
-      <c r="H164" s="0" t="s">
-        <v>19</v>
-      </c>
-      <c r="I164" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="J164" s="0" t="s">
+      <c r="H164" t="s">
+        <v>19</v>
+      </c>
+      <c r="I164" t="s">
+        <v>20</v>
+      </c>
+      <c r="J164" t="s">
         <v>23</v>
       </c>
       <c r="K164" s="2">
@@ -8029,35 +8448,35 @@
         <v>12135.6</v>
       </c>
     </row>
-    <row r="165">
-      <c r="A165" s="0" t="s">
+    <row r="165" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A165" t="s">
         <v>525</v>
       </c>
-      <c r="B165" s="0" t="s">
+      <c r="B165" t="s">
         <v>526</v>
       </c>
-      <c r="C165" s="0" t="s">
+      <c r="C165" t="s">
         <v>527</v>
       </c>
-      <c r="D165" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="E165" s="0" t="s">
+      <c r="D165" t="s">
+        <v>15</v>
+      </c>
+      <c r="E165" t="s">
         <v>177</v>
       </c>
-      <c r="F165" s="0" t="s">
+      <c r="F165" t="s">
         <v>529</v>
       </c>
-      <c r="G165" s="0" t="s">
+      <c r="G165" t="s">
         <v>452</v>
       </c>
-      <c r="H165" s="0" t="s">
-        <v>19</v>
-      </c>
-      <c r="I165" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="J165" s="0" t="s">
+      <c r="H165" t="s">
+        <v>19</v>
+      </c>
+      <c r="I165" t="s">
+        <v>20</v>
+      </c>
+      <c r="J165" t="s">
         <v>23</v>
       </c>
       <c r="K165" s="2">
@@ -8067,35 +8486,35 @@
         <v>600</v>
       </c>
     </row>
-    <row r="166">
-      <c r="A166" s="0" t="s">
+    <row r="166" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A166" t="s">
         <v>525</v>
       </c>
-      <c r="B166" s="0" t="s">
+      <c r="B166" t="s">
         <v>526</v>
       </c>
-      <c r="C166" s="0" t="s">
+      <c r="C166" t="s">
         <v>527</v>
       </c>
-      <c r="D166" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="E166" s="0" t="s">
+      <c r="D166" t="s">
+        <v>15</v>
+      </c>
+      <c r="E166" t="s">
         <v>177</v>
       </c>
-      <c r="F166" s="0" t="s">
+      <c r="F166" t="s">
         <v>530</v>
       </c>
-      <c r="G166" s="0" t="s">
+      <c r="G166" t="s">
         <v>452</v>
       </c>
-      <c r="H166" s="0" t="s">
-        <v>19</v>
-      </c>
-      <c r="I166" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="J166" s="0" t="s">
+      <c r="H166" t="s">
+        <v>19</v>
+      </c>
+      <c r="I166" t="s">
+        <v>20</v>
+      </c>
+      <c r="J166" t="s">
         <v>23</v>
       </c>
       <c r="K166" s="2">
@@ -8105,35 +8524,35 @@
         <v>16180</v>
       </c>
     </row>
-    <row r="167">
-      <c r="A167" s="0" t="s">
+    <row r="167" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A167" t="s">
         <v>531</v>
       </c>
-      <c r="B167" s="0" t="s">
+      <c r="B167" t="s">
         <v>526</v>
       </c>
-      <c r="C167" s="0" t="s">
+      <c r="C167" t="s">
         <v>527</v>
       </c>
-      <c r="D167" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="E167" s="0" t="s">
+      <c r="D167" t="s">
+        <v>15</v>
+      </c>
+      <c r="E167" t="s">
         <v>177</v>
       </c>
-      <c r="F167" s="0" t="s">
+      <c r="F167" t="s">
         <v>532</v>
       </c>
-      <c r="G167" s="0" t="s">
+      <c r="G167" t="s">
         <v>448</v>
       </c>
-      <c r="H167" s="0" t="s">
-        <v>19</v>
-      </c>
-      <c r="I167" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="J167" s="0" t="s">
+      <c r="H167" t="s">
+        <v>19</v>
+      </c>
+      <c r="I167" t="s">
+        <v>20</v>
+      </c>
+      <c r="J167" t="s">
         <v>20</v>
       </c>
       <c r="K167" s="2">
@@ -8143,35 +8562,35 @@
         <v>35846</v>
       </c>
     </row>
-    <row r="168">
-      <c r="A168" s="0" t="s">
+    <row r="168" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A168" t="s">
         <v>531</v>
       </c>
-      <c r="B168" s="0" t="s">
+      <c r="B168" t="s">
         <v>526</v>
       </c>
-      <c r="C168" s="0" t="s">
+      <c r="C168" t="s">
         <v>527</v>
       </c>
-      <c r="D168" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="E168" s="0" t="s">
+      <c r="D168" t="s">
+        <v>15</v>
+      </c>
+      <c r="E168" t="s">
         <v>177</v>
       </c>
-      <c r="F168" s="0" t="s">
+      <c r="F168" t="s">
         <v>533</v>
       </c>
-      <c r="G168" s="0" t="s">
+      <c r="G168" t="s">
         <v>452</v>
       </c>
-      <c r="H168" s="0" t="s">
-        <v>19</v>
-      </c>
-      <c r="I168" s="0" t="s">
+      <c r="H168" t="s">
+        <v>19</v>
+      </c>
+      <c r="I168" t="s">
         <v>23</v>
       </c>
-      <c r="J168" s="0" t="s">
+      <c r="J168" t="s">
         <v>23</v>
       </c>
       <c r="K168" s="2">
@@ -8181,35 +8600,35 @@
         <v>45000</v>
       </c>
     </row>
-    <row r="169">
-      <c r="A169" s="0" t="s">
+    <row r="169" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A169" t="s">
         <v>534</v>
       </c>
-      <c r="B169" s="0" t="s">
+      <c r="B169" t="s">
         <v>535</v>
       </c>
-      <c r="C169" s="0" t="s">
+      <c r="C169" t="s">
         <v>536</v>
       </c>
-      <c r="D169" s="0" t="s">
+      <c r="D169" t="s">
         <v>27</v>
       </c>
-      <c r="E169" s="0" t="s">
+      <c r="E169" t="s">
         <v>28</v>
       </c>
-      <c r="F169" s="0" t="s">
+      <c r="F169" t="s">
         <v>537</v>
       </c>
-      <c r="G169" s="0" t="s">
+      <c r="G169" t="s">
         <v>101</v>
       </c>
-      <c r="H169" s="0" t="s">
-        <v>19</v>
-      </c>
-      <c r="I169" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="J169" s="0" t="s">
+      <c r="H169" t="s">
+        <v>19</v>
+      </c>
+      <c r="I169" t="s">
+        <v>20</v>
+      </c>
+      <c r="J169" t="s">
         <v>20</v>
       </c>
       <c r="K169" s="2">
@@ -8219,35 +8638,35 @@
         <v>326.88</v>
       </c>
     </row>
-    <row r="170">
-      <c r="A170" s="0" t="s">
+    <row r="170" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A170" t="s">
         <v>538</v>
       </c>
-      <c r="B170" s="0" t="s">
+      <c r="B170" t="s">
         <v>539</v>
       </c>
-      <c r="C170" s="0" t="s">
+      <c r="C170" t="s">
         <v>540</v>
       </c>
-      <c r="D170" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="E170" s="0" t="s">
+      <c r="D170" t="s">
+        <v>15</v>
+      </c>
+      <c r="E170" t="s">
         <v>16</v>
       </c>
-      <c r="F170" s="0" t="s">
+      <c r="F170" t="s">
         <v>541</v>
       </c>
-      <c r="G170" s="0" t="s">
+      <c r="G170" t="s">
         <v>375</v>
       </c>
-      <c r="H170" s="0" t="s">
+      <c r="H170" t="s">
         <v>23</v>
       </c>
-      <c r="I170" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="J170" s="0" t="s">
+      <c r="I170" t="s">
+        <v>20</v>
+      </c>
+      <c r="J170" t="s">
         <v>20</v>
       </c>
       <c r="K170" s="2">
@@ -8257,73 +8676,73 @@
         <v>2035.7</v>
       </c>
     </row>
-    <row r="171">
-      <c r="A171" s="0" t="s">
+    <row r="171" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A171" t="s">
         <v>542</v>
       </c>
-      <c r="B171" s="0" t="s">
+      <c r="B171" t="s">
         <v>543</v>
       </c>
-      <c r="C171" s="0" t="s">
+      <c r="C171" t="s">
         <v>544</v>
       </c>
-      <c r="D171" s="0" t="s">
+      <c r="D171" t="s">
         <v>27</v>
       </c>
-      <c r="E171" s="0" t="s">
+      <c r="E171" t="s">
         <v>76</v>
       </c>
-      <c r="F171" s="0" t="s">
+      <c r="F171" t="s">
         <v>545</v>
       </c>
-      <c r="G171" s="0" t="s">
+      <c r="G171" t="s">
         <v>135</v>
       </c>
-      <c r="H171" s="0" t="s">
-        <v>19</v>
-      </c>
-      <c r="I171" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="J171" s="0" t="s">
+      <c r="H171" t="s">
+        <v>19</v>
+      </c>
+      <c r="I171" t="s">
+        <v>20</v>
+      </c>
+      <c r="J171" t="s">
         <v>20</v>
       </c>
       <c r="K171" s="2">
         <v>1</v>
       </c>
       <c r="L171" s="2">
-        <v>38424.12</v>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" s="0" t="s">
+        <v>38424.120000000003</v>
+      </c>
+    </row>
+    <row r="172" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A172" t="s">
         <v>546</v>
       </c>
-      <c r="B172" s="0" t="s">
+      <c r="B172" t="s">
         <v>547</v>
       </c>
-      <c r="C172" s="0" t="s">
+      <c r="C172" t="s">
         <v>548</v>
       </c>
-      <c r="D172" s="0" t="s">
+      <c r="D172" t="s">
         <v>27</v>
       </c>
-      <c r="E172" s="0" t="s">
+      <c r="E172" t="s">
         <v>28</v>
       </c>
-      <c r="F172" s="0" t="s">
+      <c r="F172" t="s">
         <v>549</v>
       </c>
-      <c r="G172" s="0" t="s">
+      <c r="G172" t="s">
         <v>250</v>
       </c>
-      <c r="H172" s="0" t="s">
-        <v>19</v>
-      </c>
-      <c r="I172" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="J172" s="0" t="s">
+      <c r="H172" t="s">
+        <v>19</v>
+      </c>
+      <c r="I172" t="s">
+        <v>20</v>
+      </c>
+      <c r="J172" t="s">
         <v>20</v>
       </c>
       <c r="K172" s="2">
@@ -8333,73 +8752,73 @@
         <v>32588.87</v>
       </c>
     </row>
-    <row r="173">
-      <c r="A173" s="0" t="s">
+    <row r="173" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A173" t="s">
         <v>550</v>
       </c>
-      <c r="B173" s="0" t="s">
+      <c r="B173" t="s">
         <v>551</v>
       </c>
-      <c r="C173" s="0" t="s">
+      <c r="C173" t="s">
         <v>552</v>
       </c>
-      <c r="D173" s="0" t="s">
+      <c r="D173" t="s">
         <v>27</v>
       </c>
-      <c r="E173" s="0" t="s">
+      <c r="E173" t="s">
         <v>28</v>
       </c>
-      <c r="F173" s="0" t="s">
+      <c r="F173" t="s">
         <v>553</v>
       </c>
-      <c r="G173" s="0" t="s">
+      <c r="G173" t="s">
         <v>427</v>
       </c>
-      <c r="H173" s="0" t="s">
-        <v>19</v>
-      </c>
-      <c r="I173" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="J173" s="0" t="s">
+      <c r="H173" t="s">
+        <v>19</v>
+      </c>
+      <c r="I173" t="s">
+        <v>20</v>
+      </c>
+      <c r="J173" t="s">
         <v>20</v>
       </c>
       <c r="K173" s="2">
         <v>2</v>
       </c>
       <c r="L173" s="2">
-        <v>4198.1</v>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" s="0" t="s">
+        <v>4198.1000000000004</v>
+      </c>
+    </row>
+    <row r="174" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A174" t="s">
         <v>554</v>
       </c>
-      <c r="B174" s="0" t="s">
+      <c r="B174" t="s">
         <v>555</v>
       </c>
-      <c r="C174" s="0" t="s">
+      <c r="C174" t="s">
         <v>556</v>
       </c>
-      <c r="D174" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="E174" s="0" t="s">
+      <c r="D174" t="s">
+        <v>15</v>
+      </c>
+      <c r="E174" t="s">
         <v>16</v>
       </c>
-      <c r="F174" s="0" t="s">
+      <c r="F174" t="s">
         <v>557</v>
       </c>
-      <c r="G174" s="0" t="s">
+      <c r="G174" t="s">
         <v>309</v>
       </c>
-      <c r="H174" s="0" t="s">
+      <c r="H174" t="s">
         <v>23</v>
       </c>
-      <c r="I174" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="J174" s="0" t="s">
+      <c r="I174" t="s">
+        <v>20</v>
+      </c>
+      <c r="J174" t="s">
         <v>20</v>
       </c>
       <c r="K174" s="2">
@@ -8409,35 +8828,35 @@
         <v>1850</v>
       </c>
     </row>
-    <row r="175">
-      <c r="A175" s="0" t="s">
+    <row r="175" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A175" t="s">
         <v>558</v>
       </c>
-      <c r="B175" s="0" t="s">
+      <c r="B175" t="s">
         <v>559</v>
       </c>
-      <c r="C175" s="0" t="s">
+      <c r="C175" t="s">
         <v>560</v>
       </c>
-      <c r="D175" s="0" t="s">
+      <c r="D175" t="s">
         <v>27</v>
       </c>
-      <c r="E175" s="0" t="s">
+      <c r="E175" t="s">
         <v>28</v>
       </c>
-      <c r="F175" s="0" t="s">
+      <c r="F175" t="s">
         <v>561</v>
       </c>
-      <c r="G175" s="0" t="s">
+      <c r="G175" t="s">
         <v>53</v>
       </c>
-      <c r="H175" s="0" t="s">
-        <v>19</v>
-      </c>
-      <c r="I175" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="J175" s="0" t="s">
+      <c r="H175" t="s">
+        <v>19</v>
+      </c>
+      <c r="I175" t="s">
+        <v>20</v>
+      </c>
+      <c r="J175" t="s">
         <v>20</v>
       </c>
       <c r="K175" s="2">
@@ -8447,35 +8866,35 @@
         <v>936</v>
       </c>
     </row>
-    <row r="176">
-      <c r="A176" s="0" t="s">
+    <row r="176" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A176" t="s">
         <v>562</v>
       </c>
-      <c r="B176" s="0" t="s">
+      <c r="B176" t="s">
         <v>563</v>
       </c>
-      <c r="C176" s="0" t="s">
+      <c r="C176" t="s">
         <v>564</v>
       </c>
-      <c r="D176" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="E176" s="0" t="s">
+      <c r="D176" t="s">
+        <v>15</v>
+      </c>
+      <c r="E176" t="s">
         <v>16</v>
       </c>
-      <c r="F176" s="0" t="s">
+      <c r="F176" t="s">
         <v>565</v>
       </c>
-      <c r="G176" s="0" t="s">
+      <c r="G176" t="s">
         <v>566</v>
       </c>
-      <c r="H176" s="0" t="s">
-        <v>19</v>
-      </c>
-      <c r="I176" s="0" t="s">
+      <c r="H176" t="s">
+        <v>19</v>
+      </c>
+      <c r="I176" t="s">
         <v>23</v>
       </c>
-      <c r="J176" s="0" t="s">
+      <c r="J176" t="s">
         <v>23</v>
       </c>
       <c r="K176" s="2">
@@ -8485,83 +8904,238 @@
         <v>84946.72</v>
       </c>
     </row>
-    <row r="177">
-      <c r="A177" s="0" t="s">
+    <row r="177" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A177" t="s">
         <v>567</v>
       </c>
-      <c r="B177" s="0" t="s">
+      <c r="B177" t="s">
         <v>568</v>
       </c>
-      <c r="C177" s="0" t="s">
+      <c r="C177" t="s">
         <v>569</v>
       </c>
-      <c r="D177" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="E177" s="0" t="s">
+      <c r="D177" t="s">
+        <v>15</v>
+      </c>
+      <c r="E177" t="s">
         <v>177</v>
       </c>
-      <c r="F177" s="0" t="s">
+      <c r="F177" t="s">
         <v>570</v>
       </c>
-      <c r="G177" s="0" t="s">
+      <c r="G177" t="s">
         <v>464</v>
       </c>
-      <c r="H177" s="0" t="s">
-        <v>19</v>
-      </c>
-      <c r="I177" s="0" t="s">
+      <c r="H177" t="s">
+        <v>19</v>
+      </c>
+      <c r="I177" t="s">
         <v>23</v>
       </c>
-      <c r="J177" s="0" t="s">
+      <c r="J177" t="s">
         <v>23</v>
       </c>
       <c r="K177" s="2">
         <v>2</v>
       </c>
       <c r="L177" s="2">
-        <v>4845.27</v>
-      </c>
-    </row>
-    <row r="178">
-      <c r="A178" s="0" t="s">
+        <v>4845.2700000000004</v>
+      </c>
+    </row>
+    <row r="178" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A178" t="s">
         <v>567</v>
       </c>
-      <c r="B178" s="0" t="s">
+      <c r="B178" t="s">
         <v>568</v>
       </c>
-      <c r="C178" s="0" t="s">
+      <c r="C178" t="s">
         <v>569</v>
       </c>
-      <c r="D178" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="E178" s="0" t="s">
+      <c r="D178" t="s">
+        <v>15</v>
+      </c>
+      <c r="E178" t="s">
         <v>177</v>
       </c>
-      <c r="F178" s="0" t="s">
+      <c r="F178" t="s">
         <v>571</v>
       </c>
-      <c r="G178" s="0" t="s">
+      <c r="G178" t="s">
         <v>452</v>
       </c>
-      <c r="H178" s="0" t="s">
-        <v>19</v>
-      </c>
-      <c r="I178" s="0" t="s">
+      <c r="H178" t="s">
+        <v>19</v>
+      </c>
+      <c r="I178" t="s">
         <v>23</v>
       </c>
-      <c r="J178" s="0" t="s">
+      <c r="J178" t="s">
         <v>23</v>
       </c>
       <c r="K178" s="2">
         <v>2</v>
       </c>
       <c r="L178" s="2">
-        <v>2437.3</v>
+        <v>2437.3000000000002</v>
       </c>
     </row>
   </sheetData>
-  <headerFooter/>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F7FEAA92-B6C3-4EC1-AE38-6BB7C9890E40}">
+  <dimension ref="A1:A29"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>591</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>595</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>598</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>600</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>